--- a/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_24.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_24.xlsx
@@ -625,76 +625,76 @@
         <v>138</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.7700348484457962</v>
+        <v>-0.7370119879005941</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.103089198929645</v>
+        <v>-1.069662585533663</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.093661067445439</v>
+        <v>-1.058553767591675</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.404216796312184</v>
+        <v>-5.36829692697804</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.370856200076126</v>
+        <v>-9.305651774434764</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.467118830857551</v>
+        <v>-8.402080740848895</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.075705367504248</v>
+        <v>-7.009722515199364</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.633589938508678</v>
+        <v>-6.567240122390594</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.47923465560492</v>
+        <v>-9.412906629106175</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.531141626505679</v>
+        <v>-9.463873397188983</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.42581351045882</v>
+        <v>-11.35882835737069</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.819574366266657</v>
+        <v>-8.752208265781995</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.054055842569483</v>
+        <v>-6.98533338169478</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-5.109742742283295</v>
+        <v>-5.040710970102147</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-2.878218367764156</v>
+        <v>-2.808368426337132</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-4.454220647000092</v>
+        <v>-4.385022998492637</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-7.481695927153993</v>
+        <v>-7.412306258314537</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.035592394911262</v>
+        <v>-8.966038189357228</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-10.99331149204863</v>
+        <v>-10.92396623130399</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-11.53387289896058</v>
+        <v>-11.46469912353386</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-11.35634826591011</v>
+        <v>-11.28649358188908</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-9.263410624903457</v>
+        <v>-9.193417982108329</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.542936696314335</v>
+        <v>-7.473217247687842</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-6.172133231629793</v>
+        <v>-6.102278883922686</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>202</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.610878807427369</v>
+        <v>-5.577934615079201</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.945302266632957</v>
+        <v>-5.911951961594625</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.969130796336032</v>
+        <v>-1.934060701458939</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.677899649569127</v>
+        <v>-2.641991584128888</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.532797336242645</v>
+        <v>-3.46760492717388</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.856242628573085</v>
+        <v>-2.791216130757292</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.625662306701464</v>
+        <v>-3.559705356561444</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.44156464007208</v>
+        <v>-1.375226571160923</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.877849927992358</v>
+        <v>-2.81152747066978</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-4.141861324825086</v>
+        <v>-4.074606444205692</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.869690747247894</v>
+        <v>-3.802707659386698</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.642451860870182</v>
+        <v>-4.575103146906748</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.750890498146013</v>
+        <v>-6.682201925026078</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-9.441059252012117</v>
+        <v>-9.372077389131235</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-12.07599220523579</v>
+        <v>-12.0062051524858</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-11.48663564306847</v>
+        <v>-11.41748713274159</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-10.63631471440313</v>
+        <v>-10.56695796545155</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-7.286454358540517</v>
+        <v>-7.21691610668131</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.590633990729707</v>
+        <v>-5.521294724712014</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.406057826977381</v>
+        <v>-5.336887707525307</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-3.972628093826252</v>
+        <v>-3.902774499224087</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-5.039686170850402</v>
+        <v>-4.969696706510852</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-7.24141511485174</v>
+        <v>-7.171698849658753</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-6.329975102773432</v>
+        <v>-6.260120755066048</v>
       </c>
     </row>
     <row r="8">
@@ -789,978 +789,978 @@
         <v>264</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.750485862802876</v>
+        <v>5.783502889584376</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.171833117762048</v>
+        <v>6.205260164010134</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.119400822238497</v>
+        <v>5.154498658234317</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.422278006728718</v>
+        <v>7.45824076600249</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.806625426962214</v>
+        <v>4.871814812351985</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4778571168706236</v>
+        <v>0.5428348442463431</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6661973228142983</v>
+        <v>-0.6002930065616141</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.956551669878245</v>
+        <v>-3.890305161945136</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.278503884776214</v>
+        <v>-1.21223819071384</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.671733549141003</v>
+        <v>-1.60452883611913</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.529997176010802</v>
+        <v>-2.46306819665633</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9235258894042317</v>
+        <v>-0.8562134611523646</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.9116487427705806</v>
+        <v>-0.8429856661466246</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.509794869892325</v>
+        <v>-1.4408294139606</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.167434283321512</v>
+        <v>-2.097656459422915</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.330779315848339</v>
+        <v>-2.261641273551447</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.710001934485916</v>
+        <v>-1.640654616889279</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.084122140050148</v>
+        <v>-4.01460733563831</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.6266728030485</v>
+        <v>-4.557357772692036</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-7.846255238752406</v>
+        <v>-7.777111667103952</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.635607328213631</v>
+        <v>-7.565775067204882</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.714808981246193</v>
+        <v>-7.644832999127992</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-7.443396105078421</v>
+        <v>-7.373685583801368</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-6.765018607123871</v>
+        <v>-6.695164259416686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 4.422</t>
+          <t>X ≈ 4.421</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>252</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2904489973836775</v>
+        <v>0.3233465791845163</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.31843895499231</v>
+        <v>2.351775650642828</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.644989996452892</v>
+        <v>3.680027310873378</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.513035642077661</v>
+        <v>4.548930058011628</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.156230290899337</v>
+        <v>4.221321287107529</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.285459770832887</v>
+        <v>8.350425718436171</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.310547188449952</v>
+        <v>8.376446904740753</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10.40408370723347</v>
+        <v>10.47036934579219</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>10.05485059523448</v>
+        <v>10.12113156620829</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>12.44662333333647</v>
+        <v>12.51386470435109</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>13.51473419781712</v>
+        <v>13.58171065683511</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>13.63604839836452</v>
+        <v>13.70339717538057</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>11.33726511075368</v>
+        <v>11.40594297986485</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>11.12173285734891</v>
+        <v>11.19071202902283</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>13.63253802222044</v>
+        <v>13.70234455871293</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>13.43943527556862</v>
+        <v>13.50859879485796</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>12.51916898887863</v>
+        <v>12.58853218495742</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>12.41876333769204</v>
+        <v>12.48829758786371</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>12.24267084255361</v>
+        <v>12.31200278008917</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>13.62255160701251</v>
+        <v>13.69171778185</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>15.85885216134168</v>
+        <v>15.92870540949666</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>16.58148242353233</v>
+        <v>16.65147340328075</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>15.67202745299119</v>
+        <v>15.74174474818817</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>13.6173767752715</v>
+        <v>13.68723112297878</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 5.008</t>
+          <t>X ≈ 5.007</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>266</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.547600711266533</v>
+        <v>4.580491997364014</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.821515730372603</v>
+        <v>6.854863936531174</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.885408165114569</v>
+        <v>6.920441079704077</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.925725951618396</v>
+        <v>6.961606296974914</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.926530125094331</v>
+        <v>9.991587718201117</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.624547221610513</v>
+        <v>8.689423534690931</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.728529669458958</v>
+        <v>9.794356363129062</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>10.57653263467155</v>
+        <v>10.64274150211627</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11.74313827764971</v>
+        <v>11.80936392158877</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>11.72613390948535</v>
+        <v>11.79330430966272</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>13.8736264552132</v>
+        <v>13.94055200524485</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>14.34907212685997</v>
+        <v>14.41637812191573</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>13.23896049926237</v>
+        <v>13.30759880465681</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>13.77413413889716</v>
+        <v>13.84308129992881</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>12.00006545950423</v>
+        <v>12.06981752988735</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>11.0999680614267</v>
+        <v>11.16907850700461</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>10.59678444767488</v>
+        <v>10.6661010844706</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>9.371822845524349</v>
+        <v>9.441311249780867</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>9.216270411816247</v>
+        <v>9.285564001735331</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>9.031755121200803</v>
+        <v>9.100886822439961</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>7.366089963738879</v>
+        <v>7.435909844168471</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>5.415102862641724</v>
+        <v>5.485067652444492</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.316219835757302</v>
+        <v>5.385924379005232</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>5.618212197159572</v>
+        <v>5.688066544866849</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 5.594</t>
+          <t>X ≈ 5.593</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.04807797451685</v>
+        <v>-1.18359687170728</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.902469008139938</v>
+        <v>2.782849844814351</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.516639088289061</v>
+        <v>2.402445914214155</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.079191923804018</v>
+        <v>0.9631450550543761</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.490439420500287</v>
+        <v>2.411101844058649</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.161540759261491</v>
+        <v>1.884231519090868</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.435115818572186</v>
+        <v>3.969587272829514</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.514069855601171</v>
+        <v>4.048254432024777</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.770658822811036</v>
+        <v>2.297162475360508</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.475384538908912</v>
+        <v>0.9942514183923947</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5236403406584245</v>
+        <v>0.3987798316129556</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.269376586130825</v>
+        <v>-0.5987789187693195</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1155450003992016</v>
+        <v>-0.6682262503453344</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.9474483572984624</v>
+        <v>0.3941132490318822</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6509344917247972</v>
+        <v>0.3009477668894931</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.8867074934105901</v>
+        <v>0.7507163979907503</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.905210538058476</v>
+        <v>2.98797063810715</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.085604064147475</v>
+        <v>2.377667499637703</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.943666618763686</v>
+        <v>2.234369804690076</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.054879043755321</v>
+        <v>1.341657593312419</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.1535034916796008</v>
+        <v>0.4398027339278698</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.07784392967311504</v>
+        <v>0.364418959435767</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.006944395618482702</v>
+        <v>0.2782001498267448</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.162228112247043</v>
+        <v>-0.8807019467592525</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 6.18</t>
+          <t>X ≈ 6.179</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.01254731896646177</v>
+        <v>0.2478683715226424</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.188800765409162</v>
+        <v>-0.9491897089198673</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.32722940403287</v>
+        <v>-1.091440831832479</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.316950223379095</v>
+        <v>-5.303869823491297</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.132759024325928</v>
+        <v>-4.337545088440329</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.945444277453738</v>
+        <v>-4.151669543302127</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.282009438512134</v>
+        <v>-4.49625939736837</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.566959655406492</v>
+        <v>-2.787682919394051</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.968336975326288</v>
+        <v>-1.193877715415731</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.29908751074192</v>
+        <v>-1.534320909832083</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.778047556470248</v>
+        <v>-3.44393078691963</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.494490087951888</v>
+        <v>-3.914964137580249</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.608112627255359</v>
+        <v>-4.786042171327139</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.82735608400386</v>
+        <v>-5.005853689491353</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-5.922476255535514</v>
+        <v>-6.098338775495598</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-7.524725088977952</v>
+        <v>-7.69086909505689</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-9.855862511416355</v>
+        <v>-10.00971191052359</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-9.525654274647586</v>
+        <v>-9.676046648708343</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-7.997545011920089</v>
+        <v>-8.153964595334031</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-6.496099967021131</v>
+        <v>-6.658527567518746</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-7.482127684130852</v>
+        <v>-7.642014864625622</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-9.762240712036395</v>
+        <v>-9.912410666356209</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-9.493269002267446</v>
+        <v>-9.643763865463285</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-7.81294278280145</v>
+        <v>-7.971081324807535</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 6.766</t>
+          <t>X ≈ 6.765</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>213</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.554977960289406</v>
+        <v>-1.522240503807495</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.760614115099948</v>
+        <v>-3.727441701861395</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.660685621070215</v>
+        <v>-5.625831334646747</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.168367455340906</v>
+        <v>-2.132784954569573</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.132251155453247</v>
+        <v>-1.066266674464465</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9454771872838847</v>
+        <v>-0.8790579878664531</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.248089465667888</v>
+        <v>-1.180548588573494</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5939493005949572</v>
+        <v>-0.5235562925115502</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3798709301817951</v>
+        <v>0.4529002433157174</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.011328052698268</v>
+        <v>1.086540368940881</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.751644080272001</v>
+        <v>1.827967494607918</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.805459137788034</v>
+        <v>3.887930603904678</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.425810375814272</v>
+        <v>6.51402142879703</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>8.07257769982477</v>
+        <v>8.164990742297391</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>7.891894391681085</v>
+        <v>7.97819950556373</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7.55736978747877</v>
+        <v>7.636445139082056</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.430299464437667</v>
+        <v>7.504168710421823</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>7.799351556899509</v>
+        <v>7.868570585325273</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>7.083264253302623</v>
+        <v>7.152330072273223</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.806439182827816</v>
+        <v>6.875385667701053</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.736840504457881</v>
+        <v>6.806521728248974</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.665513811316451</v>
+        <v>6.735385244853724</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.943809602785443</v>
+        <v>7.013467492730953</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.401861461164764</v>
+        <v>6.471715808872041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 7.352</t>
+          <t>X ≈ 7.351</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>203</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.940907328556563</v>
+        <v>1.202107105941863</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.002471974692035</v>
+        <v>-4.253669728649463</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2008988859301226</v>
+        <v>-0.05795632896548142</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.01686324281239848</v>
+        <v>-0.02245638645980108</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.335800147672423</v>
+        <v>-2.809596061060795</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1939359532036278</v>
+        <v>-0.3927638166362115</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.481863757402813</v>
+        <v>1.558281366962305</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.241743115085384</v>
+        <v>-1.172183088849479</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.668187601707949</v>
+        <v>-2.602605242848021</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.457704105771008</v>
+        <v>-2.390840904909858</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.695573347212836</v>
+        <v>-1.62707403290684</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.9571240060985957</v>
+        <v>1.035517327569146</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8246951565126253</v>
+        <v>0.9016813520044735</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.048906803261033</v>
+        <v>3.133165225104449</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.379306274057022</v>
+        <v>3.460321418473967</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.508781191166257</v>
+        <v>2.58310874299152</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.829762541354569</v>
+        <v>4.902993309511572</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>6.692245199702256</v>
+        <v>6.761317863883662</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.950004451526986</v>
+        <v>5.018932605976083</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.632443102248814</v>
+        <v>5.701285904117114</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>6.077799271334008</v>
+        <v>6.147405097538659</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>6.00745730413896</v>
+        <v>6.07727638640916</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.809698292242125</v>
+        <v>4.879326322419644</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.229308904445013</v>
+        <v>5.29916325215229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 7.938</t>
+          <t>X ≈ 7.937</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>241</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.155692325680711</v>
+        <v>0.07650253752765224</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.133388957985183</v>
+        <v>-2.321020058007818</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.567218215787847</v>
+        <v>-3.758067819760392</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.449476359155149</v>
+        <v>-3.644296614137659</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.987614379065697</v>
+        <v>-2.92733140888042</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.571127580562838</v>
+        <v>-1.504846600282029</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.930060879667387</v>
+        <v>-1.862460480668247</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.617411052637465</v>
+        <v>-2.551924345626631</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.397889447230312</v>
+        <v>-3.335584046950068</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.341657489744584</v>
+        <v>-3.278509094564669</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.535483303832059</v>
+        <v>-5.481211123531054</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-7.875434562628982</v>
+        <v>-7.826350458844423</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.28186929242549</v>
+        <v>-5.224902698876221</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.271702215607519</v>
+        <v>-4.209141931408119</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-3.277768593142653</v>
+        <v>-3.211267036386033</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.846702503769805</v>
+        <v>1.921868083838092</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.304873931725965</v>
+        <v>1.376258186184074</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.441256529369994</v>
+        <v>2.510018488162679</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.074077593092973</v>
+        <v>3.142770817223216</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.85182378015493</v>
+        <v>2.920468140401823</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.554784270241733</v>
+        <v>3.624245036228878</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.726843686044198</v>
+        <v>4.796570854305706</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.421068620489969</v>
+        <v>5.490653999859703</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.520031059668533</v>
+        <v>4.58988540737581</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 8.524</t>
+          <t>X ≈ 8.523</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.805028405202435</v>
+        <v>-5.028568705649597</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.597315057708983</v>
+        <v>-5.827613186650325</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.636287634369388</v>
+        <v>-5.855213474512155</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.234805566246415</v>
+        <v>-1.409053372576615</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.69726182560872</v>
+        <v>-6.893117527599905</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-7.910825100027779</v>
+        <v>-8.116570102671744</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.752510606065513</v>
+        <v>-7.949820509789205</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-6.634859590902693</v>
+        <v>-6.820323303098604</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-8.910554802402736</v>
+        <v>-9.119145302517978</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-9.674215202997168</v>
+        <v>-9.88596323167193</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-8.004780831886499</v>
+        <v>-8.204872465497736</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-10.6067387953147</v>
+        <v>-10.82731868743671</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-10.78422159417995</v>
+        <v>-11.00229709348044</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-12.40291462258185</v>
+        <v>-12.63176214880205</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-13.06434559753679</v>
+        <v>-13.28380769950012</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-14.81621302318877</v>
+        <v>-14.56952744082843</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-14.03146064433545</v>
+        <v>-14.23307914827237</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-17.41397271632948</v>
+        <v>-17.14859446296114</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-18.14977103976666</v>
+        <v>-17.88845676071823</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-16.57975961940001</v>
+        <v>-16.31139338805654</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-17.13972203949054</v>
+        <v>-17.34011642090881</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-15.35918995448969</v>
+        <v>-15.55057477166291</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-14.16327211868151</v>
+        <v>-14.35047309789448</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-14.72489910221558</v>
+        <v>-14.91414653500259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 9.111</t>
+          <t>X ≈ 9.109</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5166116791318416</v>
+        <v>-0.1806909270665429</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.864598494132984</v>
+        <v>-2.442360210783825</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.669814522196447</v>
+        <v>-3.250941126061505</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.064930785031322</v>
+        <v>-2.68748338522154</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.531718079819058</v>
+        <v>-1.13671300578666</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.6603608524764866</v>
+        <v>-0.3027731931598012</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.756874852720195</v>
+        <v>-2.352887186610516</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.040400316069992</v>
+        <v>-2.632852180641223</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.715002925508308</v>
+        <v>-1.327228083387084</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7631169291362028</v>
+        <v>1.075103697784691</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.037476196251539</v>
+        <v>1.349163339946614</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7484406571140312</v>
+        <v>1.066906837943392</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.505418322232032</v>
+        <v>3.746676812771121</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6566490461436771</v>
+        <v>0.9762815143142944</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.929304506452276</v>
+        <v>2.216973913659338</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.226632236571369</v>
+        <v>0.9072644908438647</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.9028986239131314</v>
+        <v>-0.506571504971518</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.6879441349551314</v>
+        <v>0.0180259249605399</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.630128151875276</v>
+        <v>1.506869100698282</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.5818027697048009</v>
+        <v>-0.8643193540533929</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.8863757586079899</v>
+        <v>-2.062632553250722</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.217729076459229</v>
+        <v>-2.387271835796362</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-3.179346348795548</v>
+        <v>-4.279128350200132</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.8549242864335653</v>
+        <v>-2.033159597411974</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 9.697</t>
+          <t>X ≈ 9.695</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>144</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.07506399666039698</v>
+        <v>0.1083382889792261</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.181563294658694</v>
+        <v>3.215236303272036</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.729643866740581</v>
+        <v>1.764998290409068</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3669288534254989</v>
+        <v>-0.3307351360065951</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7719102709030778</v>
+        <v>-0.7062372410074005</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.566417212148508</v>
+        <v>-0.5009426091622373</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.348447567076427</v>
+        <v>-1.28205551592648</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.324501397997395</v>
+        <v>-2.257766146081963</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.562852073346491</v>
+        <v>2.629558442153993</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.471242143189691</v>
+        <v>2.538868246730132</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>4.134490299193956</v>
+        <v>4.201816777780984</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.765953580469755</v>
+        <v>1.833624559083688</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.391747471138672</v>
+        <v>3.46074760138363</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.775392289299461</v>
+        <v>1.844670354132184</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.1305751795709327</v>
+        <v>-0.2206902780850086</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.151269628816124</v>
+        <v>0.3828608667318747</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.132372013098589</v>
+        <v>0.9311692103669529</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>4.110721930336638</v>
+        <v>2.897442876047243</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>2.152892599144607</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.902777777777786</v>
+        <v>5.542117347716996</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>6.05402181322426</v>
+        <v>6.123958434652913</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>5.283622313137251</v>
+        <v>5.353668028799412</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.475064146285973</v>
+        <v>3.544809407948058</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.010233918128613</v>
+        <v>2.08008826583589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 10.29</t>
+          <t>X ≈ 10.28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3407880724174603</v>
+        <v>0.4132069406220893</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.657369746271506</v>
+        <v>3.456808520650611</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.551002615518762</v>
+        <v>2.694465147295332</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.503875968992268</v>
+        <v>2.657186803528269</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1386061839682</v>
+        <v>0.9700449796296482</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3408958696916713</v>
+        <v>0.4813354900513502</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.219571331587666</v>
+        <v>1.06073815751239</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.725649980597602</v>
+        <v>-0.5688246385920763</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.982532751091739</v>
+        <v>1.499689570349695</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.208697340322274</v>
+        <v>0.7267738943131619</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.14972327410424</v>
+        <v>1.676509212150719</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5.203962703962674</v>
+        <v>4.776138187081102</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.412804818808901</v>
+        <v>2.97730044454935</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.5247813411079179</v>
+        <v>0.05351886540011463</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4.532516768737231</v>
+        <v>4.125105297549233</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>3.794243485025284</v>
+        <v>3.368140868140891</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>6.326816457543032</v>
+        <v>6.612602109541768</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>8.221833041447752</v>
+        <v>7.859112757071927</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>9.104622871046239</v>
+        <v>9.426355489347621</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>9.958333333333343</v>
+        <v>10.28887697499133</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>10.74846625766872</v>
+        <v>11.09768215837664</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>9.339177868692722</v>
+        <v>9.670484845616151</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>10.94728636850824</v>
+        <v>11.29631090944962</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>8.87134502923977</v>
+        <v>9.193451629199309</v>
       </c>
     </row>
     <row r="20">
@@ -1770,79 +1770,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6468662485702197</v>
+        <v>-0.6287989206608486</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.015394437629574</v>
+        <v>2.650882112314612</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.575693973543437</v>
+        <v>2.417682340392076</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.331036462819334</v>
+        <v>4.114366875166134</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>11.37317408520278</v>
+        <v>9.802672788161075</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>12.79490659944416</v>
+        <v>11.19445825136692</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>8.012871013259662</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.570646315698696</v>
+        <v>5.325021014289725</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4.37759447948676</v>
+        <v>5.366508196204428</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.603759068717295</v>
+        <v>4.593592520167903</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.878118335832667</v>
+        <v>4.867652162329861</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.129888629888626</v>
+        <v>2.179264204664996</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.474533213870622</v>
+        <v>3.465740692025747</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.253176402836267</v>
+        <v>3.244661815579121</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.594245163799002</v>
+        <v>2.586518517998627</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.514398490283348</v>
+        <v>-0.4335523913837491</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-6.586763789370544</v>
+        <v>-6.591565913903352</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-5.457179304231261</v>
+        <v>-4.286768063507637</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-5.241056141299445</v>
+        <v>-5.275695959691781</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-9.992283950617285</v>
+        <v>-9.908127258157492</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-11.77005226084981</v>
+        <v>-11.65549270323195</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-14.31514311896155</v>
+        <v>-14.14097721885792</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-10.33666424877572</v>
+        <v>-10.2520446750506</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-5.474333983105915</v>
+        <v>-5.508599819840143</v>
       </c>
     </row>
     <row r="21">
@@ -1855,76 +1855,76 @@
         <v>57</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.796928423294709</v>
+        <v>-2.76365413097588</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-10.14964779758811</v>
+        <v>-10.11597478897477</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-16.85250615641114</v>
+        <v>-16.81715173274265</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-17.56629946960425</v>
+        <v>-17.53010575218534</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.159639430066889</v>
+        <v>-9.093966400171212</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.218088852147865</v>
+        <v>-7.152614249161594</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-9.74534094911413</v>
+        <v>-9.678948897964183</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-6.51512366480808</v>
+        <v>-6.448388412892648</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.473607599785488</v>
+        <v>-6.406901230977986</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.493057045642587</v>
+        <v>-5.425430942102146</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.973083743439581</v>
+        <v>-6.905757264852554</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-14.26972150656361</v>
+        <v>-14.20205052794968</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-11.88544079522615</v>
+        <v>-11.81644066498119</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-10.35241164134827</v>
+        <v>-10.28313357651555</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.993799020736489</v>
+        <v>-3.923733014447023</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.864418923621827</v>
+        <v>1.933811802232903</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>8.747869089121977</v>
+        <v>8.817438524904503</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>5.134113743202136</v>
+        <v>5.203825891258759</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.59585094122167</v>
+        <v>3.665331307270804</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>5.537280701754383</v>
+        <v>5.606563082151112</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>4.994080292756372</v>
+        <v>5.064016914185025</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>8.426897166938325</v>
+        <v>8.496942882600486</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>5.192900403595992</v>
+        <v>5.262645665258077</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>5.116959064327524</v>
+        <v>5.186813412034802</v>
       </c>
     </row>
     <row r="22">
@@ -1937,76 +1937,76 @@
         <v>40</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.325878594249204</v>
+        <v>6.359152886568033</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>10.99070307960488</v>
+        <v>11.02437608821822</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.051002615518733</v>
+        <v>2.08635703918722</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.337209302325654</v>
+        <v>1.373403019744558</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-13.84089586969171</v>
+        <v>-13.77542126670544</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-19.61376200174571</v>
+        <v>-19.54736995059576</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-24.89231664726434</v>
+        <v>-24.82558139534891</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-32.35080058224167</v>
+        <v>-32.28409421343417</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-33.12463599301106</v>
+        <v>-33.05700988947062</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-32.85027672589576</v>
+        <v>-32.78295024730873</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-28.12937062937063</v>
+        <v>-28.06169965075669</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-34.25386184785784</v>
+        <v>-34.18486171761288</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-31.97521865889212</v>
+        <v>-31.9059405940594</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-32.63414989792942</v>
+        <v>-32.56408389163995</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-29.53908984830812</v>
+        <v>-29.46969696969704</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-29.67318354245697</v>
+        <v>-29.60361410667444</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-29.77816695855218</v>
+        <v>-29.70845481049555</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-27.06204379562036</v>
+        <v>-26.99256342957123</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-26.87499999999993</v>
+        <v>-26.8057176196032</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-22.41820040899788</v>
+        <v>-22.34826378756923</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-22.49415546464049</v>
+        <v>-22.42410974897833</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-19.71938029815843</v>
+        <v>-19.64963503649635</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-17.29532163742697</v>
+        <v>-17.2254672897197</v>
       </c>
     </row>
     <row r="23">
@@ -2019,76 +2019,76 @@
         <v>23</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.847617724684049</v>
+        <v>2.880892017002878</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.420567832910052</v>
+        <v>5.455922256578539</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3589484327603643</v>
+        <v>0.395142150179268</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.341504734692847</v>
+        <v>4.407177764588525</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.528669347699683</v>
+        <v>4.594143950685954</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8.103629302602052</v>
+        <v>8.170021353751999</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.8705775168294849</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.8290614518067869</v>
+        <v>-0.7623550829992851</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.950722949532803</v>
+        <v>-5.883096845992362</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.676363682417396</v>
+        <v>-5.609037203830368</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.955457585892297</v>
+        <v>-5.887786607278365</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.079948804379512</v>
+        <v>-7.010948674134553</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-11.64913170237026</v>
+        <v>-11.57985363753754</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-12.30806294140768</v>
+        <v>-12.23799693511822</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-20.40865506569935</v>
+        <v>-20.33926218708827</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-24.8905748468048</v>
+        <v>-24.82100541102227</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-24.9955582629002</v>
+        <v>-24.92584611484357</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-20.43160901301192</v>
+        <v>-20.36212864696279</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-15.89673913043485</v>
+        <v>-15.82745675003812</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-12.09211345247616</v>
+        <v>-12.0221768310475</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-7.820242421162305</v>
+        <v>-7.750196705500144</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.197641167723901</v>
+        <v>-3.127895906061816</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-7.621408593948765</v>
+        <v>-7.551554246241487</v>
       </c>
     </row>
     <row r="24">
@@ -2101,158 +2101,158 @@
         <v>19</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-16.83201614259298</v>
+        <v>-16.79874185027415</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.640875867763469</v>
+        <v>-6.607202859150128</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.34373422658653</v>
+        <v>-13.30837980291804</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-19.3206854345166</v>
+        <v>-19.28449171709769</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-19.68595521954057</v>
+        <v>-19.6202821896449</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-19.49879060653379</v>
+        <v>-19.43331600354752</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-20.27165673858774</v>
+        <v>-20.20526468743779</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-10.02389559463276</v>
+        <v>-9.95716034271733</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15.2455374243469</v>
+        <v>-15.1788310555394</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-26.54568862458993</v>
+        <v>-26.47806252104949</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-31.53448725221152</v>
+        <v>-31.46716077362449</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-31.81358115568649</v>
+        <v>-31.74591017707256</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-38.20123026891041</v>
+        <v>-38.13223013866545</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-22.63311339573438</v>
+        <v>-22.56383533090166</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-23.29204463477154</v>
+        <v>-23.22197862848207</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-22.69698458515015</v>
+        <v>-22.62759170653908</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-22.83107827929908</v>
+        <v>-22.76150884351655</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-28.1992195901312</v>
+        <v>-28.12950744207457</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-38.50941221667307</v>
+        <v>-38.43993185062394</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-38.32236842105271</v>
+        <v>-38.25308604065598</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-33.60241093531381</v>
+        <v>-33.53247431388516</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-28.41520809621951</v>
+        <v>-28.34516238055735</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-28.14043292973716</v>
+        <v>-28.07068766807507</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-22.95321637426886</v>
+        <v>-22.88336202656158</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 13.8</t>
+          <t>X ≈ 13.79</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>19</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-11.56885824785606</v>
+        <v>-11.53558395553723</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-11.90403376250054</v>
+        <v>-11.8703607538872</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-18.60689212132337</v>
+        <v>-18.57153769765488</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.794369645042764</v>
+        <v>-8.75817592762386</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.366676359406803</v>
+        <v>1.43234938930248</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.816998867150424</v>
+        <v>6.882473470136695</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.780974840359562</v>
+        <v>0.8473668915095089</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.765578089577915</v>
+        <v>5.832313341493347</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.543936259863635</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2298991509058723</v>
+        <v>-0.1622730473654315</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.218697778527307</v>
+        <v>-5.15137129994028</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.497791682002209</v>
+        <v>-5.430120703388276</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.359125005752503</v>
+        <v>-1.290124875507544</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.580481816786858</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.023744838912677</v>
+        <v>3.093810845202142</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>8.8819627832709</v>
+        <v>8.951355661881976</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>19.27418487859575</v>
+        <v>19.34375431437827</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>19.16920146250047</v>
+        <v>19.23891361055709</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>19.38532462543228</v>
+        <v>19.45480499148142</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>14.30921052631578</v>
+        <v>14.37849290671251</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.239694327844148</v>
+        <v>3.309630949272801</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.099418622535296</v>
+        <v>-2.029372906873135</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.438514438683605</v>
+        <v>3.50825970034569</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.900584795321635</v>
+        <v>-1.830730447614357</v>
       </c>
     </row>
     <row r="26">
@@ -2265,76 +2265,76 @@
         <v>23</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.847617724683985</v>
+        <v>2.880892017002814</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.275084341003058</v>
+        <v>-3.239729917334571</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3589484327604282</v>
+        <v>0.395142150179332</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.16698282621342</v>
+        <v>-4.10150822322715</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.477248570127095</v>
+        <v>3.543983822042527</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.518764635149729</v>
+        <v>3.585471003957231</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.74492922438025</v>
+        <v>2.812555327920691</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>11.71494066540862</v>
+        <v>11.78226714399565</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.43584676193372</v>
+        <v>11.50351774054765</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.65918163040309</v>
+        <v>14.72818176064805</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18.78565090632527</v>
+        <v>18.85492897115799</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>22.47454575424448</v>
+        <v>22.54461176053395</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>23.06960580386586</v>
+        <v>23.13899868247694</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>27.28333819667341</v>
+        <v>27.35290763245594</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>27.17835478057813</v>
+        <v>27.24806692863476</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>27.39447794351</v>
+        <v>27.46395830955914</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>23.23369565217391</v>
+        <v>23.30297803257064</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>22.69049524317595</v>
+        <v>22.76043186460461</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>26.96236627448987</v>
+        <v>27.03241199015203</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>22.88931535401547</v>
+        <v>22.95906061567756</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>18.46554792779049</v>
+        <v>18.53540227549777</v>
       </c>
     </row>
     <row r="27">
@@ -2347,158 +2347,158 @@
         <v>9</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-31.45189918352857</v>
+        <v>-31.41862489120975</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.6573697462717</v>
+        <v>12.69104275488505</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.21766928218557</v>
+        <v>11.25302370585405</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-11.71834625323029</v>
+        <v>-11.68215253581138</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.13860618396804</v>
+        <v>10.20427921386371</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>21.43688190808611</v>
+        <v>21.50235651107238</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.552904664920796</v>
+        <v>9.619296716070743</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>20.38546113051336</v>
+        <v>20.4521963824288</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>20.426977195536</v>
+        <v>20.4936835643435</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>30.76425289587782</v>
+        <v>30.83187899941827</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>31.038612162993</v>
+        <v>31.10593864158003</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>30.7595182595181</v>
+        <v>30.82718923813204</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>29.63502704103112</v>
+        <v>29.70402717127607</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>18.30255911888566</v>
+        <v>18.37183718371838</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>18.10459423532082</v>
+        <v>18.17416367110334</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>17.99961081922554</v>
+        <v>18.06932296728216</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.104622871046068</v>
+        <v>7.174103237095203</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>18.40277777777763</v>
+        <v>18.47206015817436</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>40.08179959100205</v>
+        <v>40.1517362124307</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>40.00584453535944</v>
+        <v>40.0758902510216</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>40.28061970184172</v>
+        <v>40.35036496350381</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 15.56</t>
+          <t>X ≈ 15.55</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>10</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.3258785942492</v>
+        <v>16.35915288656803</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>15.99070307960488</v>
+        <v>16.02437608821822</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>24.55100261551881</v>
+        <v>24.5863570391873</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>13.83720930232572</v>
+        <v>13.87340301974463</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>23.47193951730168</v>
+        <v>23.53761254719736</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>23.65910413030832</v>
+        <v>23.72457873329459</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32.88623799825444</v>
+        <v>32.95263004940438</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>32.60768335273573</v>
+        <v>32.67441860465117</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>32.64919941775837</v>
+        <v>32.71590578656587</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>31.87536400698894</v>
+        <v>31.94299011052938</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>32.14972327410442</v>
+        <v>32.21704975269144</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>21.87062937062952</v>
+        <v>21.93830034924345</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>20.74613815214209</v>
+        <v>20.81513828238705</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>30.52478134110773</v>
+        <v>30.59405940594046</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>29.86585010207057</v>
+        <v>29.93591610836004</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>30.46091015169196</v>
+        <v>30.53030303030303</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>30.32681645754303</v>
+        <v>30.39638589332556</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>30.22183304144775</v>
+        <v>30.29154518950438</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>30.43795620437971</v>
+        <v>30.50743657042884</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>30.62500000000014</v>
+        <v>30.69428238039687</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>30.08179959100219</v>
+        <v>30.15173621243084</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>30.00584453535944</v>
+        <v>30.0758902510216</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>30.28061970184142</v>
+        <v>30.35036496350351</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>30.20467836257324</v>
+        <v>30.27453271028052</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>4</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.674121405750974</v>
+        <v>-3.640847113432145</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20.99070307960488</v>
+        <v>21.02437608821822</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-56.16279069767442</v>
+        <v>-56.12659698025551</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-56.52806048269846</v>
+        <v>-56.46238745280279</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-56.34089586969186</v>
+        <v>-56.27542126670559</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-32.11376200174571</v>
+        <v>-32.04736995059576</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.392316647264266</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-32.35080058224163</v>
+        <v>-32.28409421343413</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-33.12463599301106</v>
+        <v>-33.05700988947062</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-8.129370629370626</v>
+        <v>-8.061699650756694</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-9.253861847857415</v>
+        <v>-9.184861717612456</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-9.47521865889177</v>
+        <v>-9.405940594059047</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>14.86585010207057</v>
+        <v>14.93591610836004</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-9.539089848308045</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-34.67318354245697</v>
+        <v>-34.60361410667444</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-59.77816695855225</v>
+        <v>-59.70845481049562</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-59.56204379562043</v>
+        <v>-59.4925634295713</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-59.375</v>
+        <v>-59.30571761960327</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-59.91820040899831</v>
+        <v>-59.84826378756966</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-34.99415546464056</v>
+        <v>-34.9241097489784</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-9.719380298158434</v>
+        <v>-9.649635036496349</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>15.20467836257274</v>
+        <v>15.27453271028002</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>6</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.99254526091599</v>
+        <v>13.02581955323482</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>45.99070307960488</v>
+        <v>46.02437608821822</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>44.55100261551861</v>
+        <v>44.5863570391871</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>43.8372093023257</v>
+        <v>43.8734030197446</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>43.47193951730165</v>
+        <v>43.53761254719733</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>26.99243746364176</v>
+        <v>27.05791206662803</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.274350019402391</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.350800582241632</v>
+        <v>-7.28409421343413</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>25.48305660743762</v>
+        <v>25.55038308602465</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>41.87062937062937</v>
+        <v>41.93830034924331</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>40.74613815214223</v>
+        <v>40.81513828238719</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>40.52478134110812</v>
+        <v>40.59405940594084</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>39.86585010207057</v>
+        <v>39.93591610836004</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>40.46091015169196</v>
+        <v>40.53030303030303</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>40.32681645754303</v>
+        <v>40.39638589332556</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>40.22183304144775</v>
+        <v>40.29154518950438</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>23.77128953771265</v>
+        <v>23.84076990376179</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-9.848263787569302</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-9.994155464640329</v>
+        <v>-9.924109748978168</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>23.61395303517465</v>
+        <v>23.68369829683674</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>23.53801169590619</v>
+        <v>23.60786604361346</v>
       </c>
     </row>
     <row r="31">
@@ -2675,322 +2675,322 @@
         <v>1</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46.3258785942492</v>
+        <v>46.35915288656803</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-54.00929692039512</v>
+        <v>-53.97562391178178</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>44.55100261551874</v>
+        <v>44.58635703918723</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>43.83720930232558</v>
+        <v>43.87340301974449</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>43.47193951730154</v>
+        <v>43.53761254719721</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>43.65910413030903</v>
+        <v>43.7245787332953</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>42.88623799825429</v>
+        <v>42.95263004940424</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>42.60768335273573</v>
+        <v>42.67441860465117</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>42.64919941775837</v>
+        <v>42.71590578656587</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>41.87536400698965</v>
+        <v>41.94299011053009</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>42.14972327410428</v>
+        <v>42.2170497526913</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>41.87062937063008</v>
+        <v>41.93830034924402</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>40.74613815214223</v>
+        <v>40.81513828238719</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>40.52478134110503</v>
+        <v>40.59405940593776</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>39.86585010207128</v>
+        <v>39.93591610836075</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>40.46091015169267</v>
+        <v>40.53030303030374</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>40.32681645754303</v>
+        <v>40.39638589332556</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>40.22183304144775</v>
+        <v>40.29154518950438</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>40.43795620437957</v>
+        <v>40.5074365704287</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>40.625</v>
+        <v>40.69428238039673</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>40.08179959100205</v>
+        <v>40.1517362124307</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>40.00584453535659</v>
+        <v>40.07589025101876</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>40.28061970184299</v>
+        <v>40.35036496350507</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>40.20467836257452</v>
+        <v>40.2745327102818</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 17.91</t>
+          <t>X ≈ 17.9</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>19.55100261551874</v>
+        <v>19.58635703918723</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>43.83720930232541</v>
+        <v>43.87340301974432</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>43.47193951730137</v>
+        <v>43.53761254719704</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>43.65910413030815</v>
+        <v>43.72457873329442</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>42.88623799825429</v>
+        <v>42.95263004940424</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>42.60768335273573</v>
+        <v>42.67441860465117</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>42.64919941775837</v>
+        <v>42.71590578656587</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>41.87536400698877</v>
+        <v>41.94299011052921</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>42.14972327410428</v>
+        <v>42.2170497526913</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>41.8706293706292</v>
+        <v>41.93830034924314</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>40.74613815214223</v>
+        <v>40.81513828238719</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>40.52478134110823</v>
+        <v>40.59405940594095</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>39.8658501020704</v>
+        <v>39.93591610835987</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>40.46091015169178</v>
+        <v>40.53030303030286</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>40.32681645754303</v>
+        <v>40.39638589332556</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>40.22183304144775</v>
+        <v>40.29154518950438</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>40.43795620437992</v>
+        <v>40.50743657042906</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>40.625</v>
+        <v>40.69428238039673</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>40.08179959100205</v>
+        <v>40.1517362124307</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>40.00584453535979</v>
+        <v>40.07589025102195</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>40.28061970184157</v>
+        <v>40.35036496350365</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 18.49</t>
+          <t>X ≈ 18.48</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>6</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-37.00745473908401</v>
+        <v>-36.97418044676518</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-37.34263025372846</v>
+        <v>-37.30895724511512</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-22.11566405114793</v>
+        <v>-22.08030962747944</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-22.82945736434109</v>
+        <v>-22.79326364692218</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-23.19472714936514</v>
+        <v>-23.12905411946946</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-23.00756253635835</v>
+        <v>-22.94208793337208</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-23.78042866841238</v>
+        <v>-23.71403661726243</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-24.05898331393094</v>
+        <v>-23.99224806201551</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-24.01746724890818</v>
+        <v>-23.95076088010067</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-24.79130265967773</v>
+        <v>-24.72367655613729</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-24.5169433925624</v>
+        <v>-24.44961691397537</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-24.7960372960373</v>
+        <v>-24.72836631742337</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-25.92052851452444</v>
+        <v>-25.85152838427948</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-26.14188532555867</v>
+        <v>-26.07260726072595</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-26.80081656459597</v>
+        <v>-26.7307505583065</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-42.87242318164138</v>
+        <v>-42.8030303030303</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-26.33985020912364</v>
+        <v>-26.27028077334111</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-26.44483362521903</v>
+        <v>-26.37512147716241</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-26.2287104622871</v>
+        <v>-26.15923009623797</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-26.04166666666667</v>
+        <v>-25.97238428626994</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-26.58486707566463</v>
+        <v>-26.51493045423597</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-26.66082213130711</v>
+        <v>-26.59077641564495</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-26.38604696482511</v>
+        <v>-26.31630170316302</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-26.46198830409357</v>
+        <v>-26.3921339563863</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 19.08</t>
+          <t>X ≈ 19.07</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>14</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>17.75445002282058</v>
+        <v>17.78772431513941</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.27641736531911</v>
+        <v>10.31009037393245</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.836716901232975</v>
+        <v>8.872071324901462</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22.40863787375415</v>
+        <v>22.44483159117306</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>29.1862252315872</v>
+        <v>29.25189826148288</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>29.37338984459403</v>
+        <v>29.4388644475803</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>28.60052371253996</v>
+        <v>28.66691576368991</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>28.32196906702144</v>
+        <v>28.38870431893687</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>28.36348513204403</v>
+        <v>28.43019150085154</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>20.44679257841751</v>
+        <v>20.51441868195795</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.57829470267565</v>
+        <v>13.64562118126268</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.29920079920085</v>
+        <v>13.36687177781478</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.3175667235708</v>
+        <v>19.38656685381576</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.09620991253644</v>
+        <v>19.16548797736917</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>18.43727867349914</v>
+        <v>18.50734467978861</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>26.17519586597772</v>
+        <v>26.2445887445888</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>18.8982450289716</v>
+        <v>18.96781446475413</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>25.93611875573352</v>
+        <v>26.00583090379014</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>26.15224191866533</v>
+        <v>26.22172228471447</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>26.33928571428567</v>
+        <v>26.40856809468239</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>25.79608530528771</v>
+        <v>25.86602192671636</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>25.7201302496451</v>
+        <v>25.79017596530726</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>25.99490541612727</v>
+        <v>26.06465067778936</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>25.91896407685881</v>
+        <v>25.98881842456608</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3327</v>
+        <v>3331</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.002479614706018651</v>
+        <v>-0.003399289937632943</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.006827295788816912</v>
+        <v>0.005885184549867972</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04682101456294419</v>
+        <v>0.04578424682446069</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.006913515053390995</v>
+        <v>0.005900781606619887</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.01281840260282507</v>
+        <v>-0.01462625877293533</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.01802591453472502</v>
+        <v>-0.0198225805304304</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06327149107726626</v>
+        <v>0.06135167425490096</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1607793742732753</v>
+        <v>0.1587329159747384</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1895943908283897</v>
+        <v>0.1875136765837979</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2111916035169301</v>
+        <v>0.2090588698716829</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2634957291940907</v>
+        <v>0.2613081258970382</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3312463218123582</v>
+        <v>0.3289674147533219</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4525491767078407</v>
+        <v>0.4500874146433205</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.5187879338558474</v>
+        <v>0.5162383942674467</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.5073369126221365</v>
+        <v>0.5047783838091391</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.4908951591882129</v>
+        <v>0.4883743091290285</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.5247768654614475</v>
+        <v>0.5222097399402941</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.4978606442080249</v>
+        <v>0.4953210360731504</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.491977813023027</v>
+        <v>0.4894509589179137</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.4568823176223304</v>
+        <v>0.4544023204267162</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.4721899813924395</v>
+        <v>0.4696726251481564</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.4744537273089691</v>
+        <v>0.4719298549819939</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.5270139326107923</v>
+        <v>0.5244345913547974</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.5292951344396428</v>
+        <v>0.5267092338468657</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3189</v>
+        <v>3193</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.03073538129777376</v>
+        <v>0.02830711542375042</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05485754861764747</v>
+        <v>0.05236986737840965</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.09617395508259818</v>
+        <v>0.093513230848707</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2410734344539733</v>
+        <v>0.2381711492184948</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3921390185484199</v>
+        <v>0.386927615690368</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.3475980498593074</v>
+        <v>0.3424547843690249</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3722018160958385</v>
+        <v>0.366960267472777</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.4547972372911104</v>
+        <v>0.4494263952401383</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.6080009158857109</v>
+        <v>0.6024394524012848</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.6327789304981479</v>
+        <v>0.6271185795034953</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7693360161405067</v>
+        <v>0.7635251113937329</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.727236680844932</v>
+        <v>0.7214516752963434</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.7773881521422297</v>
+        <v>0.771442901613149</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.7623555830584863</v>
+        <v>0.7564072048790962</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.653842597380148</v>
+        <v>0.6479710740065059</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.704888881751387</v>
+        <v>0.6990003124023758</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.8712469957157438</v>
+        <v>0.8651358933255651</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.9104089412912657</v>
+        <v>0.9042366555875248</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.9889893916056138</v>
+        <v>0.9827336310916124</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.9757673034763457</v>
+        <v>0.9695404348227541</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.9840552300997913</v>
+        <v>0.9777687531065453</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.8958476691732855</v>
+        <v>0.8896617690184669</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.8762309871080234</v>
+        <v>0.8700894469100433</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.8192910938368172</v>
+        <v>0.813211069190487</v>
       </c>
     </row>
     <row r="8">
@@ -3348,1063 +3348,1063 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2987</v>
+        <v>2991</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.4122573317907339</v>
+        <v>0.4069299270458089</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.4606266422502685</v>
+        <v>0.4551759554601702</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.23584304105065</v>
+        <v>0.2304473446321111</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4384730203169411</v>
+        <v>0.4326856500998559</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6575682598165074</v>
+        <v>0.6472470986922261</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5642622001918554</v>
+        <v>0.5540901988977822</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6425628983874532</v>
+        <v>0.6321513259999918</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.5830413280937137</v>
+        <v>0.5726560506105969</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.8437363931081308</v>
+        <v>0.8330049216290831</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.9556705714674436</v>
+        <v>0.9446540040401956</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.083056607437612</v>
+        <v>1.071909939109418</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.090369283933811</v>
+        <v>1.079159490102441</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.286498392302335</v>
+        <v>1.274831820028759</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.452375602035474</v>
+        <v>1.44044394442777</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.514715255608621</v>
+        <v>1.50258277502671</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.529357564045874</v>
+        <v>1.517298695524772</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.649461748124189</v>
+        <v>1.637213111470992</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.464733141681627</v>
+        <v>1.452706350665537</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.433945509192405</v>
+        <v>1.421989307411344</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.407347041123373</v>
+        <v>1.395450994753986</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.319257784981978</v>
+        <v>1.307380835009184</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.29724634198373</v>
+        <v>1.285379058238433</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.425198015094587</v>
+        <v>1.413199188102581</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.302770093406714</v>
+        <v>1.29091519105603</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 4.129</t>
+          <t>X &gt; 4.128</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2723</v>
+        <v>2727</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1052940204631057</v>
+        <v>-0.1135743861592431</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.09308562713464852</v>
+        <v>-0.1014878623092486</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2376271220905934</v>
+        <v>-0.2462484921082577</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2386200815606756</v>
+        <v>-0.2474560992944603</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2553093203649937</v>
+        <v>0.2382680461047144</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5726393364374758</v>
+        <v>0.5551798261907663</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.7694496770864063</v>
+        <v>0.7514638686462192</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.023163454962827</v>
+        <v>1.004713901771105</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.049491601834333</v>
+        <v>1.0310042548372</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.210402370160296</v>
+        <v>1.191439581525373</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.433349005098421</v>
+        <v>1.414130044662109</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.28562022986155</v>
+        <v>1.266522328067694</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.499612914395343</v>
+        <v>1.479857055214062</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.739563631631114</v>
+        <v>1.719379099035223</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.87170661744392</v>
+        <v>1.85112078672261</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.90360513521447</v>
+        <v>1.883136668328625</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.975168105894682</v>
+        <v>1.954542440509172</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>2.002705155775345</v>
+        <v>1.981995244389111</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.02153391698954</v>
+        <v>2.00084799063368</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.304501283461683</v>
+        <v>2.283443859708335</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.187448894010117</v>
+        <v>2.166388227082713</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.170982150038334</v>
+        <v>2.149910038489537</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.285024988185178</v>
+        <v>2.263854699574033</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.084957466502587</v>
+        <v>2.064044994842163</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 4.715</t>
+          <t>X &gt; 4.714</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1456530817732471</v>
+        <v>-0.158060884448787</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3390201454252093</v>
+        <v>-0.3512746927189099</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6335880746899321</v>
+        <v>-0.6460147556845683</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7232082006852565</v>
+        <v>-0.7358154171292597</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1425183140237678</v>
+        <v>-0.1672791929792083</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2139372517728333</v>
+        <v>-0.2385179373833139</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.0003859082221424615</v>
+        <v>-0.02489804048340005</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.0664690383006743</v>
+        <v>0.04093807474350086</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1310980500994816</v>
+        <v>0.105464019497596</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06449881584205741</v>
+        <v>0.03861084174673834</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2012530647645008</v>
+        <v>0.1752491096044864</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.02608647896606442</v>
+        <v>0.0002223436140269541</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4963396025854152</v>
+        <v>0.4692010337950734</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7827418409063469</v>
+        <v>0.7550252007092126</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.6723017149737984</v>
+        <v>0.6444507299381428</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.7271465373313291</v>
+        <v>0.699453251809274</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.8998592339756399</v>
+        <v>0.8718089392562547</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.9404442647016893</v>
+        <v>0.9122626421444338</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.9791516809546863</v>
+        <v>0.9509849575254847</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.150252525252526</v>
+        <v>1.121874151272081</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.7931981358686571</v>
+        <v>0.7651341139641943</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.7013560598236523</v>
+        <v>0.673387223165328</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.919778277893343</v>
+        <v>0.89156044007877</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.9088467154666588</v>
+        <v>0.8805933163409847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 5.301</t>
+          <t>X &gt; 5.3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2205</v>
+        <v>2209</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7118233806161527</v>
+        <v>-0.7286607335036521</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.202830822505582</v>
+        <v>-1.219012526752643</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.540641589333013</v>
+        <v>-1.5571407186603</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.645936765090141</v>
+        <v>-1.662711829963897</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.357197173345952</v>
+        <v>-1.39057416734498</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.28016712475241</v>
+        <v>-1.313589205636703</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.173167942339759</v>
+        <v>-1.207298072788028</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.201411649515506</v>
+        <v>-1.235693754899394</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.269719501160544</v>
+        <v>-1.303878386096002</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.342301608153015</v>
+        <v>-1.376847946150782</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.448112614083279</v>
+        <v>-1.482320184302402</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.701765757922729</v>
+        <v>-1.735720362147966</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.040865457966078</v>
+        <v>-1.076753609504706</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.7844737378988924</v>
+        <v>-0.8209924192058651</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.694222165318763</v>
+        <v>-0.7313517004767505</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.5241779639881159</v>
+        <v>-0.5612621478656692</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2699285695817366</v>
+        <v>-0.3075852258080189</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.0766744212388204</v>
+        <v>-0.1147753522563448</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.01453248340323654</v>
+        <v>-0.05263569696063541</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1994680851063819</v>
+        <v>0.1610695471387018</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.0002778518716155531</v>
+        <v>-0.03813720529082332</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.1327135883725816</v>
+        <v>0.09398161239654712</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.389413899484353</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.3407327843418031</v>
+        <v>0.3016943218693271</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 5.887</t>
+          <t>X &gt; 5.886</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6633133769293877</v>
+        <v>-0.6634343824258124</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.795084767974942</v>
+        <v>-1.792778508597394</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.125968018175229</v>
+        <v>-2.124845427410918</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.039079357468232</v>
+        <v>-2.039193381283795</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.912279152115687</v>
+        <v>-1.935638481609367</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.776687514869607</v>
+        <v>-1.772075924451158</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.982250913555916</v>
+        <v>-1.949532669442306</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.025959578120819</v>
+        <v>-1.99327845871823</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.852607500155933</v>
+        <v>-1.820176687660933</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.748797066836566</v>
+        <v>-1.716803703903608</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.732568930335582</v>
+        <v>-1.752022412257148</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.908410381564742</v>
+        <v>-1.89872904735288</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.174357459628553</v>
+        <v>-1.135326113897641</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.034330687802807</v>
+        <v>-0.9952078799211108</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.8882821293343852</v>
+        <v>-0.879357369452137</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.7277203392641169</v>
+        <v>-0.7493667323388706</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.7279922291167367</v>
+        <v>-0.780084694909732</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3886170361518424</v>
+        <v>-0.4721287011045021</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2970334436535609</v>
+        <v>-0.3805345188846658</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.07606162610046852</v>
+        <v>-0.008196958446248459</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.02182735200312891</v>
+        <v>-0.1066617203858371</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1406293979825648</v>
+        <v>0.05520772775376059</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.4465948055760052</v>
+        <v>0.3607115749883931</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.5575584871190244</v>
+        <v>0.4712200808807836</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 6.473</t>
+          <t>X &gt; 6.472</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7535606580872454</v>
+        <v>-0.7853692579541161</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.876041514199912</v>
+        <v>-1.905653066300729</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.232623115475405</v>
+        <v>-2.263117873298185</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.601387188902486</v>
+        <v>-1.602370477044772</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.615779780944074</v>
+        <v>-1.614256611681284</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.487094700101032</v>
+        <v>-1.453679595168289</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.675165510517637</v>
+        <v>-1.60877345936769</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.953720156036198</v>
+        <v>-1.886984904120766</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.970683623177301</v>
+        <v>-1.903977254369799</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.808846519326856</v>
+        <v>-1.741220415786415</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.59296678437525</v>
+        <v>-1.525640305788222</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.696622091358925</v>
+        <v>-1.628951112744993</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7158501519513365</v>
+        <v>-0.6468500217063777</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5278502378395018</v>
+        <v>-0.4585721730067789</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2160691489534159</v>
+        <v>-0.1810429559674418</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1798797067270854</v>
+        <v>0.1794258373205722</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.4908469203432659</v>
+        <v>0.4548654254893023</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.8314461715767081</v>
+        <v>0.7593814468143165</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.7312113363443729</v>
+        <v>0.6595723223303906</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.9536384976525838</v>
+        <v>0.8816360103733132</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.9743421629339295</v>
+        <v>0.9015897566603357</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.462953818555683</v>
+        <v>1.388903146683965</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.773858972858619</v>
+        <v>1.699338570541777</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.675266597867221</v>
+        <v>1.600823790092591</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 7.059</t>
+          <t>X &gt; 7.058</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6387645011477261</v>
+        <v>-0.6801019371179251</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.606092648031975</v>
+        <v>-1.645397546934916</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.741582554821946</v>
+        <v>-1.782730235962674</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.520172127200141</v>
+        <v>-1.526596980255512</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.685041110620979</v>
+        <v>-1.692540888426542</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.564676764815253</v>
+        <v>-1.535768396211417</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.736340492059661</v>
+        <v>-1.669948440909714</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.148495671980371</v>
+        <v>-2.081760420064938</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.307380408560945</v>
+        <v>-2.240674039753443</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.212812345716472</v>
+        <v>-2.145186242176031</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.07205361300327</v>
+        <v>-2.004727134416243</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.484748050880313</v>
+        <v>-2.41707707226638</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.738831787737531</v>
+        <v>-1.669831657492573</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.759787797168677</v>
+        <v>-1.690509732335954</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.377465405950822</v>
+        <v>-1.346649021900475</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.8768824904485157</v>
+        <v>-0.8858626343596328</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.5031701555761074</v>
+        <v>-0.552177900929621</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1666465298851421</v>
+        <v>-0.2562170015443854</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.1786657795346471</v>
+        <v>-0.267964499090013</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1152749832327302</v>
+        <v>0.02538605932649318</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.1489136849617765</v>
+        <v>0.05802804643337822</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.7177317079584924</v>
+        <v>0.6251199898025703</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.033307873884581</v>
+        <v>0.9401772959433288</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.9982224109927316</v>
+        <v>0.9049820731241027</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 7.645</t>
+          <t>X &gt; 7.644</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.046609813787889</v>
+        <v>-0.9767544493393032</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.227225823022636</v>
+        <v>-1.234311170469041</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.048688265470446</v>
+        <v>-2.054569601739409</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.757844793501313</v>
+        <v>-1.763662617321145</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.582156309591824</v>
+        <v>-1.516483279696146</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.781390460108994</v>
+        <v>-1.715915857122724</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.245137581343847</v>
+        <v>-2.1787455301939</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.291852968748032</v>
+        <v>-2.2251177168326</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.250336903725398</v>
+        <v>-2.183630534917896</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.174095034742123</v>
+        <v>-2.106468931201682</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.131575025741164</v>
+        <v>-2.064248547154136</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.028906950854392</v>
+        <v>-2.961235972240459</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.144124599016962</v>
+        <v>-2.075124468772003</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.520040915460903</v>
+        <v>-2.45076285062818</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.129509526699728</v>
+        <v>-2.104269363046448</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.412154863787919</v>
+        <v>-1.432602688398674</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.346305153611105</v>
+        <v>-1.411960319966553</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.251035175606511</v>
+        <v>-1.362241518378156</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.9895069453489072</v>
+        <v>-1.101225455866739</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.7569875776397552</v>
+        <v>-0.869185111863338</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.7884412792388247</v>
+        <v>-0.9017107279256109</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1185722609080528</v>
+        <v>-0.2341872683582551</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.4362617251878689</v>
+        <v>0.3193331559008641</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.3292889544734052</v>
+        <v>0.212420909038137</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 8.231</t>
+          <t>X &gt; 8.23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.252468984098378</v>
+        <v>-1.219194691779549</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.017843928942128</v>
+        <v>-0.9841709203287863</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.69781029996085</v>
+        <v>-1.662455876292363</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.366969235186289</v>
+        <v>-1.330775517767385</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.257405212043196</v>
+        <v>-1.191732182147518</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.829974692103832</v>
+        <v>-1.764500089117561</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.317940539257577</v>
+        <v>-2.25154848810763</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.21662813824242</v>
+        <v>-2.149892886326988</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.985178549952934</v>
+        <v>-1.918472181145432</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.904313106021512</v>
+        <v>-1.836687002481071</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.345053554005887</v>
+        <v>-1.277727075418859</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.909047742381077</v>
+        <v>-1.841376763767144</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.41910401309994</v>
+        <v>-1.350103882854981</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.115294632301435</v>
+        <v>-2.046016567468712</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.864187920743113</v>
+        <v>-1.849459010348419</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.165160257442196</v>
+        <v>-2.204739704739708</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.958897828171253</v>
+        <v>-2.053756556816893</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.104191744062256</v>
+        <v>-2.253564022271505</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.928456009360886</v>
+        <v>-2.078114760369772</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.590854823304674</v>
+        <v>-1.741493071553791</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.792005380317264</v>
+        <v>-1.943501882807396</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.238174603396544</v>
+        <v>-1.392174572619965</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.7155488805339161</v>
+        <v>-0.8710090822978742</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.6390416757778112</v>
+        <v>-0.7951903078667115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 8.818</t>
+          <t>X &gt; 8.816</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3407880724174603</v>
+        <v>-0.2520242834676338</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1573697462715415</v>
+        <v>0.2455413676474691</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6870926225764933</v>
+        <v>-0.5979473603371517</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.400885935769651</v>
+        <v>-1.310901379779892</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1386061839682</v>
+        <v>0.25580517502123</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.269467298263109</v>
+        <v>-0.1517589599277613</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9232858112695155</v>
+        <v>-0.804801579608835</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.082792837740456</v>
+        <v>-0.9641069601526411</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.2079434393844934</v>
+        <v>-0.09027732877301275</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.08964972127465387</v>
+        <v>0.2069615730739756</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3640089883899904</v>
+        <v>0.4810212152358986</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3230103230103296</v>
+        <v>0.4400839402064491</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9842333902374634</v>
+        <v>1.100512836489443</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.6416218316243061</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.010069410771408</v>
+        <v>1.053633111927226</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.081435211357828</v>
+        <v>0.9345836486145629</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.139241786097394</v>
+        <v>1.038478640055637</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.824703854844877</v>
+        <v>1.528168257280825</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.234363390008312</v>
+        <v>1.936007999000132</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.255695443645088</v>
+        <v>1.957691200420562</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.14662552137419</v>
+        <v>1.965578694530933</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.385652227667123</v>
+        <v>2.202533022825662</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.735493348050952</v>
+        <v>2.5513219013027</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.975762699922491</v>
+        <v>2.78950277016061</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 9.404</t>
+          <t>X &gt; 9.402</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>679</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3016873881554929</v>
+        <v>-0.2684130958366637</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8294127570242296</v>
+        <v>0.863085765637571</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.02377744313228902</v>
+        <v>0.01157698053619782</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.030825888290259</v>
+        <v>-0.9946321708713555</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5100626844569689</v>
+        <v>0.5757357143526463</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1825380984306832</v>
+        <v>-0.1170634954444125</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5155215325374911</v>
+        <v>-0.4491294813875442</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6474486120736458</v>
+        <v>-0.5807133601582137</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1272052828610128</v>
+        <v>0.1939116516685147</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.06011986397879809</v>
+        <v>0.007506239561642758</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2142394031365384</v>
+        <v>0.2815658817235658</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2284006316264424</v>
+        <v>0.2960716102403751</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4235575069809414</v>
+        <v>0.4925576372259002</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4954558279113996</v>
+        <v>0.5647338927441226</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.8056445220411987</v>
+        <v>0.786355991057988</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.0491454458096</v>
+        <v>0.9408602150537675</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.593384940606363</v>
+        <v>1.393453342005913</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.077503144540536</v>
+        <v>1.875122902114349</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.146350902464988</v>
+        <v>2.034602502880979</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.627945508100147</v>
+        <v>2.606047086279084</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.821122124139009</v>
+        <v>2.891058745567662</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.18699328351849</v>
+        <v>3.257038999180651</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.050870070030072</v>
+        <v>4.120615331692157</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.827653325754241</v>
+        <v>3.897507673461519</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 9.99</t>
+          <t>X &gt; 9.988</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>535</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.403093368367621</v>
+        <v>-0.3698190760487918</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.196310556240384</v>
+        <v>0.2299835648537254</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4957263564438747</v>
+        <v>-0.4603719327753879</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.209519669637032</v>
+        <v>-1.173325952218129</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8551170873949943</v>
+        <v>0.9207901172906716</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.07921362670102639</v>
+        <v>-0.01373902371475566</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2913320952036429</v>
+        <v>-0.2249400440536959</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1960549650212755</v>
+        <v>-0.1293197131058434</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5283706756995699</v>
+        <v>-0.4616643068920681</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7414584229176029</v>
+        <v>-0.673832319377162</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.840930931503209</v>
+        <v>-0.7736044529161816</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1854453957257718</v>
+        <v>-0.1177744171118391</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3753571749605769</v>
+        <v>-0.3063570447156181</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.1509495654069468</v>
+        <v>0.2202276302396697</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.9873454291733808</v>
+        <v>1.057411435462846</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.021657815243358</v>
+        <v>1.091050693854434</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.448311784645838</v>
+        <v>1.517881220428364</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.530244256401026</v>
+        <v>1.59995640445765</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.933283307183309</v>
+        <v>2.002763673232444</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.746495327102807</v>
+        <v>1.815777707499535</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.950958469506716</v>
+        <v>2.020895090935369</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.622666965265971</v>
+        <v>2.692712680928132</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>4.205853346701382</v>
+        <v>4.275598608363467</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>4.316827895283375</v>
+        <v>4.386682242990652</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 10.58</t>
+          <t>X &gt; 10.57</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4273681589975524</v>
+        <v>-0.6692708860417866</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7625436736418791</v>
+        <v>-1.004047684391601</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.682763618247499</v>
+        <v>-1.666872934972979</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.656297191180919</v>
+        <v>-2.638224887232262</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.134277179639199</v>
+        <v>0.9019536324685333</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.02274049394468136</v>
+        <v>-0.2030698455167794</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4903853783690835</v>
+        <v>-0.7166205965905874</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.01028075533313455</v>
+        <v>0.03875968992248602</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.506644738085789</v>
+        <v>-1.211742792245502</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.50125936963444</v>
+        <v>-1.209464669832379</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.006120881739882</v>
+        <v>-1.710598826120069</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.285214785214784</v>
+        <v>-1.989348229568066</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.851264445260369</v>
+        <v>-1.562122699524956</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.005300821627351127</v>
+        <v>0.2839818865607455</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3938901576696878</v>
+        <v>-0.115763478203263</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.05857036778856894</v>
+        <v>0.2202255109231785</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.4524043216777471</v>
+        <v>-0.4304874916873587</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.076868257253551</v>
+        <v>-0.7937261283250763</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8607450943217358</v>
+        <v>-0.836232680217293</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.452922077922082</v>
+        <v>-1.42458066869888</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.476641967439512</v>
+        <v>-1.450330971031832</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>0.02421066445829467</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.579321000542862</v>
+        <v>1.590675041023026</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.542340700235435</v>
+        <v>2.5484345190659</v>
       </c>
     </row>
     <row r="21">
@@ -4417,76 +4417,76 @@
         <v>304</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7135950899613306</v>
+        <v>-0.6803207976425014</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.035612709868808</v>
+        <v>-2.001939701255466</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.817418437112842</v>
+        <v>-2.782064013444355</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.51805385556915</v>
+        <v>-4.481860138150246</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.593849956382677</v>
+        <v>-1.528176926486999</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.380369553902213</v>
+        <v>-3.314894950915942</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.166393580693075</v>
+        <v>-3.100001529543128</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.471264015685314</v>
+        <v>-1.404528763769882</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.074484792767947</v>
+        <v>-3.007778423960445</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.861478098274212</v>
+        <v>-2.793851994733771</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.57396093642204</v>
+        <v>-3.506634457835013</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.195160103054839</v>
+        <v>-3.127489124440906</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.00386184785777</v>
+        <v>-2.934861717612812</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5936397115237071</v>
+        <v>-0.5243616466909842</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.9236235821399603</v>
+        <v>-0.8535575758504947</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3293312043235375</v>
+        <v>0.3987240829346135</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.182079615437765</v>
+        <v>1.251649051220291</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.09025409407933438</v>
+        <v>0.1599662421359582</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.3063772570111496</v>
+        <v>0.3758576230602841</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8223684210526301</v>
+        <v>0.8916508014493587</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.266010117317833</v>
+        <v>1.335946738746486</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.821634009043649</v>
+        <v>3.89167972470581</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>4.754303912367881</v>
+        <v>4.824049174029966</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>4.678362573099413</v>
+        <v>4.748216920806691</v>
       </c>
     </row>
     <row r="22">
@@ -4499,76 +4499,76 @@
         <v>247</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.23282585919209</v>
+        <v>-0.1995515668732608</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1631430742412761</v>
+        <v>-0.1294700656279346</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4214479596482974</v>
+        <v>0.4568023833167842</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.506920252330282</v>
+        <v>-1.470726534911378</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.152101460621374</v>
+        <v>0.2177744905170513</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.494742023537832</v>
+        <v>-2.429267420551561</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.648174957211289</v>
+        <v>-1.581782906061342</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3072964043492945</v>
+        <v>-0.2405611524338624</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.290071837302364</v>
+        <v>-2.223365468494862</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.254190648881504</v>
+        <v>-2.186564545341064</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.789547980956456</v>
+        <v>-2.722221502369429</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.639492086860507</v>
+        <v>-0.5718211082465743</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9542667061573695</v>
+        <v>-0.8852665759124108</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.658384579974275</v>
+        <v>1.727662644806998</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.2151215578484553</v>
+        <v>-0.1450555515589897</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.02491980782222214</v>
+        <v>0.04447307078885387</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.5638718015662789</v>
+        <v>-0.4943023657837529</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.073713517256699</v>
+        <v>-1.004001369200076</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.4527320547297435</v>
+        <v>-0.383251688680609</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.2656882591093108</v>
+        <v>-0.1964058787125822</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4056862306781639</v>
+        <v>0.4756228521068167</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.758880972606406</v>
+        <v>2.828926688268567</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>4.65308933746909</v>
+        <v>4.722834599131176</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>4.577147998200623</v>
+        <v>4.6470023459079</v>
       </c>
     </row>
     <row r="23">
@@ -4581,76 +4581,76 @@
         <v>207</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.500208362272538</v>
+        <v>-1.466934069953709</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.318475664356477</v>
+        <v>-2.284802655743135</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1065581710742975</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.056510504437703</v>
+        <v>-2.0203167870188</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.442954010055161</v>
+        <v>1.508627039950838</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.302248526696502</v>
+        <v>-0.2367739237102313</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.823436065887144</v>
+        <v>1.889828117037091</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.443432145006263</v>
+        <v>4.510167396921695</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.51876463514968</v>
+        <v>3.585471003957181</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.711112799259467</v>
+        <v>3.778738902799908</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.019288491495587</v>
+        <v>3.086614970082614</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.672561737779134</v>
+        <v>4.740232716393066</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.480437669050438</v>
+        <v>5.549437799295397</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8.157631582653771</v>
+        <v>8.226909647486494</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>6.049424981297626</v>
+        <v>6.119490987587092</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>5.678301456039783</v>
+        <v>5.747694334650859</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.061115974451241</v>
+        <v>5.130685410233767</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.473040770916342</v>
+        <v>4.542752918972965</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>4.689163933848157</v>
+        <v>4.758644299897291</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>4.876207729468589</v>
+        <v>4.945490109865318</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>4.816099107910254</v>
+        <v>4.886035729338907</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>7.638694776905332</v>
+        <v>7.708740492567493</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>9.362745305706291</v>
+        <v>9.432490567368376</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>8.803712178998218</v>
+        <v>8.873566526705496</v>
       </c>
     </row>
     <row r="24">
@@ -4663,158 +4663,158 @@
         <v>184</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.043686623142108</v>
+        <v>-2.010412330823279</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.835383876916865</v>
+        <v>-1.801710868303523</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5576930366551736</v>
+        <v>-0.5223386129866867</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.358442871587464</v>
+        <v>-2.32224915416856</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.08063516947545</v>
+        <v>1.146308199371127</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9061132609960225</v>
+        <v>-0.8406386580097518</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.038411911297779</v>
+        <v>1.104803962447725</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.107683352735734</v>
+        <v>5.174418604651166</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.062242896019235</v>
+        <v>4.128949264826737</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.918842267858508</v>
+        <v>4.986468371398949</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.106245013234705</v>
+        <v>4.173571491821733</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.001064153238062</v>
+        <v>6.068735131851994</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.050485978229183</v>
+        <v>7.119486108474142</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>10.63347699328178</v>
+        <v>10.70275505811451</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8.344110971635793</v>
+        <v>8.414176977925258</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.939171021257174</v>
+        <v>9.00856389986825</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>8.805077327108251</v>
+        <v>8.874646762890777</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>8.156615650143408</v>
+        <v>8.226327798200032</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>7.82926055220566</v>
+        <v>7.898740918254795</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>7.472826086956516</v>
+        <v>7.542108467353245</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.929625677958562</v>
+        <v>6.999562299387215</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>9.571061926663781</v>
+        <v>9.641107642325942</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>10.93279361488505</v>
+        <v>11.00253887654713</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>10.85685227561658</v>
+        <v>10.92670662332386</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 13.51</t>
+          <t>X &gt; 13.5</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>165</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3407880724174603</v>
+        <v>-0.3075137800986312</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.282024193122403</v>
+        <v>-1.248351184509062</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.9146389791551002</v>
+        <v>0.949993402823587</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4052149400986522</v>
+        <v>-0.3690212226797485</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.2348617060659</v>
+        <v>1.30033630905217</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.492298604314904</v>
+        <v>3.558690655464851</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.850107595159983</v>
+        <v>6.916842847075415</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.285563054122001</v>
+        <v>6.352269422929503</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.210329334710337</v>
+        <v>8.277655813297365</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>10.35547785547786</v>
+        <v>10.42314883409179</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>12.26128966729375</v>
+        <v>12.3302897975387</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>14.46417528050181</v>
+        <v>14.53345334533454</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>11.9870622232827</v>
+        <v>12.05712822957216</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>12.58212227290408</v>
+        <v>12.65151515151516</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>12.44802857875516</v>
+        <v>12.51759801453768</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>12.34304516265988</v>
+        <v>12.4127573107165</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>13.1652289316523</v>
+        <v>13.23470929770144</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>12.74621212121212</v>
+        <v>12.81549450160885</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>11.59695110615356</v>
+        <v>11.66688772758221</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>13.94523847475337</v>
+        <v>14.01528419041554</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>15.43213485335671</v>
+        <v>15.50188011501879</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>14.75013290802764</v>
+        <v>14.81998725573492</v>
       </c>
     </row>
     <row r="26">
@@ -4827,76 +4827,76 @@
         <v>146</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.120399142194408</v>
+        <v>1.153673434513237</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1002921207007716</v>
+        <v>0.1339651293141131</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.455112204559839</v>
+        <v>3.490466628228326</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6865243708187379</v>
+        <v>0.7227180882376416</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.745912120041261</v>
+        <v>3.811585149936938</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5084191988014766</v>
+        <v>0.5738938017877473</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.845142107843337</v>
+        <v>3.911534158993284</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.991244996571353</v>
+        <v>7.057980248486786</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.032761061593988</v>
+        <v>7.099467430401489</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.683583185071136</v>
+        <v>9.751209288611577</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.957942452186472</v>
+        <v>10.0252689307735</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>12.41857457610882</v>
+        <v>12.48624555472276</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.03380938501895</v>
+        <v>14.10280951526391</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>16.55217860138185</v>
+        <v>16.62145666621457</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>13.15352133494729</v>
+        <v>13.22358734123676</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>13.06364987771935</v>
+        <v>13.13304275633043</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>11.55969316987179</v>
+        <v>11.62926260565432</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>11.45470975377651</v>
+        <v>11.52442190183314</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>12.35576442355765</v>
+        <v>12.42524478960679</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>12.54280821917808</v>
+        <v>12.61209059957481</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>12.68453931702944</v>
+        <v>12.75447593845809</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>16.03324179563341</v>
+        <v>16.10328751129557</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>16.99294846896485</v>
+        <v>17.06269373062693</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>16.91700712969638</v>
+        <v>16.98686147740366</v>
       </c>
     </row>
     <row r="27">
@@ -4909,158 +4909,158 @@
         <v>123</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7974233096963559</v>
+        <v>0.8306976020151851</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.275255925133337</v>
+        <v>1.308928933746678</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.713604241535009</v>
+        <v>4.748958665203496</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7477784080166359</v>
+        <v>0.7839721254355396</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.821533013236497</v>
+        <v>2.887206043132174</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.382681366080682</v>
+        <v>1.448155969066953</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.674855884433157</v>
+        <v>4.741247935583104</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.64833375923979</v>
+        <v>7.715069011155222</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.689849824262424</v>
+        <v>7.756556193069926</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10.98105506389951</v>
+        <v>11.04868116743995</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.629398070852247</v>
+        <v>9.696724549439274</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>12.60233668770255</v>
+        <v>12.67000766631648</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>13.9168698594593</v>
+        <v>13.98586998970426</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>16.13453743866885</v>
+        <v>16.20381550350157</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>11.41056554922505</v>
+        <v>11.48063155551451</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>11.19261746876513</v>
+        <v>11.2620103473762</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>8.619499384372304</v>
+        <v>8.68906882015483</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>8.514515968277024</v>
+        <v>8.584228116333648</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>9.54364726129014</v>
+        <v>9.613127627339274</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.54369918699187</v>
+        <v>10.6129815673886</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.81350690807522</v>
+        <v>10.88344352950387</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>13.98958437275781</v>
+        <v>14.05963008841997</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>15.89037579940254</v>
+        <v>15.96012106106463</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>16.62744259021537</v>
+        <v>16.69729693792265</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 15.27</t>
+          <t>X &gt; 15.26</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>114</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.343422453898327</v>
+        <v>3.376696746217156</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.3766679918855829</v>
+        <v>0.4103410004989243</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.200125422536281</v>
+        <v>4.235479846204768</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.73194614443085</v>
+        <v>1.768139861849754</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.243869341862947</v>
+        <v>2.309542371758624</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2005449924986991</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.289746770184124</v>
+        <v>4.356138821334071</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.64277107203398</v>
+        <v>6.709506323949412</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.684287137056614</v>
+        <v>6.750993505864116</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.419223656111747</v>
+        <v>9.486849759652188</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.93919695831481</v>
+        <v>8.006523436901837</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.16887498466447</v>
+        <v>11.2365459632784</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.67596271354574</v>
+        <v>12.7449628437907</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>15.96337783233594</v>
+        <v>16.03265589716867</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>11.79567466347408</v>
+        <v>11.86574066976355</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>11.51354173063933</v>
+        <v>11.5829346092504</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.87067610666584</v>
+        <v>7.940245542448366</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.76569269057056</v>
+        <v>7.835404838627184</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>9.736201818414663</v>
+        <v>9.805682184463798</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>9.923245614035096</v>
+        <v>9.992527994431825</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>8.502852222580991</v>
+        <v>8.572788844009644</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>11.93566909676294</v>
+        <v>12.0057148124251</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>13.96483022815735</v>
+        <v>14.03457548981943</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>14.76608187134503</v>
+        <v>14.83593621905231</v>
       </c>
     </row>
     <row r="29">
@@ -5073,158 +5073,158 @@
         <v>104</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.095109363479978</v>
+        <v>2.128383655798807</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.124681535779736</v>
+        <v>-1.091008527166395</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.243310307826427</v>
+        <v>2.278664731494914</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.5679785330948093</v>
+        <v>0.604172250513713</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2027087480707621</v>
+        <v>0.2683817779664395</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.494742023537832</v>
+        <v>-2.429267420551561</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.540084152100448</v>
+        <v>1.606476203250395</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.146144891197274</v>
+        <v>4.212880143112706</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.259979391604325</v>
+        <v>7.327605495144766</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.611261735642735</v>
+        <v>5.678588214229762</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.13986013986015</v>
+        <v>10.20753111847408</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.89998430598839</v>
+        <v>11.96898443623335</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>14.56324287956942</v>
+        <v>14.63252094440215</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>10.05815779437827</v>
+        <v>10.12822380066773</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>9.691679382461182</v>
+        <v>9.761072261072258</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.711431842158419</v>
+        <v>5.781001277940945</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.606448426063139</v>
+        <v>5.676160574119763</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.745648512071874</v>
+        <v>7.815128878121008</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>7.932692307692307</v>
+        <v>8.001974688089035</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.427953437155885</v>
+        <v>6.497890058584538</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>10.19815222766713</v>
+        <v>10.26819794332929</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>12.39600431722618</v>
+        <v>12.46574957888826</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>13.28160143949616</v>
+        <v>13.35145578720344</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 16.44</t>
+          <t>X &gt; 16.43</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>100</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.325878594249211</v>
+        <v>2.35915288656804</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.009296920395123</v>
+        <v>-1.975623911781781</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.551002615518733</v>
+        <v>2.58635703918722</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.837209302325583</v>
+        <v>2.873403019744487</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.471939517301536</v>
+        <v>2.537612547197213</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3408958696916713</v>
+        <v>-0.2754212667054006</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>2.952630049404242</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.607683352735734</v>
+        <v>4.674418604651166</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.649199417758368</v>
+        <v>5.71590578656587</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.875364006988939</v>
+        <v>8.942990110529379</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.149723274104275</v>
+        <v>6.217049752691302</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.87062937062937</v>
+        <v>10.93830034924331</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.74613815214223</v>
+        <v>12.81513828238719</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>15.52478134110788</v>
+        <v>15.5940594059406</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.865850102070574</v>
+        <v>9.93591610836004</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>10.46091015169196</v>
+        <v>10.53030303030303</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>7.326816457543032</v>
+        <v>7.396385893325558</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>8.221833041447752</v>
+        <v>8.291545189504376</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>10.43795620437957</v>
+        <v>10.5074365704287</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>10.625</v>
+        <v>10.69428238039673</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>9.081799591002046</v>
+        <v>9.151736212430698</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>12.00584453535944</v>
+        <v>12.0758902510216</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>13.28061970184157</v>
+        <v>13.35036496350365</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>13.2046783625731</v>
+        <v>13.27453271028038</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>94</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.645027530419419</v>
+        <v>1.678301822738248</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.073126707629164</v>
+        <v>-5.039453699015823</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1298484483110443</v>
+        <v>-0.09449402464255741</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2201880257298328</v>
+        <v>0.2563817431487365</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1450817592942144</v>
+        <v>-0.07940872939853705</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.085576720755512</v>
+        <v>-2.020102117769241</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.460706083360677</v>
+        <v>2.527098134510624</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.309811012310199</v>
+        <v>4.376546264225631</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.478986651800923</v>
+        <v>6.545693020608425</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.896640602733619</v>
+        <v>8.96426670627406</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.915680720912782</v>
+        <v>4.983007199499809</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.891905966374054</v>
+        <v>8.959576944987987</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.95890410958904</v>
+        <v>11.02790423983399</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.92903666025681</v>
+        <v>13.99831472508953</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>7.950956485049296</v>
+        <v>8.021022491338762</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>8.546016534670677</v>
+        <v>8.615409413281753</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.220433478819629</v>
+        <v>5.290002914602155</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.179279849958391</v>
+        <v>6.248991998015015</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>9.586892374592345</v>
+        <v>9.65637274064148</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>10.83776595744681</v>
+        <v>10.90704833784353</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>10.29456554844885</v>
+        <v>10.3645021698775</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>13.41009985450837</v>
+        <v>13.48014557017053</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>12.62104523375647</v>
+        <v>12.69079049541855</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>12.545103894488</v>
+        <v>12.61495824219528</v>
       </c>
     </row>
     <row r="32">
@@ -5319,158 +5319,158 @@
         <v>93</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.164588271668556</v>
+        <v>1.197862563987385</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.546931328997275</v>
+        <v>-4.513258320383933</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6102877070619073</v>
+        <v>-0.5749332833934204</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2488122030507682</v>
+        <v>-0.2126184856318645</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.6140819880748154</v>
+        <v>-0.548408958179138</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.57745500947663</v>
+        <v>-2.511980406490359</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.026022944490855</v>
+        <v>2.092414995640802</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.898005933380894</v>
+        <v>3.964741185296326</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.090059632812128</v>
+        <v>6.15676600161963</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.515314671953739</v>
+        <v>4.582641150540766</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.537296037296031</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.6386112704218</v>
+        <v>10.70761140066676</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.64306091100035</v>
+        <v>13.71233897583308</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7.607785585941535</v>
+        <v>7.677851592231001</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.202845635562916</v>
+        <v>8.272238514173992</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.842945489801096</v>
+        <v>4.912514925583622</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.81323089091012</v>
+        <v>5.882943038966744</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>9.255160505454846</v>
+        <v>9.324640871503981</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>10.51747311827957</v>
+        <v>10.5867554986763</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9.974272709281614</v>
+        <v>10.04420933071027</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>13.12412410525192</v>
+        <v>13.19416982091408</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>12.32363045452974</v>
+        <v>12.39337571619183</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>12.24768911526127</v>
+        <v>12.31754346296855</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 18.2</t>
+          <t>X &gt; 18.19</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>89</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.382058369530107</v>
+        <v>1.415332661848936</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.571094673204115</v>
+        <v>-4.537421664590774</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.516413114818342</v>
+        <v>-1.481058691149855</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.230206428011499</v>
+        <v>-2.194012710592595</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.595476213035546</v>
+        <v>-2.529803183139869</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.655502611264708</v>
+        <v>-4.590028008278438</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1896087847711456</v>
+        <v>0.2560008359210926</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.158245150488547</v>
+        <v>2.224980402403979</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.446952226747129</v>
+        <v>4.513658595554631</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.04390333283164</v>
+        <v>7.111529436372081</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.823880577475066</v>
+        <v>2.891207056062093</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.039168696472075</v>
+        <v>7.106839675086007</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.285463994838857</v>
+        <v>9.354464125083815</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.43489370065844</v>
+        <v>12.50417176549117</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.157984933531246</v>
+        <v>6.228050939820712</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>6.753044983152627</v>
+        <v>6.822437861763703</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.248164772149771</v>
+        <v>3.317734207932297</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.266776861672469</v>
+        <v>4.336489009729092</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>7.853686541458224</v>
+        <v>7.923166907507358</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>9.164325842696627</v>
+        <v>9.233608223093356</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.621125433698673</v>
+        <v>8.691062055127325</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>11.91595689491</v>
+        <v>11.98600261057216</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>11.06713655577415</v>
+        <v>11.13688181743623</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>10.99119521650568</v>
+        <v>11.06104956421296</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>83</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.157203895454018</v>
+        <v>4.190478187772847</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.202068004732475</v>
+        <v>-2.168394996119133</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.02731063749330787</v>
+        <v>0.00804378617517898</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7411039506864654</v>
+        <v>-0.7049102332675616</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.106373735710513</v>
+        <v>-1.040700705814835</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.328847676920589</v>
+        <v>-3.263373073934318</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.92238257656755</v>
+        <v>1.988774627717497</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.053466485265851</v>
+        <v>4.120201737181283</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.504621104505347</v>
+        <v>6.571327473312849</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9.345243525061228</v>
+        <v>9.412869628601669</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.800325683742834</v>
+        <v>4.867652162329861</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.340508888701663</v>
+        <v>9.408179867315596</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.83047550153982</v>
+        <v>11.89947563178477</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.22357652183076</v>
+        <v>15.29285458666348</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.540548897251291</v>
+        <v>8.610614903540757</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>10.34042822398111</v>
+        <v>10.40982110259219</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>5.387057421398453</v>
+        <v>5.456626857180979</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>6.486893282411614</v>
+        <v>6.556605430468238</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>10.31747427666873</v>
+        <v>10.38695464271786</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>11.70933734939759</v>
+        <v>11.77861972979431</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>11.16613694039963</v>
+        <v>11.23607356182828</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>14.70463971608232</v>
+        <v>14.77468543174448</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>13.77459560545602</v>
+        <v>13.84434086711811</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>13.69865426618755</v>
+        <v>13.76850861389483</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 19.37</t>
+          <t>X &gt; 19.36</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.398342362365149</v>
+        <v>1.431616654683978</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.790454555015664</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.438153016514995</v>
+        <v>-5.401959299096092</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.252698163857879</v>
+        <v>-7.187025133962202</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.96408427548878</v>
+        <v>-9.898609672502509</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-3.490573595948597</v>
+        <v>-3.42418154479865</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.8705775168294849</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2.069489272830829</v>
+        <v>2.136195641638331</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.092755311336767</v>
+        <v>7.160381414877207</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>3.019288491495587</v>
+        <v>3.086614970082614</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>8.537296037296031</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.31135554344657</v>
+        <v>10.38035567369153</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>14.43782481936874</v>
+        <v>14.50710288420146</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.645657037253173</v>
+        <v>2.715226473035699</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.540673621157893</v>
+        <v>2.610385769214517</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>8.740942028985515</v>
+        <v>8.810224409382243</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.197741619987561</v>
+        <v>8.267678241416213</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12.46961265130147</v>
+        <v>12.53965836696363</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>11.29511245546475</v>
+        <v>11.36485771712684</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>11.21917111619629</v>
+        <v>11.28902546390356</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.848034449229054</v>
+        <v>-5.814760156910225</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.98031141314875</v>
+        <v>-11.94663840453541</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16.31856260187256</v>
+        <v>-16.28320817820408</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.58308055274688</v>
+        <v>-15.54688683532797</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.49907497545209</v>
+        <v>-14.43340194555641</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.3119103624453</v>
+        <v>-14.24643575945903</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-17.98332721913701</v>
+        <v>-17.91693516798706</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-22.60970795161209</v>
+        <v>-22.54297269969666</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-24.0174672489083</v>
+        <v>-23.9507608801008</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-24.79130265967773</v>
+        <v>-24.72367655613729</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-27.41549411720007</v>
+        <v>-27.34816763861304</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-30.59313874531265</v>
+        <v>-30.52546776669872</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-36.06545605075632</v>
+        <v>-35.99645592051137</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-39.18536358642835</v>
+        <v>-39.11608552159564</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-38.39501946314682</v>
+        <v>-38.32495345685735</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-37.79995941352544</v>
+        <v>-37.73056653491436</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-39.3833284699932</v>
+        <v>-39.31375903421068</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-38.03903652376964</v>
+        <v>-37.96932437571301</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-37.82291336083782</v>
+        <v>-37.75343299478869</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-36.18659420289855</v>
+        <v>-36.11731182250182</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-36.72979461189651</v>
+        <v>-36.65985799046786</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-36.80574966753912</v>
+        <v>-36.73570395187696</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-37.98024986337582</v>
+        <v>-37.91050460171374</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-36.60691584032546</v>
+        <v>-36.53706149261818</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>207</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.466391937151755</v>
+        <v>-2.433117644832926</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.173635065640674</v>
+        <v>-6.138280641972187</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.819795528592294</v>
+        <v>-8.783601811173391</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-11.11743246337479</v>
+        <v>-11.05175943347911</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.44717606292839</v>
+        <v>-10.38170145994212</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-10.73695040754281</v>
+        <v>-10.67055835639286</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-11.98168862794059</v>
+        <v>-11.91495337602516</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.35563150011603</v>
+        <v>-14.28892513130852</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-14.64637512344584</v>
+        <v>-14.5787490199054</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-16.78747479352857</v>
+        <v>-16.72014831494155</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-16.10038512212425</v>
+        <v>-16.03271414351032</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.74178455317178</v>
+        <v>-16.67278442292682</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-16.48004957676652</v>
+        <v>-16.4107715119338</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-14.72352187860575</v>
+        <v>-14.65345587231629</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-15.57773719130321</v>
+        <v>-15.50834431269214</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-18.12728982265021</v>
+        <v>-18.05772038686768</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-18.7153650261851</v>
+        <v>-18.64565287812847</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-19.94851722557213</v>
+        <v>-19.87903685952299</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-19.76147342995169</v>
+        <v>-19.69219104955496</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-19.82158205151003</v>
+        <v>-19.75164543008137</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-18.4482617448338</v>
+        <v>-18.37821602917164</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-17.69039479091206</v>
+        <v>-17.62064952924997</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-16.31706076786168</v>
+        <v>-16.24720642015441</v>
       </c>
     </row>
     <row r="8">
@@ -5995,1060 +5995,1060 @@
         <v>409</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.040869572009967</v>
+        <v>-4.007595279691138</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.354040196678739</v>
+        <v>-5.320367188065397</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.104254108197637</v>
+        <v>-4.06889968452915</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.796042531415246</v>
+        <v>-5.759848813996342</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.383806203969861</v>
+        <v>-7.318133174074184</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.70764403595085</v>
+        <v>-6.642169432964579</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.23601139049876</v>
+        <v>-7.169619339348813</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.781069703498993</v>
+        <v>-6.714334451583561</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.695543858525248</v>
+        <v>-8.628837489717746</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-9.469379269294677</v>
+        <v>-9.401753165754236</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.4175138897099</v>
+        <v>-10.35018741112287</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-10.45210901567869</v>
+        <v>-10.38443803706476</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.82109901167195</v>
+        <v>-11.75209888142699</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-13.02045093273076</v>
+        <v>-12.95117286789804</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-13.43488339426194</v>
+        <v>-13.36481738797248</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-13.5733196771589</v>
+        <v>-13.50392679854782</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.44090970382616</v>
+        <v>-14.37134026804364</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-13.07890045488477</v>
+        <v>-13.00918830682814</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-12.86277729195295</v>
+        <v>-12.79329692590382</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-12.67573349633252</v>
+        <v>-12.60645111593579</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-11.99644001779991</v>
+        <v>-11.92650339637126</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-11.82789629593641</v>
+        <v>-11.75785058027424</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-12.53111623947873</v>
+        <v>-12.46137097781664</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-11.38456369121663</v>
+        <v>-11.31470934350936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 4.129</t>
+          <t>X &lt; 4.128</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>673</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1822937683065149</v>
+        <v>-0.1490194759876857</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.8146461031588643</v>
+        <v>-0.7809730945455229</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4712856459968577</v>
+        <v>-0.4359312223283709</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5907253187739698</v>
+        <v>-0.5545316013550661</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.590467614942149</v>
+        <v>-2.524794585046472</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.889187102975477</v>
+        <v>-3.823712499989206</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.662053235029504</v>
+        <v>-4.595661183879557</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.683549931068121</v>
+        <v>-5.616814679152689</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.790622276149513</v>
+        <v>-5.723915907342011</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.415869276814917</v>
+        <v>-6.348243173274476</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.330217290531685</v>
+        <v>-7.262890811944658</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.717780733382519</v>
+        <v>-6.650109754768586</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.545095131661625</v>
+        <v>-7.476095001416667</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.509393993216051</v>
+        <v>-8.440115928383328</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-9.019736822149341</v>
+        <v>-8.949670815859875</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-9.167618823048016</v>
+        <v>-9.09822594443694</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-9.450300927300951</v>
+        <v>-9.380731491518425</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-9.555284343396231</v>
+        <v>-9.485572195339607</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.636338000672438</v>
+        <v>-9.566857634623304</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-10.78658989598812</v>
+        <v>-10.71730751559139</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-10.28967143425798</v>
+        <v>-10.21973481282933</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-10.21703807979658</v>
+        <v>-10.14699236413442</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-10.5366165537305</v>
+        <v>-10.46687129206842</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-9.572439022270885</v>
+        <v>-9.502584674563607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 4.715</t>
+          <t>X &lt; 4.714</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>925</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.052499784129175</v>
+        <v>-0.01922549181034583</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.04475713365893341</v>
+        <v>0.07843014227227485</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6591107236268527</v>
+        <v>0.6944651472953396</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8101822752985512</v>
+        <v>0.846375992717455</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7442766989146818</v>
+        <v>-0.6786036690190045</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.557112085907896</v>
+        <v>-0.4916374829216252</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.113762001745698</v>
+        <v>-1.047369950595751</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.284208539156154</v>
+        <v>-1.217473287240722</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.458908690349745</v>
+        <v>-1.392202321542243</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.259771128146198</v>
+        <v>-1.192145024605757</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.634060509679507</v>
+        <v>-1.56673403109248</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.156397656397658</v>
+        <v>-1.088726677783725</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.388996982992907</v>
+        <v>-2.319996852747948</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.150894334567802</v>
+        <v>-3.081616269735079</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-2.836852600632128</v>
+        <v>-2.766786594342662</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.998549307767505</v>
+        <v>-2.929156429156428</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-3.456967326240751</v>
+        <v>-3.387397890458224</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.56195074233603</v>
+        <v>-3.492238594279407</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.670151903728545</v>
+        <v>-3.600671537679411</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.131756756756758</v>
+        <v>-4.062474376360029</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.161443652241196</v>
+        <v>-3.091507030812544</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-2.913074383559476</v>
+        <v>-2.843028667897315</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.395055973834111</v>
+        <v>-3.325310712172026</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.254781096886362</v>
+        <v>-3.184926749179084</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 5.301</t>
+          <t>X &lt; 5.3</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1191</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9858282164154559</v>
+        <v>1.019102508734285</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.574246320578851</v>
+        <v>1.607919329192192</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.065696150363401</v>
+        <v>2.101050574031888</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.191533399722729</v>
+        <v>2.227727117141633</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.658337502188189</v>
+        <v>1.724010532083867</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.509649890173975</v>
+        <v>1.575124493160246</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.324525151906684</v>
+        <v>1.390917203056631</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.381822731409116</v>
+        <v>1.448557983324548</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.507301852686993</v>
+        <v>1.574008221494495</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.657060060725293</v>
+        <v>1.724686164265734</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.847456271585386</v>
+        <v>1.914782750172414</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.324029874407714</v>
+        <v>2.391700853021646</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.11557559966532</v>
+        <v>1.184575729910279</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6423296198652224</v>
+        <v>0.7116076846979453</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.4871767183594002</v>
+        <v>0.5572427246488658</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1586431491730664</v>
+        <v>0.2280360277841424</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.3113027699968498</v>
+        <v>-0.2417333342143237</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.6681753548578726</v>
+        <v>-0.5984632068012488</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.7879044169470504</v>
+        <v>-0.7184240508979158</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.188602015113347</v>
+        <v>-1.119319634716618</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.808208805303579</v>
+        <v>-0.7382721838749262</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.052089973456681</v>
+        <v>-0.9820442577945201</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.449019257016538</v>
+        <v>-1.379273995354453</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.273071427519255</v>
+        <v>-1.203217079811978</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 5.887</t>
+          <t>X &lt; 5.886</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5941712771760379</v>
+        <v>0.5964410221612511</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.817261345187539</v>
+        <v>1.820986257709741</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.139078496277548</v>
+        <v>2.145679073085539</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.967290603138593</v>
+        <v>1.975097934998729</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.805272850634871</v>
+        <v>1.842697292959926</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.625205825223574</v>
+        <v>1.62288381804035</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.909304484007343</v>
+        <v>1.86788428669238</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.969962864268979</v>
+        <v>1.928655892786757</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.740108508667461</v>
+        <v>1.698956634023503</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.617387089134219</v>
+        <v>1.576640042686776</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.592658056712963</v>
+        <v>1.619629521869847</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.829840791431543</v>
+        <v>1.816100756575281</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.8821925739109346</v>
+        <v>0.828716014905865</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7017724915503578</v>
+        <v>0.6484072320275516</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.5193558883197227</v>
+        <v>0.5069562171295843</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.2975337051296734</v>
+        <v>0.3262213976499666</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2995870497826516</v>
+        <v>0.3691564855651777</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1457639633173926</v>
+        <v>-0.03543028733485443</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2700083973903418</v>
+        <v>-0.1601383614514091</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.7636997957794378</v>
+        <v>-0.6544914615651223</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.6261650107678634</v>
+        <v>-0.5158387194494125</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.8382671052123882</v>
+        <v>-0.72792446287486</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.176153613338826</v>
+        <v>-1.06652876946638</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.252094952607294</v>
+        <v>-1.142361022689656</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 6.473</t>
+          <t>X &lt; 6.472</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1696</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5145136264694727</v>
+        <v>0.5477879187883019</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.409566582826905</v>
+        <v>1.443239591440246</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.668753054886054</v>
+        <v>1.70410747855454</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9884402519152644</v>
+        <v>0.9911534591117999</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.008596408797132</v>
+        <v>1.006856835422163</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.8774139894632498</v>
+        <v>0.8423291726619055</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.07766489197126</v>
+        <v>1.007697419058609</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.362089933229271</v>
+        <v>1.291065732435456</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.379358147917102</v>
+        <v>1.308281153134786</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.228305183459526</v>
+        <v>1.156605134003556</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.007875128136057</v>
+        <v>0.9369558008416305</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.116801337649399</v>
+        <v>1.045233369219801</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1450774567975017</v>
+        <v>0.07439754164644086</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.04125639474118259</v>
+        <v>-0.1118229470005829</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3464140488728233</v>
+        <v>-0.3819179116517262</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.753712489817481</v>
+        <v>-0.7535603383659932</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.064692976419224</v>
+        <v>-1.029660070139386</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.405525449118286</v>
+        <v>-1.335813301061663</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.307326814488363</v>
+        <v>-1.237846448439228</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.533018867924532</v>
+        <v>-1.463736487527804</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.545558899563993</v>
+        <v>-1.47562227813534</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.034249804263212</v>
+        <v>-1.964204088601051</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.290135015139562</v>
+        <v>-2.220389753477477</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-2.130227297804254</v>
+        <v>-2.060372950096976</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 7.059</t>
+          <t>X &lt; 7.058</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1909</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2842119275825326</v>
+        <v>0.3174862199013617</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8344530796048772</v>
+        <v>0.8681260882182187</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.853085948852069</v>
+        <v>0.8884403725205559</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6376261861192276</v>
+        <v>0.6442363530778223</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7712095902942409</v>
+        <v>0.7771958805305488</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6752752309864718</v>
+        <v>0.6516620666279209</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.819432152742813</v>
+        <v>0.7651300494042417</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.145542360568626</v>
+        <v>1.09026018880958</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.269889072930773</v>
+        <v>1.214341657264512</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.206257890940847</v>
+        <v>1.150084528891405</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.093237918455742</v>
+        <v>1.037509042879186</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.420603206317494</v>
+        <v>1.363887816606237</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8508501940270392</v>
+        <v>0.7942396407988923</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8705120901911698</v>
+        <v>0.8136098502688824</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.5782649789694787</v>
+        <v>0.5530709200755197</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1780395388056348</v>
+        <v>0.1849341135055482</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.1132044958356957</v>
+        <v>-0.07481829515612048</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.3753382524233828</v>
+        <v>-0.305626104366759</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.3687488768147702</v>
+        <v>-0.2992685107656357</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.6007726558407569</v>
+        <v>-0.5314902754440283</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.620138596530694</v>
+        <v>-0.5502019751020413</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.062777779988913</v>
+        <v>-0.9927320643267521</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.259453634983998</v>
+        <v>-1.189708373321913</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.178244633760059</v>
+        <v>-1.108390286052781</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 7.645</t>
+          <t>X &lt; 7.644</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2112</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.443525653072733</v>
+        <v>0.4005062700266819</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3692341530512024</v>
+        <v>0.3732242311425296</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7921707737853509</v>
+        <v>0.7951999366472506</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5761348442671448</v>
+        <v>0.5792853726856606</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4733539444585375</v>
+        <v>0.4317301942560405</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5930663944592638</v>
+        <v>0.5513207295281148</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8852941568196613</v>
+        <v>0.8424086645714581</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9174095094873849</v>
+        <v>0.8742301032374087</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8919958277725399</v>
+        <v>0.8488619393240029</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8545700561382716</v>
+        <v>0.8109146388312638</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8258462055463482</v>
+        <v>0.7824107720400519</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.378670997876299</v>
+        <v>1.333956628752276</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8502555208123681</v>
+        <v>0.8056909512582351</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.08349346232</v>
+        <v>1.038293810477462</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.8506985869190586</v>
+        <v>0.8342612620243415</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4040919698737753</v>
+        <v>0.4167741750523177</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.3646952454218138</v>
+        <v>0.4058511086592063</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3070603141750254</v>
+        <v>0.3767724622316493</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1443955983189582</v>
+        <v>0.2138759643680928</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0</v>
+        <v>0.06928238039672863</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.02498140918386582</v>
+        <v>0.09491803061251858</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.3824130403981414</v>
+        <v>-0.3123673247359804</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.675819692097825</v>
+        <v>-0.6060744304357399</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.5623670919723622</v>
+        <v>-0.4925127442650847</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 8.231</t>
+          <t>X &lt; 8.23</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2353</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.383359574807109</v>
+        <v>0.3675917051334281</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1133246440869087</v>
+        <v>0.09782480075514854</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3462648828622221</v>
+        <v>0.3296002824304693</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1639126455333653</v>
+        <v>0.1471672782996265</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1188489161160931</v>
+        <v>0.08875371372300123</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3723612247598282</v>
+        <v>0.3419148855144698</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5981024050339485</v>
+        <v>0.5668432473737823</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.555966523570838</v>
+        <v>0.5246090405377473</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.452422488157012</v>
+        <v>0.4212402488859368</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4243669768658975</v>
+        <v>0.3927995133248032</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1717945814047823</v>
+        <v>0.1407785662506313</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4268926402684343</v>
+        <v>0.3952736430118478</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.219375195472729</v>
+        <v>0.1874877310725154</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5332811286131829</v>
+        <v>0.5007204156987655</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.4268360774211857</v>
+        <v>0.4197870761019757</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.5544078142503892</v>
+        <v>0.5727658753136424</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.4628130576280256</v>
+        <v>0.506836190691736</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.5278253916389914</v>
+        <v>0.5975375396956153</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.4464559918848749</v>
+        <v>0.5159363579340095</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.2935082872928234</v>
+        <v>0.362790667689552</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.3877919411932851</v>
+        <v>0.4577285626219378</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.1418411354444302</v>
+        <v>0.2118868511065912</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.05087201086561066</v>
+        <v>0.01887325079647439</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.04181547508096628</v>
+        <v>0.02803887262631122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 8.818</t>
+          <t>X &lt; 8.816</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.04868519016335426</v>
+        <v>-0.07771775634444111</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3630595270669588</v>
+        <v>-0.3917416955865036</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1521405742367961</v>
+        <v>-0.1810848212778922</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.04838942654918554</v>
+        <v>0.01919596274564839</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4503905797858465</v>
+        <v>-0.4887644892651579</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3191398479356593</v>
+        <v>-0.357687467714328</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.09860459793692655</v>
+        <v>-0.1374320623970036</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.04394961771527761</v>
+        <v>-0.08286294874690014</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3301860353727122</v>
+        <v>-0.3687872981272093</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4203558373690441</v>
+        <v>-0.4588754160932353</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5127913230152288</v>
+        <v>-0.5512239642604868</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4969718754765466</v>
+        <v>-0.5354452750273992</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.7030242942933</v>
+        <v>-0.7412819510758411</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5508227118929057</v>
+        <v>-0.5892804150014044</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.7031288535022995</v>
+        <v>-0.7182894991165938</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.7316073853306406</v>
+        <v>-0.6851235376751532</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.748787595457749</v>
+        <v>-0.7181893210158279</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.9706844955748437</v>
+        <v>-0.8780454537704827</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.105301784708509</v>
+        <v>-1.013031265828609</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.113113795791108</v>
+        <v>-1.021117229739723</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.071746784679945</v>
+        <v>-1.01785443084416</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.147701840322554</v>
+        <v>-1.093700392253261</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.223667125905905</v>
+        <v>-1.17010287275366</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.260637303833754</v>
+        <v>-1.206948771201112</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 9.404</t>
+          <t>X &lt; 9.402</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2717</v>
+        <v>2721</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.07529056906830078</v>
+        <v>-0.08375116304889474</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5005249905705611</v>
+        <v>-0.508470627110249</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.348448938411785</v>
+        <v>-0.3570529644637332</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1276773106956313</v>
+        <v>-0.1368234229143894</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5090337721240061</v>
+        <v>-0.5252299811184571</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3379676120050021</v>
+        <v>-0.3543686351264554</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2481450116321966</v>
+        <v>-0.2649202248187947</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.212829467777091</v>
+        <v>-0.2297511100525682</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4068650747297227</v>
+        <v>-0.4235014582200876</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3533749959436108</v>
+        <v>-0.3703334619450018</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.424534151638305</v>
+        <v>-0.4413171458806531</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.4257756183654919</v>
+        <v>-0.4426520317090805</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.464871022169703</v>
+        <v>-0.4820401712588307</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4810923740169457</v>
+        <v>-0.498315960628311</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.552652100572594</v>
+        <v>-0.5481322964804463</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.6183850024930706</v>
+        <v>-0.592220814157713</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.7524786966419938</v>
+        <v>-0.7045315378671049</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8725481557612085</v>
+        <v>-0.8244606842107487</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.8919482776189582</v>
+        <v>-0.8655443399971503</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.014103270856303</v>
+        <v>-1.009095005800042</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.057906291350896</v>
+        <v>-1.074401819874737</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.148991801529128</v>
+        <v>-1.165387751181854</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.330859326856007</v>
+        <v>-1.346916447223755</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.238089395984133</v>
+        <v>-1.254316977334469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 9.99</t>
+          <t>X &lt; 9.988</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2861</v>
+        <v>2865</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.06801877052194527</v>
+        <v>-0.07436511897213194</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3152282419351806</v>
+        <v>-0.3213114767280985</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2442784393043027</v>
+        <v>-0.2507877979576136</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1405761888233172</v>
+        <v>-0.147394207291903</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5211160382540214</v>
+        <v>-0.5331225429553541</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3492320975485725</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3034770816623151</v>
+        <v>-0.3159334481668949</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3189763622451522</v>
+        <v>-0.3314821242624078</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2576156031039432</v>
+        <v>-0.2702053245452447</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2115925147501869</v>
+        <v>-0.2244291322632535</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1954402610383852</v>
+        <v>-0.208245591297576</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3152390595829502</v>
+        <v>-0.3279492162763376</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2705749397797774</v>
+        <v>-0.2836099790870819</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3668940333261261</v>
+        <v>-0.3798536375376642</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.5174251592534631</v>
+        <v>-0.5303330217721722</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.5289817967221282</v>
+        <v>-0.5417470915208469</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6076326359018793</v>
+        <v>-0.6203271985964491</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.6222548553084337</v>
+        <v>-0.63496125424345</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.6995176267439476</v>
+        <v>-0.7120756246932558</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.6664485165794076</v>
+        <v>-0.6790184212763251</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.70032331402588</v>
+        <v>-0.7129778740407104</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.8254513081613482</v>
+        <v>-0.8379569760450281</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.089051856509244</v>
+        <v>-1.101135385414707</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.074594618901912</v>
+        <v>-1.086723834222248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 10.58</t>
+          <t>X &lt; 10.57</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3011</v>
+        <v>3013</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.08150439849964641</v>
+        <v>-0.05059678405120138</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1682154828745155</v>
+        <v>-0.1370736646648112</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1059894689139824</v>
+        <v>-0.1071169225794222</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.009705907176233097</v>
+        <v>-0.01054027072699881</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4884565223024211</v>
+        <v>-0.4597489303753477</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3488192767567213</v>
+        <v>-0.320290946679016</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2775664931591777</v>
+        <v>-0.2486900826089595</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3391286723716291</v>
+        <v>-0.3430789192841246</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1465705756322535</v>
+        <v>-0.183697912245222</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1411649186308921</v>
+        <v>-0.1779216833259198</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.07911270473169907</v>
+        <v>-0.1160632677977986</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.04137856850393717</v>
+        <v>-0.07822857637652447</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.08774669233162768</v>
+        <v>-0.1240151567662551</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3226201815667338</v>
+        <v>-0.3586365914130312</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.2666002290552498</v>
+        <v>-0.3023367043467786</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.3141809380728731</v>
+        <v>-0.3502001143510611</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.2629781083946767</v>
+        <v>-0.2658657623035765</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.1825421657116735</v>
+        <v>-0.2185574935032477</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.2119111696257292</v>
+        <v>-0.2148961002141121</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1378524046434464</v>
+        <v>-0.1409844409489764</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.13054281112138</v>
+        <v>-0.1334096761634669</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.3194126833594453</v>
+        <v>-0.3221196992271587</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4896326221956144</v>
+        <v>-0.4923689449236903</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.579114397307336</v>
+        <v>-0.5817567022652597</v>
       </c>
     </row>
     <row r="21">
@@ -7058,79 +7058,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3092</v>
+        <v>3096</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.06256442340729507</v>
+        <v>-0.0659833750542802</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.05939325950880203</v>
+        <v>-0.06285931909415865</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.03621228971736201</v>
+        <v>-0.03988614336009277</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1032761403718538</v>
+        <v>0.0993337001039265</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.179619466947905</v>
+        <v>-0.1863039857080793</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.006490724997142649</v>
+        <v>-0.01337887749538424</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.0214493610252191</v>
+        <v>-0.02841717192566051</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1851094400570545</v>
+        <v>-0.1919053028038533</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.0286248500240589</v>
+        <v>-0.03562105367841895</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.04350270260540157</v>
+        <v>-0.05057902130342029</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.02411940936998036</v>
+        <v>0.01698542332493957</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.01081392833969375</v>
+        <v>-0.01794160699865444</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.02086152558899812</v>
+        <v>-0.02811887886160491</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.255360502863752</v>
+        <v>-0.262347548341431</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.2179938192451374</v>
+        <v>-0.225114487453169</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3455414612112691</v>
+        <v>-0.3524289284598581</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.4282658270649051</v>
+        <v>-0.4350675388368686</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3204523039363707</v>
+        <v>-0.3274103230681504</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.3434451517715473</v>
+        <v>-0.3503512399550459</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.3956718346253183</v>
+        <v>-0.4024918131516628</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4351632522935915</v>
+        <v>-0.4420037036712685</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.685816744537135</v>
+        <v>-0.6923473216059008</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7475083291962576</v>
+        <v>-0.7539295150239553</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.7073526852923635</v>
+        <v>-0.7138393827428757</v>
       </c>
     </row>
     <row r="22">
@@ -7140,79 +7140,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3149</v>
+        <v>3153</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1117002203787933</v>
+        <v>-0.1143987507115654</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2407696419340724</v>
+        <v>-0.2433404472148482</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3385872898440425</v>
+        <v>-0.3411791926968277</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2145420387914925</v>
+        <v>-0.217362817003071</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3411917958297792</v>
+        <v>-0.3463723203942166</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1362858286433664</v>
+        <v>-0.141709503854571</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1965162658012929</v>
+        <v>-0.2019440830878736</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2991096962374158</v>
+        <v>-0.3044390791607654</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1447323142264594</v>
+        <v>-0.1502558295957428</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1417083926316778</v>
+        <v>-0.1473161730197177</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1020161313353185</v>
+        <v>-0.1076501841374977</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2679343750207437</v>
+        <v>-0.2733900141058214</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2348745060856174</v>
+        <v>-0.2404875077518724</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4375485101108652</v>
+        <v>-0.4429307932373945</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.286144831431649</v>
+        <v>-0.2917878764596864</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.3056403709561266</v>
+        <v>-0.3112028222752627</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.262537154624269</v>
+        <v>-0.2681710686997505</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.2219070536394128</v>
+        <v>-0.2276064407583647</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.2722530537054055</v>
+        <v>-0.2778705859994162</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.2884157944814447</v>
+        <v>-0.2939976322735234</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3369821348862772</v>
+        <v>-0.3425603655160643</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5209723481696003</v>
+        <v>-0.5263284494538354</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.6400152187933585</v>
+        <v>-0.6451962286333099</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6019269089416639</v>
+        <v>-0.6071672580037912</v>
       </c>
     </row>
     <row r="23">
@@ -7222,79 +7222,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3189</v>
+        <v>3193</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.03153111932488883</v>
+        <v>-0.03388193930261707</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1008571819958703</v>
+        <v>-0.1031511279559609</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3088104685934141</v>
+        <v>-0.3109671674089185</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1951995477834885</v>
+        <v>-0.1975586982760547</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.418334796912923</v>
+        <v>-0.4225368924042812</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3072195366701607</v>
+        <v>-0.3115470842077457</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.438777597503659</v>
+        <v>-0.4430085798792405</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.6060451964062281</v>
+        <v>-0.6100937044794108</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5468055759994286</v>
+        <v>-0.5509271311398649</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5536088309754703</v>
+        <v>-0.5577894342164882</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.511113702785174</v>
+        <v>-0.515327040820857</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6160935284646598</v>
+        <v>-0.6202019908502976</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.6601118478577703</v>
+        <v>-0.664262466676476</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8318926195048135</v>
+        <v>-0.8358500539407672</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.6907477716004635</v>
+        <v>-0.6949396068179752</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6714013903787333</v>
+        <v>-0.6755701343330216</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6306303509675999</v>
+        <v>-0.634864106674442</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.5919384765491174</v>
+        <v>-0.5962322409426406</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.6077545031971425</v>
+        <v>-0.6120130856063213</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6214766677106169</v>
+        <v>-0.6257051078735216</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.613689130802463</v>
+        <v>-0.6179759277445172</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.7964118106136198</v>
+        <v>-0.8004790760519498</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8792549063089083</v>
+        <v>-0.8831979669910339</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8113141115567259</v>
+        <v>-0.8153514112354401</v>
       </c>
     </row>
     <row r="24">
@@ -7304,161 +7304,161 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3212</v>
+        <v>3216</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.01106112754368382</v>
+        <v>-0.01318425452490146</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1441144837841222</v>
+        <v>-0.1460995140053711</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2680508951524629</v>
+        <v>-0.2699914316190828</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1912560442090694</v>
+        <v>-0.1933460531850599</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3844516928501207</v>
+        <v>-0.3881988902061835</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2727844145833203</v>
+        <v>-0.2766581250851203</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3779304749572248</v>
+        <v>-0.3817343180563242</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6079300301638995</v>
+        <v>-0.6114724844577424</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5488173160501191</v>
+        <v>-0.5524321892930004</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.592087945893887</v>
+        <v>-0.5957095798731018</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5479511445003737</v>
+        <v>-0.5516092748714172</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.6541845251522602</v>
+        <v>-0.6577343471631423</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7059251429244782</v>
+        <v>-0.7094976023354604</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9091106514433349</v>
+        <v>-0.912450203482841</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.7737028318008967</v>
+        <v>-0.777262186213612</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8123817737738861</v>
+        <v>-0.8158508158508155</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.8039695008291332</v>
+        <v>-0.8074614538665017</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.7663583817964934</v>
+        <v>-0.7699073244621033</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7494855115048011</v>
+        <v>-0.7530415419587513</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7307213930348269</v>
+        <v>-0.7342890481746949</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.6958053856698072</v>
+        <v>-0.6994598111791177</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.8466756886604827</v>
+        <v>-0.8501507682450224</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.895850886393724</v>
+        <v>-0.899246475725441</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.8600787980744684</v>
+        <v>-0.8635269912121615</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 13.51</t>
+          <t>X &lt; 13.5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3231</v>
+        <v>3235</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1092781359290385</v>
+        <v>-0.1110742466425307</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.182060523223285</v>
+        <v>-0.1837909366512847</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3444463389708048</v>
+        <v>-0.3460753932452079</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3030552316639543</v>
+        <v>-0.3047843842493663</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4972912519292336</v>
+        <v>-0.5004943981008836</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3852171993315707</v>
+        <v>-0.3885476116177955</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4943038736668939</v>
+        <v>-0.4975544524407809</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6630280731958962</v>
+        <v>-0.6660920074681798</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6348424799619039</v>
+        <v>-0.6379403672802866</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7440504768323208</v>
+        <v>-0.7470683690027897</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7294382548722993</v>
+        <v>-0.7324576364712669</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8367403487662415</v>
+        <v>-0.8396485266421223</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9256693740761577</v>
+        <v>-0.9285462524248871</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.036465187741243</v>
+        <v>-1.039222566324426</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.9057548362010266</v>
+        <v>-0.9087201431812701</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.9407570295368188</v>
+        <v>-0.9436408488212322</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.9332206023704899</v>
+        <v>-0.9361249024794986</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.9273791921018315</v>
+        <v>-0.930299920029718</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9711908907996687</v>
+        <v>-0.9740449110527862</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9515069551777415</v>
+        <v>-0.9543746125023205</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.8891342370746358</v>
+        <v>-0.8921180185760917</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.008693045834498</v>
+        <v>-1.011536378573702</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.056013961524776</v>
+        <v>-1.058782131675585</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.9899982081480374</v>
+        <v>-0.9928552340782062</v>
       </c>
     </row>
     <row r="26">
@@ -7468,79 +7468,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3250</v>
+        <v>3254</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1758018212717261</v>
+        <v>-0.1773133935662372</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2501282162386431</v>
+        <v>-0.2515701877280563</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4505259690119843</v>
+        <v>-0.4518108997440677</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3523931441575954</v>
+        <v>-0.3538419405487332</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4864575460205813</v>
+        <v>-0.4892741011376458</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3433438501078356</v>
+        <v>-0.3463259121821807</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4868871930527092</v>
+        <v>-0.4897423137874384</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6256295682685504</v>
+        <v>-0.6283336889268156</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6279828180762408</v>
+        <v>-0.6306833844344339</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7410575616385131</v>
+        <v>-0.7436683962025654</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7555785953410279</v>
+        <v>-0.758156858878948</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.86388932955456</v>
+        <v>-0.8663536617793497</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9281948745367075</v>
+        <v>-0.9306503853004102</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.039635836806241</v>
+        <v>-1.041970005824112</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8828458169229876</v>
+        <v>-0.8854139559979117</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.8834729053982855</v>
+        <v>-0.8860059825725131</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8153389001480917</v>
+        <v>-0.8179655326174071</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8101079904932789</v>
+        <v>-0.8127492890232304</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.8523663762656</v>
+        <v>-0.8549445280677688</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.8624001229256351</v>
+        <v>-0.8649564164111325</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.8650187305472912</v>
+        <v>-0.8676067412076165</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.015065673742654</v>
+        <v>-1.017475842344496</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.029746339376516</v>
+        <v>-1.032123515759018</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.9953216374269047</v>
+        <v>-0.9977475601560144</v>
       </c>
     </row>
     <row r="27">
@@ -7550,161 +7550,161 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3273</v>
+        <v>3277</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1547039300226345</v>
+        <v>-0.1559986285834896</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2915427474057495</v>
+        <v>-0.2926896892901212</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4702481434369403</v>
+        <v>-0.4712536339480025</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3474247699489368</v>
+        <v>-0.3486169984538705</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4223496686036867</v>
+        <v>-0.4247660935794855</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3700663345959683</v>
+        <v>-0.3725381104079872</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4876221841165247</v>
+        <v>-0.4899929014154338</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5969381127552964</v>
+        <v>-0.5991920846898608</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5989757647233844</v>
+        <v>-0.601226655718456</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.7166651989739492</v>
+        <v>-0.7188148119865758</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.6682925506066226</v>
+        <v>-0.6704882412296769</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7777724558546453</v>
+        <v>-0.7798510645602761</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8190262814753098</v>
+        <v>-0.8211147589753338</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9007440929463471</v>
+        <v>-0.9027461918689497</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.7191590386972493</v>
+        <v>-0.7214180364969351</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.7155604365433348</v>
+        <v>-0.7177943821779493</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.6183054936764805</v>
+        <v>-0.6206664818266958</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.6137875745937293</v>
+        <v>-0.6161611766241606</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.6541731427833426</v>
+        <v>-0.6564878658906181</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.6932789136405262</v>
+        <v>-0.6955377963786447</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.699641190438733</v>
+        <v>-0.7019223241546726</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.8185829455565923</v>
+        <v>-0.8207245705703485</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.8617138351162907</v>
+        <v>-0.863790009040585</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8585663670327648</v>
+        <v>-0.8606519097989676</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 15.27</t>
+          <t>X &lt; 15.26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3282</v>
+        <v>3286</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.239930785478478</v>
+        <v>-0.2410284370947053</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2562702860125583</v>
+        <v>-0.2573651451554255</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4384009569910958</v>
+        <v>-0.4393460149403836</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3784175904666682</v>
+        <v>-0.3794705434739001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3935557871516622</v>
+        <v>-0.395821643423055</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3105928393886472</v>
+        <v>-0.3129515330492367</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4602306286023321</v>
+        <v>-0.4624471531388963</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5396786848628139</v>
+        <v>-0.5418139816601695</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5415800787536114</v>
+        <v>-0.5437125109197467</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6307039541761128</v>
+        <v>-0.6327674652281985</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5816879550307803</v>
+        <v>-0.5837989893517417</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6916049948836758</v>
+        <v>-0.6935977708294701</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7357932174295954</v>
+        <v>-0.7377886208581899</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8482441752955268</v>
+        <v>-0.8501153513409534</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.6993276554499346</v>
+        <v>-0.7014131784381377</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.6941050458764337</v>
+        <v>-0.6961693437103236</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.5670722624326459</v>
+        <v>-0.5692988925839515</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5628384913989635</v>
+        <v>-0.565076924711903</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6329291013703582</v>
+        <v>-0.6350733049891062</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.6409768715763846</v>
+        <v>-0.6431036378403476</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.5879112156950654</v>
+        <v>-0.5901306163926492</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.7067011406454355</v>
+        <v>-0.708781281825118</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.7489264449753676</v>
+        <v>-0.7509432202505337</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.7459614911746186</v>
+        <v>-0.7479870706082465</v>
       </c>
     </row>
     <row r="29">
@@ -7714,161 +7714,161 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3292</v>
+        <v>3296</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1899585098231924</v>
+        <v>-0.1910128259959976</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2072450193691751</v>
+        <v>-0.2082941950849744</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3629726335002701</v>
+        <v>-0.3638992164654695</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3354960116840786</v>
+        <v>-0.336488415719927</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3214763691376135</v>
+        <v>-0.3236242552160604</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2381768364590471</v>
+        <v>-0.2404182492038984</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3594555647556703</v>
+        <v>-0.3615866725999837</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4394750511336767</v>
+        <v>-0.441523424334342</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4412148549963959</v>
+        <v>-0.4432606284144924</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5323794896837697</v>
+        <v>-0.5343512791987166</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4826519150031316</v>
+        <v>-0.4846728221047059</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6233173606054905</v>
+        <v>-0.6251821175039751</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6707555808278016</v>
+        <v>-0.6726149682931819</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7532319841495507</v>
+        <v>-0.7550029050091922</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6067339633641424</v>
+        <v>-0.6087132411104577</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.5996959089141072</v>
+        <v>-0.601658228776877</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4734260401835471</v>
+        <v>-0.47554871157908</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4694950361750472</v>
+        <v>-0.4716286445355991</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5386892308645983</v>
+        <v>-0.5407306516252177</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5461165048543677</v>
+        <v>-0.5481418620275207</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4948316684820213</v>
+        <v>-0.4969452061810031</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6134632970631557</v>
+        <v>-0.6154378266012017</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6546976379701519</v>
+        <v>-0.6566110753195247</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6519437516431807</v>
+        <v>-0.6538653479720509</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 16.44</t>
+          <t>X &lt; 16.43</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3296</v>
+        <v>3300</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1941575612193134</v>
+        <v>-0.1951655004316706</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1816899282311653</v>
+        <v>-0.1827280659058061</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3691059162871042</v>
+        <v>-0.3699814130861867</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4028389485791237</v>
+        <v>-0.4037054139904512</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3892972851117378</v>
+        <v>-0.3912816980573766</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3058928521901692</v>
+        <v>-0.3079709954576657</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3977946005987079</v>
+        <v>-0.3997968423654257</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4478722028198234</v>
+        <v>-0.4498274749628237</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4797646414382513</v>
+        <v>-0.481680940432625</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.5717659023766188</v>
+        <v>-0.5736061477687571</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4915580797790753</v>
+        <v>-0.4934845062884818</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.632393603977647</v>
+        <v>-0.6341634188726388</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6811373241202432</v>
+        <v>-0.6828985644868624</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7637849020863143</v>
+        <v>-0.7654572103735973</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5880076891548356</v>
+        <v>-0.5899225135801203</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6105184197366142</v>
+        <v>-0.6123813711479897</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.5148426402468544</v>
+        <v>-0.5168285003847473</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5413407925922229</v>
+        <v>-0.5433005455228468</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6102110176743523</v>
+        <v>-0.6120793145939913</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6174242424242493</v>
+        <v>-0.6192769416371675</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.5668818276096559</v>
+        <v>-0.56882085690021</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6551621353500821</v>
+        <v>-0.6569989070644056</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.6656951298235896</v>
+        <v>-0.6675084082018969</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6327002782036004</v>
+        <v>-0.6345581988105309</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3302</v>
+        <v>3306</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1703620072545533</v>
+        <v>-0.1713367499594511</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.09834625854193746</v>
+        <v>-0.09942198870485441</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2879982872799332</v>
+        <v>-0.2889059605122029</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3229351889447329</v>
+        <v>-0.3238308948676547</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3100538581877785</v>
+        <v>-0.3120115129531555</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2565585202940852</v>
+        <v>-0.2585740946235759</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3798059908990652</v>
+        <v>-0.381706393568976</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.430291330808565</v>
+        <v>-0.4321437072091641</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4921934070833629</v>
+        <v>-0.4939707566440106</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.555275317498392</v>
+        <v>-0.5570098894706277</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4445452025171477</v>
+        <v>-0.4464030945518402</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5554418424062391</v>
+        <v>-0.5571788550966517</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6061105650325374</v>
+        <v>-0.6078342831841113</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6889867748341558</v>
+        <v>-0.6906209318157295</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.5146995808046952</v>
+        <v>-0.516572579422764</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.5360687002717981</v>
+        <v>-0.5378925037947297</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4407870480477811</v>
+        <v>-0.4427327302784292</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4674051689512879</v>
+        <v>-0.4693243757130219</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5659748509575948</v>
+        <v>-0.5677672954728408</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6030701754385888</v>
+        <v>-0.6048112751923966</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5838585027952305</v>
+        <v>-0.5856466827037821</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.672121566335484</v>
+        <v>-0.6738074515177033</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6215904101778094</v>
+        <v>-0.6233272046245659</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.5887801474208416</v>
+        <v>-0.590561058624651</v>
       </c>
     </row>
     <row r="32">
@@ -7960,161 +7960,161 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1563823798939126</v>
+        <v>-0.1573636299484846</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1145600782898626</v>
+        <v>-0.1156058883513253</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2745088164908864</v>
+        <v>-0.2754218069666194</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3096459489533743</v>
+        <v>-0.3105464843132211</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2968744501879286</v>
+        <v>-0.2988276211732028</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2433348940819187</v>
+        <v>-0.24534607873548</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3667740499384777</v>
+        <v>-0.3686695895849326</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4173241796535336</v>
+        <v>-0.4191715247499701</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4791911789866603</v>
+        <v>-0.4809635692438832</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5424834455283971</v>
+        <v>-0.544212539274902</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4317001275845058</v>
+        <v>-0.4335526569472492</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5426436308789278</v>
+        <v>-0.5443751554267777</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.593632517743103</v>
+        <v>-0.595349963544102</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.676546760310778</v>
+        <v>-0.678174540396455</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5025073858521267</v>
+        <v>-0.5043733970681856</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5236866468583301</v>
+        <v>-0.5255039078568444</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.4284705515204124</v>
+        <v>-0.4304095200721534</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4551086327740705</v>
+        <v>-0.4570210646459429</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.5535794667207981</v>
+        <v>-0.5553653619384491</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5906032657998139</v>
+        <v>-0.5923379759910645</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5715579407583888</v>
+        <v>-0.5733393162702072</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.6598135584378397</v>
+        <v>-0.661492644112883</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.6092108066330155</v>
+        <v>-0.6109409615265804</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5764297209873064</v>
+        <v>-0.5782039090120321</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 18.2</t>
+          <t>X &lt; 18.19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3307</v>
+        <v>3311</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1606078922372873</v>
+        <v>-0.1615429742597954</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1192398461986741</v>
+        <v>-0.1202383732279273</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2506800767889459</v>
+        <v>-0.2515781348824078</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2565688762136418</v>
+        <v>-0.2574886043924067</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2442360689883074</v>
+        <v>-0.2461712365865694</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.190519929842047</v>
+        <v>-0.1925134865912668</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3147246972932365</v>
+        <v>-0.3166007198265319</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3655336198793719</v>
+        <v>-0.3673607761723972</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4272605461188093</v>
+        <v>-0.4290130348412262</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4913929939144026</v>
+        <v>-0.4931001150345224</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3803972078234352</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4915279056586641</v>
+        <v>-0.493237417834635</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5437955428547525</v>
+        <v>-0.545487846450861</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6268617098417764</v>
+        <v>-0.6284639304038748</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4538121415964937</v>
+        <v>-0.4556501567002016</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4742331363925061</v>
+        <v>-0.4760241766870266</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3792788955046476</v>
+        <v>-0.3811909602006622</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4059967200976757</v>
+        <v>-0.4078820037425288</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5040727811276824</v>
+        <v>-0.5058324283650251</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5408109332527857</v>
+        <v>-0.5425200328762685</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.5224300162487054</v>
+        <v>-0.524184125529473</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.6106559179497211</v>
+        <v>-0.6123077568262758</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.5597672389081296</v>
+        <v>-0.5614707852886198</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5271027078835075</v>
+        <v>-0.5288499535674021</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3313</v>
+        <v>3317</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2268791995157855</v>
+        <v>-0.2276734607373569</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1862084646230073</v>
+        <v>-0.1870644628449725</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2900291781225306</v>
+        <v>-0.2908149200698205</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2972041390185538</v>
+        <v>-0.2980084276633619</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2855634838989474</v>
+        <v>-0.2873275007644196</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2316193761461989</v>
+        <v>-0.2334422562106511</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3570052449889474</v>
+        <v>-0.3587076830492748</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4082373441702387</v>
+        <v>-0.4098898261919217</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.469790966857019</v>
+        <v>-0.4713691233981194</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5352160952052358</v>
+        <v>-0.5367457045411754</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4239387824200804</v>
+        <v>-0.4255928899513464</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5353856669646078</v>
+        <v>-0.5369174338747484</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5896019200599341</v>
+        <v>-0.5911117176128116</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6729315689131923</v>
+        <v>-0.6743505730194244</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.5013985433237664</v>
+        <v>-0.5030496162340725</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.5508332990758902</v>
+        <v>-0.5524037366142664</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4261955906497406</v>
+        <v>-0.4279221692496549</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4530690374916801</v>
+        <v>-0.4547683825690498</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.5505911132816692</v>
+        <v>-0.552166078577919</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5869384986433488</v>
+        <v>-0.5884637803982073</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.5695876225082017</v>
+        <v>-0.5711553538343637</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.6578055400553424</v>
+        <v>-0.6592709421088685</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6065257417311614</v>
+        <v>-0.6080437164240209</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5740720147284435</v>
+        <v>-0.5756331022007757</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 19.37</t>
+          <t>X &lt; 19.36</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3327</v>
+        <v>3331</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1517333460492978</v>
+        <v>-0.1524750204087155</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1424710022105842</v>
+        <v>-0.1432350063239838</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2518647679938084</v>
+        <v>-0.2525451087841333</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2022290006322862</v>
+        <v>-0.2029920861940369</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1622505604031943</v>
+        <v>-0.1638799901162216</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1077120131894347</v>
+        <v>-0.1094015593300739</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2357715711236992</v>
+        <v>-0.2373341083018516</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2879193992834104</v>
+        <v>-0.2894296176374453</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3490052501051935</v>
+        <v>-0.3504420914974915</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4472938798712889</v>
+        <v>-0.448639186929519</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.365246785775966</v>
+        <v>-0.3666823047249679</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4773790151148631</v>
+        <v>-0.4786903776487037</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5061087022616135</v>
+        <v>-0.5074230581274719</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5899924077683565</v>
+        <v>-0.5912144641581705</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.421919682102093</v>
+        <v>-0.423365328765712</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4386400731956073</v>
+        <v>-0.4400473740096373</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3450491693315954</v>
+        <v>-0.346573962875766</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3422233641928187</v>
+        <v>-0.3437559792100373</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.4383943358365201</v>
+        <v>-0.4398056358063087</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4737691383968752</v>
+        <v>-0.4751329119570968</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4587409495384946</v>
+        <v>-0.4601414120444005</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5468739987348883</v>
+        <v>-0.548172155219028</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4946206827738209</v>
+        <v>-0.4959735719105112</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4625894462636921</v>
+        <v>-0.4639842515929402</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_24.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_24.xlsx
@@ -618,83 +618,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 2.663</t>
+          <t>X ≈ 2.664</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.7370119879005941</v>
+        <v>-2.325902294159143</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.069662585533663</v>
+        <v>-0.1856521865659104</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.058553767591675</v>
+        <v>0.9527337271325322</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.36829692697804</v>
+        <v>-2.816045660747406</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.305651774434764</v>
+        <v>-7.863206238231825</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.402080740848895</v>
+        <v>-8.505573184770547</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.009722515199364</v>
+        <v>-8.503101020856029</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.567240122390594</v>
+        <v>-8.012687101577072</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.412906629106175</v>
+        <v>-10.27644942763653</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.463873397188983</v>
+        <v>-11.07241002782313</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.35882835737069</v>
+        <v>-13.19487587268239</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.752208265781995</v>
+        <v>-11.0831923070028</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.98533338169478</v>
+        <v>-8.210880047370679</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-5.040710970102147</v>
+        <v>-5.27080222619059</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-2.808368426337132</v>
+        <v>-1.964019487893665</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-4.385022998492637</v>
+        <v>-3.001072962125484</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-7.412306258314537</v>
+        <v>-5.500734775736724</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-8.966038189357228</v>
+        <v>-5.635450230413994</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-10.92396623130399</v>
+        <v>-7.02071782704698</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-11.46469912353386</v>
+        <v>-7.607979375696537</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-11.28649358188908</v>
+        <v>-6.578919112434242</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-9.193417982108329</v>
+        <v>-5.856878711226109</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.473217247687842</v>
+        <v>-4.015861915483967</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-6.102278883922686</v>
+        <v>-4.179530298637282</v>
       </c>
     </row>
     <row r="7">
@@ -704,1309 +704,1309 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.577934615079201</v>
+        <v>-6.584676284591218</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.911951961594625</v>
+        <v>-7.341758189618467</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.934060701458939</v>
+        <v>-3.470711846152625</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.641991584128888</v>
+        <v>-4.059408724673368</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.46760492717388</v>
+        <v>-4.333854819366231</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.791216130757292</v>
+        <v>-3.154853415590601</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.559705356561444</v>
+        <v>-3.433836909997616</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.375226571160923</v>
+        <v>-1.17424496469917</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.81152747066978</v>
+        <v>-2.072554766878213</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-4.074606444205692</v>
+        <v>-2.865816943539144</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.802707659386698</v>
+        <v>-2.082000514155581</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.575103146906748</v>
+        <v>-1.845018983958468</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.682201925026078</v>
+        <v>-3.983786601439483</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-9.372077389131235</v>
+        <v>-6.801904055490532</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-12.0062051524858</v>
+        <v>-9.540727302286946</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-11.41748713274159</v>
+        <v>-9.498410223357979</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-10.56695796545155</v>
+        <v>-10.1195620244814</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-7.21691610668131</v>
+        <v>-8.198197084035648</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.521294724712014</v>
+        <v>-5.413825289810468</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.336887707525307</v>
+        <v>-6.231376365755892</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-3.902774499224087</v>
+        <v>-4.2258749148099</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-4.969696706510852</v>
+        <v>-5.333076717736219</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-7.171698849658753</v>
+        <v>-6.637518445215349</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-6.260120755066048</v>
+        <v>-5.771282875956871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 3.835</t>
+          <t>X ≈ 3.834</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.783502889584376</v>
+        <v>6.180772103195409</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.205260164010134</v>
+        <v>6.700619352745008</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.154498658234317</v>
+        <v>5.836312330993998</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.45824076600249</v>
+        <v>7.914354963517042</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.871814812351985</v>
+        <v>5.36115056791035</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5428348442463431</v>
+        <v>1.330485243012809</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6002930065616141</v>
+        <v>-0.2207348494573509</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.890305161945136</v>
+        <v>-3.572197921796018</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.21223819071384</v>
+        <v>-0.7776370696701704</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.60452883611913</v>
+        <v>-1.569980229255016</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.46306819665633</v>
+        <v>-2.44346144590515</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.8562134611523646</v>
+        <v>-0.8127016983837407</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8429856661466246</v>
+        <v>-0.3965705250169265</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.4408294139606</v>
+        <v>-1.40765036423285</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.097656459422915</v>
+        <v>-2.088496738404743</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.261641273551447</v>
+        <v>-2.294177495213702</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.640654616889279</v>
+        <v>-0.8701565337263943</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.01460733563831</v>
+        <v>-3.298012349665868</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.557357772692036</v>
+        <v>-3.850682488201358</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-7.777111667103952</v>
+        <v>-7.08173909914953</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.565775067204882</v>
+        <v>-6.886340734536468</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.644832999127992</v>
+        <v>-6.964496642434248</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-7.373685583801368</v>
+        <v>-6.723966941807788</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-6.695164259416686</v>
+        <v>-6.122825317794366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 4.421</t>
+          <t>X ≈ 4.419</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3233465791845163</v>
+        <v>0.3909273786103213</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.351775650642828</v>
+        <v>2.490511561731779</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.680027310873378</v>
+        <v>3.979185824566912</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.548930058011628</v>
+        <v>5.346283595875789</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.221321287107529</v>
+        <v>5.078027371244104</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.350425718436171</v>
+        <v>8.755606439288066</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.376446904740753</v>
+        <v>9.143715701874129</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10.47036934579219</v>
+        <v>11.19283874937365</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>10.12113156620829</v>
+        <v>10.93259328428751</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>12.51386470435109</v>
+        <v>13.27783967904773</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>13.58171065683511</v>
+        <v>14.33786352360774</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>13.70339717538057</v>
+        <v>14.45874482775412</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>11.40594297986485</v>
+        <v>12.1787063025612</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>11.19071202902283</v>
+        <v>11.93654935686937</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>13.70234455871293</v>
+        <v>14.39964802825572</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>13.50859879485796</v>
+        <v>14.179290306545</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>12.58853218495742</v>
+        <v>12.90271671969598</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>12.48829758786371</v>
+        <v>12.77449367179646</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>12.31200278008917</v>
+        <v>12.59985638526044</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>13.69171778185</v>
+        <v>13.99789649466608</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>15.92870540949666</v>
+        <v>16.18819955125301</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>16.65147340328075</v>
+        <v>16.90535256497933</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>15.74174474818817</v>
+        <v>15.9740751818289</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>13.68723112297878</v>
+        <v>13.84881615805563</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 5.007</t>
+          <t>X ≈ 5.005</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.580491997364014</v>
+        <v>4.805153965312634</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.854863936531174</v>
+        <v>7.209459978526844</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.920441079704077</v>
+        <v>7.479495487840417</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.961606296974914</v>
+        <v>7.651517033186224</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.991587718201117</v>
+        <v>10.41390424014654</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.689423534690931</v>
+        <v>8.680065996340652</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.794356363129062</v>
+        <v>10.1693098741958</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>10.64274150211627</v>
+        <v>11.00842324685446</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11.80936392158877</v>
+        <v>11.8987807851255</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>11.79330430966272</v>
+        <v>12.25033987630529</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>13.94055200524485</v>
+        <v>14.42458363465198</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>14.41637812191573</v>
+        <v>14.91406318502433</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>13.30759880465681</v>
+        <v>13.81323202638493</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>13.84308129992881</v>
+        <v>13.95317452443478</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>12.06981752988735</v>
+        <v>12.13856224584281</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>11.16907850700461</v>
+        <v>11.56213837255167</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>10.6661010844706</v>
+        <v>11.08327890450931</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>9.441311249780867</v>
+        <v>9.813308022625165</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>9.285564001735331</v>
+        <v>9.650406467334449</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>9.100886822439961</v>
+        <v>9.48765906064358</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>7.435909844168471</v>
+        <v>7.780616797808207</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>5.485067652444492</v>
+        <v>5.801758919743143</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.385924379005232</v>
+        <v>5.666052797043314</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>5.688066544866849</v>
+        <v>5.887645273881809</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 5.593</t>
+          <t>X ≈ 5.591</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.18359687170728</v>
+        <v>-1.299448673653245</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.782849844814351</v>
+        <v>3.87375784931465</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.402445914214155</v>
+        <v>3.15125996573304</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.9631450550543761</v>
+        <v>1.700701467014262</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.411101844058649</v>
+        <v>2.823910391503574</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.884231519090868</v>
+        <v>2.633487917146226</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.969587272829514</v>
+        <v>4.478342379430245</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.048254432024777</v>
+        <v>4.177333804909949</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.297162475360508</v>
+        <v>2.90863684999281</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9942514183923947</v>
+        <v>1.067234016550856</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3987798316129556</v>
+        <v>0.2897012680081019</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5987789187693195</v>
+        <v>-0.686362906190773</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6682262503453344</v>
+        <v>-0.545079238716184</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3941132490318822</v>
+        <v>0.6110209944367497</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.3009477668894931</v>
+        <v>0.2835103492438904</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7507163979907503</v>
+        <v>0.1421582918693431</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.98797063810715</v>
+        <v>2.14493511345961</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.377667499637703</v>
+        <v>1.312123282980714</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.234369804690076</v>
+        <v>1.175611915479116</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.341657593312419</v>
+        <v>0.3364869323123543</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.4398027339278698</v>
+        <v>-0.5819549961256456</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.364418959435767</v>
+        <v>-0.6572755319222736</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.2782001498267448</v>
+        <v>-0.7660510701245542</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.8807019467592525</v>
+        <v>-1.985164101454259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 6.179</t>
+          <t>X ≈ 6.175</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2478683715226424</v>
+        <v>0.98910811320183</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.9491897089198673</v>
+        <v>-1.763432748930029</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.091440831832479</v>
+        <v>-0.9395951361001877</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.303869823491297</v>
+        <v>-6.221887639738753</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.337545088440329</v>
+        <v>-5.244096275060478</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.151669543302127</v>
+        <v>-5.51248597961532</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.49625939736837</v>
+        <v>-5.485333378172065</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.787682919394051</v>
+        <v>-3.873620427665131</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.193877715415731</v>
+        <v>-2.662479909094174</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.534320909832083</v>
+        <v>-2.405201180025756</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.44393078691963</v>
+        <v>-4.009539233265073</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.914964137580249</v>
+        <v>-4.476854075343617</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.786042171327139</v>
+        <v>-6.056996809090329</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.005853689491353</v>
+        <v>-6.068434135025512</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-6.098338775495598</v>
+        <v>-6.515819221699303</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-7.69086909505689</v>
+        <v>-8.246611098038279</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-10.00971191052359</v>
+        <v>-10.22399357925237</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-9.676046648708343</v>
+        <v>-10.10869143833493</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-8.153964595334031</v>
+        <v>-8.626049145181021</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-6.658527567518746</v>
+        <v>-7.142326889095557</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-7.642014864625622</v>
+        <v>-7.715558314771279</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-9.912410666356209</v>
+        <v>-10.08727920901895</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-9.643763865463285</v>
+        <v>-9.42435847520418</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-7.971081324807535</v>
+        <v>-8.315700511403143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 6.765</t>
+          <t>X ≈ 6.761</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.522240503807495</v>
+        <v>-1.747286918281901</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.727441701861395</v>
+        <v>-3.372924386980657</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.625831334646747</v>
+        <v>-5.574186705081196</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.132784954569573</v>
+        <v>-0.6225903148356906</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.066266674464465</v>
+        <v>0.2790895866316916</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.8790579878664531</v>
+        <v>0.689551547563525</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.180548588573494</v>
+        <v>0.351745451798223</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5235562925115502</v>
+        <v>0.9743936703145266</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4529002433157174</v>
+        <v>2.033507027754077</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.086540368940881</v>
+        <v>2.154899994134119</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.827967494607918</v>
+        <v>2.892365654033142</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.887930603904678</v>
+        <v>4.471644180577783</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.51402142879703</v>
+        <v>7.04605515300964</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>8.164990742297391</v>
+        <v>8.650065786761949</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>7.97819950556373</v>
+        <v>7.95634089021906</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7.636445139082056</v>
+        <v>8.054583735242318</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.504168710421823</v>
+        <v>7.481856892392166</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>7.868570585325273</v>
+        <v>8.271479348992671</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>7.152330072273223</v>
+        <v>7.840333478414124</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.875385667701053</v>
+        <v>7.869991697318113</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.806521728248974</v>
+        <v>8.047172697658155</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.735385244853724</v>
+        <v>7.972761122646993</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>7.013467492730953</v>
+        <v>7.755603497904382</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.471715808872041</v>
+        <v>7.597213887409232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 7.351</t>
+          <t>X ≈ 7.346</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.202107105941863</v>
+        <v>1.452915008097378</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.253669728649463</v>
+        <v>-2.718550253725027</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.05795632896548142</v>
+        <v>-0.9256209531611859</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.02245638645980108</v>
+        <v>-1.524882019341803</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.809596061060795</v>
+        <v>-4.421670640247783</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3927638166362115</v>
+        <v>-2.518012143419959</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.558281366962305</v>
+        <v>-0.69815096993743</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.172183088849479</v>
+        <v>-2.313115081468268</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.602605242848021</v>
+        <v>-4.365734423916088</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.390840904909858</v>
+        <v>-3.859744262947601</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.62707403290684</v>
+        <v>-3.149684881073732</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.035517327569146</v>
+        <v>-0.3689267043120452</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.9016813520044735</v>
+        <v>-0.1903507497905039</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.133165225104449</v>
+        <v>2.179216235896817</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.460321418473967</v>
+        <v>2.797960365637529</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.58310874299152</v>
+        <v>2.486473511323425</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.902993309511572</v>
+        <v>4.561998207168237</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>6.761317863883662</v>
+        <v>6.608519209576556</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.018932605976083</v>
+        <v>5.078542835016805</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.701285904117114</v>
+        <v>5.293129280075789</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>6.147405097538659</v>
+        <v>5.594474645861624</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>6.07727638640916</v>
+        <v>5.950277623803437</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.879326322419644</v>
+        <v>5.147476304314871</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.29916325215229</v>
+        <v>6.559334330183681</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 7.937</t>
+          <t>X ≈ 7.931</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.07650253752765224</v>
+        <v>-0.2368416041436134</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.321020058007818</v>
+        <v>-2.54886414232687</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.758067819760392</v>
+        <v>-3.390335103722585</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.644296614137659</v>
+        <v>-3.569514162034928</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.92733140888042</v>
+        <v>-2.605402880646665</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.504846600282029</v>
+        <v>-0.7955767126650599</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.862460480668247</v>
+        <v>-1.177435584401913</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.551924345626631</v>
+        <v>-2.308802308802363</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.335584046950068</v>
+        <v>-3.007319680109902</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.278509094564669</v>
+        <v>-2.97692489433755</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.481211123531054</v>
+        <v>-5.184028722708469</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-7.826350458844423</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.224902698876221</v>
+        <v>-4.922610232647017</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.209141931408119</v>
+        <v>-3.931174872592571</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-3.211267036386033</v>
+        <v>-2.960436692494106</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.921868083838092</v>
+        <v>2.146321871780096</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.376258186184074</v>
+        <v>1.629218319559222</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.510018488162679</v>
+        <v>2.736003635885275</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.142770817223216</v>
+        <v>3.363689003526815</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.920468140401823</v>
+        <v>3.165052308090033</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.624245036228878</v>
+        <v>3.837277228196854</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.796570854305706</v>
+        <v>5.001784127729174</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.490653999859703</v>
+        <v>5.65864175350341</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.58988540737581</v>
+        <v>4.670056478222214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 8.523</t>
+          <t>X ≈ 8.517</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.028568705649597</v>
+        <v>-4.716335648298447</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.827613186650325</v>
+        <v>-5.43172605207738</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.855213474512155</v>
+        <v>-5.27796944974363</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.409053372576615</v>
+        <v>-0.7060523997255643</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.893117527599905</v>
+        <v>-6.145929788651117</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-8.116570102671744</v>
+        <v>-7.397446886878484</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.949820509789205</v>
+        <v>-7.723045331036033</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-6.820323303098604</v>
+        <v>-6.150031502144131</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.119145302517978</v>
+        <v>-8.369520432835714</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-9.88596323167193</v>
+        <v>-9.16557192805503</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-8.204872465497736</v>
+        <v>-7.484886209225337</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-10.82731868743671</v>
+        <v>-10.1088860040722</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-11.00229709348044</v>
+        <v>-10.28481098537274</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-12.63176214880205</v>
+        <v>-11.94149575103114</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-13.28380769950012</v>
+        <v>-12.62365013291625</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-14.56952744082843</v>
+        <v>-13.94028038639706</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-14.23307914827237</v>
+        <v>-13.57467723004695</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-17.14859446296114</v>
+        <v>-16.52446274365936</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-17.88845676071823</v>
+        <v>-17.24896765266367</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-16.31139338805654</v>
+        <v>-15.62593050337944</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-17.34011642090881</v>
+        <v>-16.66285857283529</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-15.55057477166291</v>
+        <v>-14.86008682248999</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-14.35047309789448</v>
+        <v>-13.67748520106139</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-14.91414653500259</v>
+        <v>-14.30910776342601</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 9.109</t>
+          <t>X ≈ 9.101</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1806909270665429</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.442360210783825</v>
+        <v>-1.224430999711899</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.250941126061505</v>
+        <v>-2.479125101603479</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.68748338522154</v>
+        <v>-1.789476018360347</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.13671300578666</v>
+        <v>-0.1419572353828329</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3027731931598012</v>
+        <v>0.656002011640922</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.352887186610516</v>
+        <v>-1.42113128264311</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.632852180641223</v>
+        <v>-1.726051726051772</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.327228083387084</v>
+        <v>-0.3160715343163432</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.075103697784691</v>
+        <v>2.093005175592559</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.349163339946614</v>
+        <v>1.724214549171251</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.066906837943392</v>
+        <v>2.088658235725561</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.746676812771121</v>
+        <v>4.178894323402993</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9762815143142944</v>
+        <v>2.007583338892957</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.216973913659338</v>
+        <v>2.607480239059193</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.9072644908438647</v>
+        <v>1.245707334801928</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.506571504971518</v>
+        <v>-0.1402243589743577</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.0180259249605399</v>
+        <v>1.008942817915397</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.506869100698282</v>
+        <v>2.505456327112412</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.8643193540533929</v>
+        <v>0.1559402080687988</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.062632553250722</v>
+        <v>-1.052529934337507</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.387271835796362</v>
+        <v>-1.768718097318576</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.279128350200132</v>
+        <v>-4.089186176142768</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.033159597411974</v>
+        <v>-2.969273888380876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 9.695</t>
+          <t>X ≈ 9.686</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>144</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.1083382889792261</v>
+        <v>0.6240399385560309</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.215236303272036</v>
+        <v>3.850355325074418</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.764998290409068</v>
+        <v>2.595661223182837</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3307351360065951</v>
+        <v>0.6143701354856503</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7062372410074005</v>
+        <v>0.3388119953863935</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5009426091622373</v>
+        <v>0.4957456013844777</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.28205551592648</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.257766146081963</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.629558442153993</v>
+        <v>2.995894277649512</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.538868246730132</v>
+        <v>2.894287226874575</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>4.201816777780984</v>
+        <v>5.249855574812202</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.833624559083688</v>
+        <v>2.889940287007654</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.46074760138363</v>
+        <v>4.552825947334618</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.844670354132184</v>
+        <v>2.22125855256818</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.2206902780850086</v>
+        <v>0.8446597262386391</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.3828608667318747</v>
+        <v>2.100408189502744</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.9311692103669529</v>
+        <v>1.996527777777736</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.897442876047243</v>
+        <v>3.252532561505063</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.152892599144607</v>
+        <v>2.078105899761908</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.542117347716996</v>
+        <v>5.070470122598671</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>6.123958434652913</v>
+        <v>5.197470065662429</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>5.353668028799412</v>
+        <v>5.122307543707144</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.544809407948058</v>
+        <v>2.588164251207736</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.08008826583589</v>
+        <v>2.426025256918273</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 10.28</t>
+          <t>X ≈ 10.27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4132069406220893</v>
+        <v>0.005760368663629833</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.456808520650611</v>
+        <v>2.340498694250044</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.694465147295332</v>
+        <v>2.376127173003667</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.657186803528269</v>
+        <v>2.428886264518027</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9700449796296482</v>
+        <v>0.8630055437734896</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4813354900513502</v>
+        <v>0.3747778594489617</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.06073815751239</v>
+        <v>0.8700184278614387</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5688246385920763</v>
+        <v>-0.7252245961923123</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.499689570349695</v>
+        <v>1.983349474782045</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7267738943131619</v>
+        <v>1.187297979562743</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.676509212150719</v>
+        <v>2.104694284489703</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.776138187081102</v>
+        <v>4.408757491308648</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.97730044454935</v>
+        <v>3.293865373857919</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.05351886540011463</v>
+        <v>0.4649861511345037</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4.125105297549233</v>
+        <v>4.298960801507533</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>3.368140868140891</v>
+        <v>2.924780949359473</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>6.612602109541768</v>
+        <v>6.691868279569924</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>7.859112757071927</v>
+        <v>7.849306755053433</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>9.426355489347621</v>
+        <v>9.354091562844388</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>10.28887697499133</v>
+        <v>10.21383929822598</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>11.09768215837664</v>
+        <v>10.93671737749038</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>9.670484845616151</v>
+        <v>8.926070984567353</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>11.29631090944962</v>
+        <v>11.10518934081349</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>9.193451629199309</v>
+        <v>8.362405185233705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 10.87</t>
+          <t>X ≈ 10.86</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6287989206608486</v>
+        <v>-0.4562069750242088</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.650882112314612</v>
+        <v>3.001589892975616</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.417682340392076</v>
+        <v>2.981463692318613</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.114366875166134</v>
+        <v>6.092765197214156</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9.802672788161075</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11.19445825136692</v>
+        <v>12.14698016928568</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8.012871013259662</v>
+        <v>8.882762354583861</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.325021014289725</v>
+        <v>6.108706108706102</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.366508196204428</v>
+        <v>7.47120291962478</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.593592520167903</v>
+        <v>5.440583523170872</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.867652162329861</v>
+        <v>5.712818537775206</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.179264204664996</v>
+        <v>2.967100780834777</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.465740692025747</v>
+        <v>4.321344465853137</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.244661815579121</v>
+        <v>4.073110404419999</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>2.586518517998627</v>
+        <v>3.390956022534972</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.4335523913837491</v>
+        <v>0.2485563376508964</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-6.591565913903352</v>
+        <v>-6.028163580246911</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-4.286768063507637</v>
+        <v>-3.691911882939344</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-5.275695959691781</v>
+        <v>-4.712017557028176</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-9.908127258157492</v>
+        <v>-9.435702716907464</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-11.65549270323195</v>
+        <v>-11.23771511952277</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-14.14097721885792</v>
+        <v>-13.78201344394715</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-10.2520446750506</v>
+        <v>-9.834675254965141</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-5.508599819840143</v>
+        <v>-5.058542644316333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 11.46</t>
+          <t>X ≈ 11.45</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.76365413097588</v>
+        <v>-2.695169100991897</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-10.11597478897477</v>
+        <v>-9.720736953644931</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-16.81715173274265</v>
+        <v>-16.06017681824837</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-17.53010575218534</v>
+        <v>-18.34749427129402</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.093966400171212</v>
+        <v>-8.453560885969537</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.152614249161594</v>
+        <v>-6.601712025734123</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-9.678948897964183</v>
+        <v>-9.091709292204172</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-6.448388412892648</v>
+        <v>-6.00679922713816</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.406901230977986</v>
+        <v>-7.573785571691396</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.425430942102146</v>
+        <v>-4.980006558436152</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.905757264852554</v>
+        <v>-6.402686798069112</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-14.20205052794968</v>
+        <v>-13.45892976948956</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-11.81644066498119</v>
+        <v>-11.18399137846571</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-10.28313357651555</v>
+        <v>-9.737310185661578</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.923733014447023</v>
+        <v>-3.639803550597485</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.933811802232903</v>
+        <v>2.006246230934096</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>8.817438524904503</v>
+        <v>8.68202683615818</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>5.203825891258759</v>
+        <v>5.159312222522004</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.665331307270804</v>
+        <v>3.678859195430498</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>5.606563082151112</v>
+        <v>5.588360894726762</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>5.064016914185025</v>
+        <v>5.020916393345985</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>8.496942882600486</v>
+        <v>8.335584379865232</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>5.262645665258077</v>
+        <v>5.189388356669177</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>5.186813412034802</v>
+        <v>5.027249362379713</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 12.04</t>
+          <t>X ≈ 12.03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.359152886568033</v>
+        <v>4.352110113994669</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>11.02437608821822</v>
+        <v>12.00094012039602</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.08635703918722</v>
+        <v>2.851509176399219</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.373403019744558</v>
+        <v>2.259106977591074</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-13.77542126670544</v>
+        <v>-13.64899124072082</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-19.54736995059576</v>
+        <v>-19.70723114769035</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-24.82558139534891</v>
+        <v>-25.27530948583588</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-32.28409421343417</v>
+        <v>-33.04211741825692</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-33.05700988947062</v>
+        <v>-33.8381689134763</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-32.78295024730873</v>
+        <v>-33.56593389887193</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-28.06169965075669</v>
+        <v>-28.5793579586065</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-34.18486171761288</v>
+        <v>-34.95740797079411</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-31.9059405940594</v>
+        <v>-32.57406308485872</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-32.56408389163995</v>
+        <v>-33.25621746674378</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-29.46969696969704</v>
+        <v>-30.06333450055577</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-29.60361410667444</v>
+        <v>-30.1672149122807</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-29.70845481049555</v>
+        <v>-30.3000990174423</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-26.99256342957123</v>
+        <v>-27.45405784292811</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-26.8057176196032</v>
+        <v>-27.23947139786913</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-22.34826378756923</v>
+        <v>-22.54375800451295</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-22.42410974897833</v>
+        <v>-22.61892052646823</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-19.64963503649635</v>
+        <v>-19.74370709382158</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-17.2254672897197</v>
+        <v>-17.27426714074262</v>
       </c>
     </row>
     <row r="23">
@@ -2019,158 +2019,158 @@
         <v>23</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.880892017002878</v>
+        <v>2.979112402324184</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-10.31027269424919</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.455922256578539</v>
+        <v>1.478511464728733</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.395142150179268</v>
+        <v>0.8861092659205738</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.407177764588525</v>
+        <v>4.958377212777705</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.594143950685954</v>
+        <v>5.115310818775839</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8.170021353751999</v>
+        <v>8.668054893499516</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>4.015308363134451</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7623550829992851</v>
+        <v>4.143237272818489</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.883096845992362</v>
+        <v>-1.000640309357308</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.609037203830368</v>
+        <v>-0.7284052947530313</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.887786607278365</v>
+        <v>-1.004987249224143</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.010948674134553</v>
+        <v>-2.119879366675043</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-11.57985363753754</v>
+        <v>-6.715939515064676</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-12.23799693511822</v>
+        <v>-7.398093896949661</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-20.33926218708827</v>
+        <v>-15.53244205204305</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-24.82100541102227</v>
+        <v>-19.98414855072458</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-24.92584611484357</v>
+        <v>-20.11703265588624</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-20.36212864696279</v>
+        <v>-15.55474434178389</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-15.82745675003812</v>
+        <v>-10.99233180976844</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-12.0221768310475</v>
+        <v>-7.211950224192655</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-7.750196705500144</v>
+        <v>-2.939286659191545</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.127895906061816</v>
+        <v>1.652173913043491</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-7.551554246241487</v>
+        <v>-2.857791168202503</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 13.21</t>
+          <t>X ≈ 13.2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-16.79874185027415</v>
+        <v>-13.5426267281106</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.607202859150128</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.30837980291804</v>
+        <v>-10.04322766570612</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-19.28449171709769</v>
+        <v>-20.63562986451434</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-19.6202821896449</v>
+        <v>-20.91118800461361</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-19.43331600354752</v>
+        <v>-20.75425439861545</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-20.20526468743779</v>
+        <v>-21.54933641084817</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-9.95716034271733</v>
+        <v>-16.85425685425693</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15.1788310555394</v>
+        <v>-21.72632794457268</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-26.47806252104949</v>
+        <v>-32.52237943979209</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-31.46716077362449</v>
+        <v>-37.25014442518783</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-31.74591017707256</v>
+        <v>-37.52672637965898</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-38.13223013866545</v>
+        <v>-43.64161849710982</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-22.56383533090166</v>
+        <v>-28.88985255854293</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-23.22197862848207</v>
+        <v>-29.57200694042806</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-22.62759170653908</v>
+        <v>-29.0107029216084</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-22.76150884351655</v>
+        <v>-29.11458333333341</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-28.12950744207457</v>
+        <v>-34.24746743849494</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-38.43993185062394</v>
+        <v>-44.03300521134916</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-38.25308604065598</v>
+        <v>-43.81841876629018</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-33.53247431388516</v>
+        <v>-39.38586326767091</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-28.34516238055735</v>
+        <v>-34.46102578962605</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-28.07068766807507</v>
+        <v>-34.21739130434789</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-22.88336202656158</v>
+        <v>-29.37953029863721</v>
       </c>
     </row>
     <row r="25">
@@ -2180,817 +2180,817 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-11.53558395553723</v>
+        <v>-8.542626728110598</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-11.8703607538872</v>
+        <v>-8.788533563814539</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-18.57153769765488</v>
+        <v>-15.04322766570598</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.75817592762386</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.43234938930248</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.882473470136695</v>
+        <v>9.245745601384407</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.8473668915095089</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.832313341493347</v>
+        <v>8.145743145743211</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>3.273672055427177</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1622730473654315</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.15137129994028</v>
+        <v>-2.250144425187685</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.430120703388276</v>
+        <v>-2.526726379659124</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.290124875507544</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.093810845202142</v>
+        <v>5.42799305957201</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>8.951355661881976</v>
+        <v>10.98929707839167</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>19.34375431437827</v>
+        <v>20.88541666666674</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>19.23891361055709</v>
+        <v>20.75253256150513</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>19.45480499148142</v>
+        <v>20.96699478865077</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>14.37849290671251</v>
+        <v>16.18158123370982</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.309630949272801</v>
+        <v>5.614136732329086</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.029372906873135</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.50825970034569</v>
+        <v>5.78260869565225</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.830730447614357</v>
+        <v>0.6204697013626443</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 14.38</t>
+          <t>X ≈ 14.37</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.880892017002814</v>
+        <v>1.002827817343942</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-3.788533563814404</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.239729917334571</v>
+        <v>-0.4977731202515088</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.395142150179332</v>
+        <v>3.455279226394758</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>12.27063017720457</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.10150822322715</v>
+        <v>-1.20879985316104</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>2.541572680060852</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.543983822042527</v>
+        <v>6.782106782106773</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.585471003957231</v>
+        <v>6.910035691790881</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.812555327920691</v>
+        <v>6.113984196571543</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>11.78226714399565</v>
+        <v>15.47712830208498</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.50351774054765</v>
+        <v>15.20054634761361</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.72818176064805</v>
+        <v>18.63110877561744</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18.85492897115799</v>
+        <v>22.92832925963889</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>22.54461176053395</v>
+        <v>26.79162942320837</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>23.13899868247694</v>
+        <v>27.35293344202798</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>27.35290763245594</v>
+        <v>27.24905303030297</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>27.24806692863476</v>
+        <v>27.11616892514137</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>27.46395830955914</v>
+        <v>27.3306311522872</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>23.30297803257064</v>
+        <v>27.54521759734618</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>22.76043186460461</v>
+        <v>26.97777309596539</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>27.03241199015203</v>
+        <v>26.90261057401016</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>22.95906061567756</v>
+        <v>22.60079051383401</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>18.53540227549777</v>
+        <v>17.89319697408998</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 14.97</t>
+          <t>X ≈ 14.96</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-31.41862489120975</v>
+        <v>-23.5426267281106</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.69104275488505</v>
+        <v>6.211466436185532</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.25302370585405</v>
+        <v>4.956772334293952</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-11.68215253581138</v>
+        <v>-15.63562986451427</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.20427921386371</v>
+        <v>4.088811995386244</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>21.50235651107238</v>
+        <v>14.24574560138462</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.619296716070743</v>
+        <v>3.45066358915161</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>20.4521963824288</v>
+        <v>13.14574314574314</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>20.4936835643435</v>
+        <v>13.27367205542725</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>30.83187899941827</v>
+        <v>22.47762056020791</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>31.10593864158003</v>
+        <v>22.7498555748121</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>30.82718923813204</v>
+        <v>22.47327362034095</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>29.70402717127607</v>
+        <v>21.35838150289018</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>18.37183718371838</v>
+        <v>11.11014744145707</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>0.9892970783918145</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>18.17416367110334</v>
+        <v>20.88541666666666</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>18.06932296728216</v>
+        <v>20.75253256150506</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.174103237095203</v>
+        <v>10.96699478865069</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>18.47206015817436</v>
+        <v>11.18158123370968</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>40.1517362124307</v>
+        <v>30.61413673232923</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>40.0758902510216</v>
+        <v>40.5389742103738</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>40.35036496350381</v>
+        <v>40.78260869565231</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>40.62046970136272</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 15.55</t>
+          <t>X ≈ 15.54</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.35915288656803</v>
+        <v>24.23515104966719</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>16.02437608821822</v>
+        <v>23.98924421396323</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>24.5863570391873</v>
+        <v>33.84566122318284</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>13.87340301974463</v>
+        <v>22.14214791326366</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>23.53761254719736</v>
+        <v>21.86658977316432</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>23.72457873329459</v>
+        <v>22.02352337916226</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32.95263004940438</v>
+        <v>32.33955247804082</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>32.67441860465117</v>
+        <v>32.03463203463203</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>32.71590578656587</v>
+        <v>32.16256094431613</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>31.94299011052938</v>
+        <v>31.36650944909697</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>32.21704975269144</v>
+        <v>31.63874446370146</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>21.93830034924345</v>
+        <v>20.25105139811888</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>20.81513828238705</v>
+        <v>19.13615928066796</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>30.59405940594046</v>
+        <v>29.9990363303458</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>29.93591610836004</v>
+        <v>29.31688194846074</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>30.53030303030303</v>
+        <v>29.87818596728073</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>30.39638589332556</v>
+        <v>29.77430555555572</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>30.29154518950438</v>
+        <v>29.64142145039412</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>30.50743657042884</v>
+        <v>29.85588367753989</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>30.69428238039687</v>
+        <v>30.07047012259888</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>30.15173621243084</v>
+        <v>29.50302562121814</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>30.0758902510216</v>
+        <v>29.42786309926253</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>30.35036496350351</v>
+        <v>29.67149758454091</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>30.27453271028052</v>
+        <v>29.50935859025177</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 16.14</t>
+          <t>X ≈ 16.12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.640847113432145</v>
+        <v>-13.54262672811074</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>21.02437608821822</v>
+        <v>6.211466436185674</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-15.04322766570591</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-56.12659698025551</v>
+        <v>-55.63562986451427</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-56.46238745280279</v>
+        <v>-35.91118800461361</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-56.27542126670559</v>
+        <v>-35.75425439861566</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-32.04736995059576</v>
+        <v>-16.54933641084824</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-32.28409421343413</v>
+        <v>-16.72632794457275</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-33.05700988947062</v>
+        <v>-17.52237943979237</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>2.749855574811967</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-8.061699650756694</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-9.184861717612456</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-9.405940594059047</v>
+        <v>1.11014744145735</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>14.93591610836004</v>
+        <v>20.42799305957229</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>0.9892970783913952</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-34.60361410667444</v>
+        <v>-19.11458333333362</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-59.70845481049562</v>
+        <v>-39.24746743849522</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-59.4925634295713</v>
+        <v>-39.03300521134916</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-59.30571761960327</v>
+        <v>-38.81841876629018</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-59.84826378756966</v>
+        <v>-39.3858632676712</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-34.9241097489784</v>
+        <v>-19.46102578962591</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-9.649635036496349</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>15.27453271028002</v>
+        <v>20.62046970136243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 16.73</t>
+          <t>X ≈ 16.71</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>13.02581955323482</v>
+        <v>13.12403993855619</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>46.02437608821822</v>
+        <v>46.21146643618553</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>44.5863570391871</v>
+        <v>44.95677233429382</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>43.8734030197446</v>
+        <v>44.36437013548584</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>43.53761254719733</v>
+        <v>44.08881199538651</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>27.05791206662803</v>
+        <v>27.57907893471792</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>10.11733025581842</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>9.812409812409797</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.28409421343413</v>
+        <v>-6.726327944572752</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>25.55038308602465</v>
+        <v>26.08318890814559</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>41.93830034924331</v>
+        <v>42.47327362034095</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>40.81513828238719</v>
+        <v>41.35838150289018</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>40.59405940594084</v>
+        <v>41.11014744145731</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>39.93591610836004</v>
+        <v>40.42799305957201</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>40.53030303030303</v>
+        <v>40.98929707839167</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>40.39638589332556</v>
+        <v>40.88541666666666</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>40.29154518950438</v>
+        <v>40.75253256150506</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>23.84076990376179</v>
+        <v>24.30032812198392</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-9.848263787569302</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-9.924109748978168</v>
+        <v>-9.461025789625964</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>23.68369829683674</v>
+        <v>24.11594202898527</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>23.60786604361346</v>
+        <v>23.9538030346958</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 17.31</t>
+          <t>X ≈ 17.3</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46.35915288656803</v>
+        <v>46.4573732718894</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-53.97562391178178</v>
+        <v>-53.78853356381447</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>44.58635703918723</v>
+        <v>44.95677233429395</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>43.87340301974449</v>
+        <v>44.36437013548573</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>43.53761254719721</v>
+        <v>44.08881199538639</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>43.7245787332953</v>
+        <v>44.24574560138519</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>42.95263004940424</v>
+        <v>43.45066358915176</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>42.67441860465117</v>
+        <v>43.14574314574314</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>42.71590578656587</v>
+        <v>43.27367205542725</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>41.94299011053009</v>
+        <v>42.47762056020862</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>42.2170497526913</v>
+        <v>42.74985557481224</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>41.93830034924402</v>
+        <v>42.47327362034166</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>40.81513828238719</v>
+        <v>41.35838150289018</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>40.59405940593776</v>
+        <v>41.11014744145422</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>39.93591610836075</v>
+        <v>40.42799305957272</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>40.53030303030374</v>
+        <v>40.98929707839238</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>40.39638589332556</v>
+        <v>40.88541666666666</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>40.29154518950438</v>
+        <v>40.75253256150506</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>40.5074365704287</v>
+        <v>40.96699478865084</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>40.69428238039673</v>
+        <v>41.18158123370982</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>40.1517362124307</v>
+        <v>40.61413673232909</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>40.07589025101876</v>
+        <v>40.53897421037096</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>40.35036496350507</v>
+        <v>40.7826086956536</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>40.2745327102818</v>
+        <v>40.62046970136414</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 17.9</t>
+          <t>X ≈ 17.88</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>19.58635703918723</v>
+        <v>19.95677233429395</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>43.87340301974432</v>
+        <v>44.36437013548556</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>43.53761254719704</v>
+        <v>44.08881199538622</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>43.72457873329442</v>
+        <v>44.24574560138431</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>42.95263004940424</v>
+        <v>43.45066358915176</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>42.67441860465117</v>
+        <v>43.14574314574314</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>42.71590578656587</v>
+        <v>43.27367205542725</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>41.94299011052921</v>
+        <v>42.47762056020774</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>42.2170497526913</v>
+        <v>42.74985557481224</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>41.93830034924314</v>
+        <v>42.47327362034078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>40.81513828238719</v>
+        <v>41.35838150289018</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>40.59405940594095</v>
+        <v>41.11014744145742</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>39.93591610835987</v>
+        <v>40.42799305957184</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>40.53030303030286</v>
+        <v>40.9892970783915</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>40.39638589332556</v>
+        <v>40.88541666666666</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>40.29154518950438</v>
+        <v>40.75253256150506</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>40.50743657042906</v>
+        <v>40.96699478865119</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>40.69428238039673</v>
+        <v>41.18158123370982</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>40.1517362124307</v>
+        <v>40.61413673232909</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>40.07589025102195</v>
+        <v>40.53897421037416</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>40.35036496350365</v>
+        <v>40.78260869565218</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>40.62046970136272</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 18.48</t>
+          <t>X ≈ 18.47</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>6</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-36.97418044676518</v>
+        <v>-36.87596006144381</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-37.30895724511512</v>
+        <v>-37.1218668971478</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-22.08030962747944</v>
+        <v>-21.70989433237272</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-22.79326364692218</v>
+        <v>-22.30229653118094</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-23.12905411946946</v>
+        <v>-22.57785467128028</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-22.94208793337208</v>
+        <v>-22.42092106528219</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-23.71403661726243</v>
+        <v>-23.21600307751491</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-23.99224806201551</v>
+        <v>-23.52092352092353</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-23.95076088010067</v>
+        <v>-23.3929946112393</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-24.72367655613729</v>
+        <v>-24.18904610645876</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-24.44961691397537</v>
+        <v>-23.91681109185443</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-24.72836631742337</v>
+        <v>-24.19339304632572</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-25.85152838427948</v>
+        <v>-25.3082851637765</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-26.07260726072595</v>
+        <v>-25.55651922520948</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-26.7307505583065</v>
+        <v>-26.23867360709453</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-42.8030303030303</v>
+        <v>-42.34403625494166</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-26.27028077334111</v>
+        <v>-25.78125000000001</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-26.37512147716241</v>
+        <v>-25.91413410516172</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-26.15923009623797</v>
+        <v>-25.69967187801583</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-25.97238428626994</v>
+        <v>-25.48508543295685</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-26.51493045423597</v>
+        <v>-26.05252993433758</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-26.59077641564495</v>
+        <v>-26.12769245629274</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-26.31630170316302</v>
+        <v>-25.88405797101449</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-26.3921339563863</v>
+        <v>-26.04619696530396</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 19.07</t>
+          <t>X ≈ 19.05</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>14</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>17.78772431513941</v>
+        <v>17.88594470046078</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.31009037393245</v>
+        <v>10.49718072189977</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.872071324901462</v>
+        <v>9.242486620008187</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22.44483159117306</v>
+        <v>22.9357987069143</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>29.25189826148288</v>
+        <v>29.80309770967206</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>29.4388644475803</v>
+        <v>29.96003131567019</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>28.66691576368991</v>
+        <v>29.16494930343742</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>28.38870431893687</v>
+        <v>28.86002886002885</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>28.43019150085154</v>
+        <v>28.98795776971291</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>20.51441868195795</v>
+        <v>21.04904913163648</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.64562118126268</v>
+        <v>14.17842700338362</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.36687177781478</v>
+        <v>13.90184504891242</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.38656685381576</v>
+        <v>19.92981007431874</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.16548797736917</v>
+        <v>19.68157601288564</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>18.50734467978861</v>
+        <v>18.99942163100058</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>26.2445887445888</v>
+        <v>26.70358279267744</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>18.96781446475413</v>
+        <v>19.45684523809523</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>26.00583090379014</v>
+        <v>26.46681827579083</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>26.22172228471447</v>
+        <v>26.6812805029366</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>26.40856809468239</v>
+        <v>26.89586694799549</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>25.86602192671636</v>
+        <v>26.32842244661475</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>25.79017596530726</v>
+        <v>26.25325992465947</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>26.06465067778936</v>
+        <v>26.49689440993789</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>25.98881842456608</v>
+        <v>26.33475541564842</v>
       </c>
     </row>
   </sheetData>
@@ -3180,165 +3180,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 2.37</t>
+          <t>X &gt; 2.372</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3331</v>
+        <v>3356</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.003399289937632943</v>
+        <v>0.02351710142476549</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.005885184549867972</v>
+        <v>0.2375173538883146</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04578424682446069</v>
+        <v>0.3313651681701728</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.005900781606619887</v>
+        <v>0.3477824577606157</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.01462625877293533</v>
+        <v>0.2962194027938025</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0198225805304304</v>
+        <v>0.2327047003767717</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06135167425490096</v>
+        <v>0.2843428064657161</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1587329159747384</v>
+        <v>0.3818048302034001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1875136765837979</v>
+        <v>0.4673831203931371</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2090588698716829</v>
+        <v>0.4598164059052365</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2613081258970382</v>
+        <v>0.5414851384809864</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3289674147533219</v>
+        <v>0.6383567557328718</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4500874146433205</v>
+        <v>0.817840962349635</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.5162383942674467</v>
+        <v>0.8843601568462489</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.5047783838091391</v>
+        <v>0.9034759719048466</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.4883743091290285</v>
+        <v>0.8882269238137965</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.5222097399402941</v>
+        <v>0.8913637377341672</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.4953210360731504</v>
+        <v>0.8358163211719258</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.4894509589179137</v>
+        <v>0.9193899091506808</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.4544023204267162</v>
+        <v>0.8244383765669596</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.4696726251481564</v>
+        <v>0.8999360773722529</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.4719298549819939</v>
+        <v>0.8427264438461108</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.5244345913547974</v>
+        <v>0.9255935035163461</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.5267092338468657</v>
+        <v>0.8409702973102711</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 2.956</t>
+          <t>X &gt; 2.957</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3193</v>
+        <v>3231</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.02830711542375042</v>
+        <v>0.1144107642065535</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05236986737840965</v>
+        <v>0.2538888155276808</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.093513230848707</v>
+        <v>0.3073258398290122</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2381711492184948</v>
+        <v>0.4701837313023987</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.386927615690368</v>
+        <v>0.6118889184633147</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.3424547843690249</v>
+        <v>0.5707686854103287</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.366960267472777</v>
+        <v>0.6243089093487981</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.4494263952401383</v>
+        <v>0.706568523014468</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.6024394524012848</v>
+        <v>0.883037428193731</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.6271185795034953</v>
+        <v>0.9059718699151489</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7635251113937329</v>
+        <v>1.072913527956509</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.7214516752963434</v>
+        <v>1.091836679237034</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.771442901613149</v>
+        <v>1.167141527566294</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.7564072048790962</v>
+        <v>1.122489311250341</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.6479710740065059</v>
+        <v>1.014412812658428</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.6990003124023758</v>
+        <v>1.03869504072572</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.8651358933255651</v>
+        <v>1.138659409100264</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.9042366555875248</v>
+        <v>1.086174822858169</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.9827336310916124</v>
+        <v>1.226574516710166</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.9695404348227541</v>
+        <v>1.150669332627906</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.9777687531065453</v>
+        <v>1.189275878896801</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.8896617690184669</v>
+        <v>1.101918843841169</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.8700894469100433</v>
+        <v>1.116767111493765</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.813211069190487</v>
+        <v>1.035201982390262</v>
       </c>
     </row>
     <row r="8">
@@ -3348,2293 +3348,2293 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2991</v>
+        <v>3037</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.4069299270458089</v>
+        <v>0.5423405921508362</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.4551759554601702</v>
+        <v>0.7390898425274699</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2304473446321111</v>
+        <v>0.5486624585581694</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4326856500998559</v>
+        <v>0.7595287877591943</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6472470986922261</v>
+        <v>0.927817230988488</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5540901988977822</v>
+        <v>0.8087570580129508</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6321513259999918</v>
+        <v>0.8835385072919024</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.5726560506105969</v>
+        <v>0.8267126839023291</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.8330049216290831</v>
+        <v>1.071837193041922</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.9446540040401956</v>
+        <v>1.14690931799224</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.071909939109418</v>
+        <v>1.274445738746678</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.079159490102441</v>
+        <v>1.279439576392107</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.274831820028759</v>
+        <v>1.496176778480731</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.44044394442777</v>
+        <v>1.628690270469214</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.50258277502671</v>
+        <v>1.688662790366493</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.517298695524772</v>
+        <v>1.711792973301364</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.637213111470992</v>
+        <v>1.857821397284276</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.452706350665537</v>
+        <v>1.679249617042359</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.421989307411344</v>
+        <v>1.650755472411518</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.395450994753986</v>
+        <v>1.622225758537176</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.307380835009184</v>
+        <v>1.535189363908032</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.285379058238433</v>
+        <v>1.512978817152344</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.413199188102581</v>
+        <v>1.612101783209788</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.29091519105603</v>
+        <v>1.46999225651583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 4.128</t>
+          <t>X &gt; 4.127</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2727</v>
+        <v>2776</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1135743861592431</v>
+        <v>0.01221428653749257</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1014878623092486</v>
+        <v>0.1785858071648008</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2462484921082577</v>
+        <v>0.05151670326070246</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2474560992944603</v>
+        <v>0.08683079356870138</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2382680461047144</v>
+        <v>0.5109944640804898</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5551798261907663</v>
+        <v>0.7597040838468985</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.7514638686462192</v>
+        <v>0.9873624792341076</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.004713901771105</v>
+        <v>1.24029901966864</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.0310042548372</v>
+        <v>1.245725083015927</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.191439581525373</v>
+        <v>1.402351743003607</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.414130044662109</v>
+        <v>1.624004015113435</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.266522328067694</v>
+        <v>1.476143060800062</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.479857055214062</v>
+        <v>1.674133207231769</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.719379099035223</v>
+        <v>1.914167541959579</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.85112078672261</v>
+        <v>2.043791982372724</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.883136668328625</v>
+        <v>2.088435009426156</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.954542440509172</v>
+        <v>2.114306354054378</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.981995244389111</v>
+        <v>2.147212647773934</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.00084799063368</v>
+        <v>2.168001620725626</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.283443859708335</v>
+        <v>2.440574039465218</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.166388227082713</v>
+        <v>2.326983079936142</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.149910038489537</v>
+        <v>2.310032525708571</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.263854699574033</v>
+        <v>2.395860406131114</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.064044994842163</v>
+        <v>2.183870277731593</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 4.714</t>
+          <t>X &gt; 4.712</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2475</v>
+        <v>2522</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.158060884448787</v>
+        <v>-0.02592731750156219</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3512746927189099</v>
+        <v>-0.05425683425471561</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6460147556845683</v>
+        <v>-0.3440534620096258</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7358154171292597</v>
+        <v>-0.4428682594788711</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1672791929792083</v>
+        <v>0.05103159396963264</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2385179373833139</v>
+        <v>-0.04559298129268541</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.02489804048340005</v>
+        <v>0.1659058104987423</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.04093807474350086</v>
+        <v>0.2379417273034221</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.105464019497596</v>
+        <v>0.2701245583835004</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.03861084174673834</v>
+        <v>0.2063271848135884</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1752491096044864</v>
+        <v>0.3435439377313827</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0002223436140269541</v>
+        <v>0.1686169510433899</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4692010337950734</v>
+        <v>0.6161785814531413</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7550252007092126</v>
+        <v>0.9047761934317862</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.6444507299381428</v>
+        <v>0.799387765221951</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.699453251809274</v>
+        <v>0.8707200032928597</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.8718089392562547</v>
+        <v>1.027765421115056</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.9122626421444338</v>
+        <v>1.076899650112665</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.9509849575254847</v>
+        <v>1.117370728500461</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.121874151272081</v>
+        <v>1.276593110194383</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.7651341139641943</v>
+        <v>0.9309684154974036</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.673387223165328</v>
+        <v>0.840083560611518</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.89156044007877</v>
+        <v>1.028347895018015</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.8805933163409847</v>
+        <v>1.009050193035989</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 5.3</t>
+          <t>X &gt; 5.298</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2209</v>
+        <v>2260</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7286607335036521</v>
+        <v>-0.5859907228543548</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.219012526752643</v>
+        <v>-0.8963337390993118</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.5571407186603</v>
+        <v>-1.251031260620557</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.662711829963897</v>
+        <v>-1.381243899601998</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.39057416734498</v>
+        <v>-1.150327978286263</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.313589205636703</v>
+        <v>-1.057151676929834</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.207298072788028</v>
+        <v>-0.9937808552926839</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.235693754899394</v>
+        <v>-1.010671616998508</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.303878386096002</v>
+        <v>-1.077976296221102</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.376847946150782</v>
+        <v>-1.18992561393457</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.482320184302402</v>
+        <v>-1.288859779345252</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.735720362147966</v>
+        <v>-1.540810886701301</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.076753609504706</v>
+        <v>-0.9137453134902742</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8209924192058651</v>
+        <v>-0.6079142325517424</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.7313517004767505</v>
+        <v>-0.5151537011155227</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.5612621478656692</v>
+        <v>-0.3687276129663459</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.3075852258080189</v>
+        <v>-0.1379622481987965</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1147753522563448</v>
+        <v>0.06409478568863847</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.05263569696063541</v>
+        <v>0.1281426915205941</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1610695471387018</v>
+        <v>0.3246907743458607</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.03813720529082332</v>
+        <v>0.1368941340082728</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.09398161239654712</v>
+        <v>0.2648804880042164</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>0.4907024594734892</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.3016943218693271</v>
+        <v>0.4434785509202399</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 5.886</t>
+          <t>X &gt; 5.883</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1932</v>
+        <v>1976</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6634343824258124</v>
+        <v>-0.4834491955128115</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.792778508597394</v>
+        <v>-1.581913704235731</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.124845427410918</v>
+        <v>-1.883749230400127</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.039193381283795</v>
+        <v>-1.824195561605549</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.935638481609367</v>
+        <v>-1.721524181231764</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.772075924451158</v>
+        <v>-1.587587731948858</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.949532669442306</v>
+        <v>-1.780260105627356</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.99327845871823</v>
+        <v>-1.756316120957017</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.820176687660933</v>
+        <v>-1.650951060150639</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.716803703903608</v>
+        <v>-1.514335196453729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.752022412257148</v>
+        <v>-1.515737986555969</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.89872904735288</v>
+        <v>-1.663616163252414</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.135326113897641</v>
+        <v>-0.9667317331440444</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9952078799211108</v>
+        <v>-0.783105327928638</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.879357369452137</v>
+        <v>-0.6299414492441073</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.7493667323388706</v>
+        <v>-0.4421545345115518</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.780084694909732</v>
+        <v>-0.4660709783156918</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.4721287011045021</v>
+        <v>-0.1152777311286357</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3805345188846658</v>
+        <v>-0.02240450463538224</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.008196958446248459</v>
+        <v>0.3229953751239591</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1066617203858371</v>
+        <v>0.2402105069627467</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.05520772775376059</v>
+        <v>0.3974170819612581</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.3607115749883931</v>
+        <v>0.6713289789096351</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.4712200808807836</v>
+        <v>0.792534478690655</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 6.472</t>
+          <t>X &gt; 6.468</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1704</v>
+        <v>1741</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7853692579541161</v>
+        <v>-0.6822148287971004</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.905653066300729</v>
+        <v>-1.557412282349937</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.263117873298185</v>
+        <v>-2.01119105243373</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.602370477044772</v>
+        <v>-1.230595539571482</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.614256611681284</v>
+        <v>-1.246047764201471</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.453679595168289</v>
+        <v>-1.057805372269584</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.60877345936769</v>
+        <v>-1.280149698362557</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.886984904120766</v>
+        <v>-1.470522604543227</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.903977254369799</v>
+        <v>-1.514415000701042</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.741220415786415</v>
+        <v>-1.394086198096787</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.525640305788222</v>
+        <v>-1.179124952106427</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.628951112744993</v>
+        <v>-1.2838856007358</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6468500217063777</v>
+        <v>-0.2796482794694981</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4585721730067789</v>
+        <v>-0.06969219199081067</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1810429559674418</v>
+        <v>0.1645337239477271</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1794258373205722</v>
+        <v>0.61129020553944</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.4548654254893023</v>
+        <v>0.8510524054982795</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.7593814468143165</v>
+        <v>1.23363221786245</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.6595723223303906</v>
+        <v>1.138914559424478</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.8816360103733132</v>
+        <v>1.330663802517165</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.9015897566603357</v>
+        <v>1.314079359982557</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.388903146683965</v>
+        <v>1.812640303317004</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.699338570541777</v>
+        <v>2.034043827684329</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.600823790092591</v>
+        <v>2.021963095963521</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 7.058</t>
+          <t>X &gt; 7.053</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1491</v>
+        <v>1526</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6801019371179251</v>
+        <v>-0.5321555239221141</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.645397546934916</v>
+        <v>-1.301622569050068</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.782730235962674</v>
+        <v>-1.509196252093481</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.526596980255512</v>
+        <v>-1.316258136765583</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.692540888426542</v>
+        <v>-1.460926224508896</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.535768396211417</v>
+        <v>-1.303992618510811</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.669948440909714</v>
+        <v>-1.510069395141436</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.081760420064938</v>
+        <v>-1.814989838550055</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.240674039753443</v>
+        <v>-2.014286059755996</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.145186242176031</v>
+        <v>-1.89410718848319</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.004727134416243</v>
+        <v>-1.752762226234871</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.41707707226638</v>
+        <v>-2.09478920688418</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.669831657492573</v>
+        <v>-1.311775565172653</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.690509732335954</v>
+        <v>-1.298229521893717</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.346649021900475</v>
+        <v>-0.9332634849306132</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.8858626343596328</v>
+        <v>-0.4374044922889482</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.552177900929621</v>
+        <v>-0.08316972076789142</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2562170015443854</v>
+        <v>0.2420613573165795</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.267964499090013</v>
+        <v>0.1947434797503149</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.02538605932649318</v>
+        <v>0.409329924809299</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.05802804643337822</v>
+        <v>0.3654456328526479</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.6251199898025703</v>
+        <v>0.9447333726774616</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.9401772959433288</v>
+        <v>1.227926311893171</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.9049820731241027</v>
+        <v>1.236459216434802</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 7.644</t>
+          <t>X &gt; 7.639</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1288</v>
+        <v>1297</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9767544493393032</v>
+        <v>-0.8826421483110636</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.234311170469041</v>
+        <v>-1.051447981701905</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.054569601739409</v>
+        <v>-1.612233062776212</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.763662617321145</v>
+        <v>-1.279423233828069</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.516483279696146</v>
+        <v>-0.9381733554231602</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.715915857122724</v>
+        <v>-1.089643758677205</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.1787455301939</v>
+        <v>-1.653422763970823</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.2251177168326</v>
+        <v>-1.727040200440356</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.183630534917896</v>
+        <v>-1.599111290756248</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.106468931201682</v>
+        <v>-1.547051760532256</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.064248547154136</v>
+        <v>-1.506119752867022</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.961235972240459</v>
+        <v>-2.399509725842549</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.075124468772003</v>
+        <v>-1.509775783154545</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.45076285062818</v>
+        <v>-1.912211849213712</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.104269363046448</v>
+        <v>-1.592053201029373</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.432602688398674</v>
+        <v>-0.9536481798966818</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.411960319966553</v>
+        <v>-0.9033265869956324</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.362241518378156</v>
+        <v>-0.8820086875311759</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.101225455866739</v>
+        <v>-0.6675464603854024</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.869185111863338</v>
+        <v>-0.4529600153264184</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.9017107279256109</v>
+        <v>-0.557798502828966</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.2341872683582551</v>
+        <v>0.06094799603301482</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.3193331559008641</v>
+        <v>0.5358854882504858</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.212420909038137</v>
+        <v>0.2966454916479861</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 8.23</t>
+          <t>X &gt; 8.224</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.219194691779549</v>
+        <v>-1.030778386878374</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9841709203287863</v>
+        <v>-0.7079648434353203</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.662455876292363</v>
+        <v>-1.204365106464344</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.330775517767385</v>
+        <v>-0.7541132768365486</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.191732182147518</v>
+        <v>-0.5557377676467752</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.764500089117561</v>
+        <v>-1.157098000511262</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.25154848810763</v>
+        <v>-1.762606553028334</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.149892886326988</v>
+        <v>-1.593593347147852</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.918472181145432</v>
+        <v>-1.276090977748112</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.836687002481071</v>
+        <v>-1.219061904247063</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.277727075418859</v>
+        <v>-0.6624667000692739</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.841376763767144</v>
+        <v>-1.223408844114026</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.350103882854981</v>
+        <v>-0.7269265539818619</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.046016567468712</v>
+        <v>-1.449094264704065</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.849459010348419</v>
+        <v>-1.278168077868749</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.204739704739708</v>
+        <v>-1.664731357627282</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.053756556816893</v>
+        <v>-1.484251579778835</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.253564022271505</v>
+        <v>-1.711922414798259</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.078114760369772</v>
+        <v>-1.592246917510295</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.741493071553791</v>
+        <v>-1.282873742593502</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.943501882807396</v>
+        <v>-1.565958054400774</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.392174572619965</v>
+        <v>-1.072400197209134</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.8710090822978742</v>
+        <v>-0.6391922522151177</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7951903078667115</v>
+        <v>-0.7065445166467654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 8.816</t>
+          <t>X &gt; 8.809</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2520242834676338</v>
+        <v>-0.0984462055452795</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2455413676474691</v>
+        <v>0.4870008779907593</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5979473603371517</v>
+        <v>-0.1738689958723114</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.310901379779892</v>
+        <v>-0.7662711946805345</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.25580517502123</v>
+        <v>0.858408194911334</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1517589599277613</v>
+        <v>0.4215175728809157</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.804801579608835</v>
+        <v>-0.2547995937461067</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9641069601526411</v>
+        <v>-0.4409551915490226</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.09027732877301275</v>
+        <v>0.5183276373749948</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2069615730739756</v>
+        <v>0.7911597526069656</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4810212152358986</v>
+        <v>1.0633947672113</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4400839402064491</v>
+        <v>1.024342503951395</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.100512836489443</v>
+        <v>1.690923070586138</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6416218316243061</v>
+        <v>1.205159317941629</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.053633111927226</v>
+        <v>1.591888546507882</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.9345836486145629</v>
+        <v>1.440603491693338</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.038478640055637</v>
+        <v>1.574252771179729</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.528168257280825</v>
+        <v>2.035192894046638</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.936007999000132</v>
+        <v>2.368419966798108</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.957691200420562</v>
+        <v>2.345476720645692</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.965578694530933</v>
+        <v>2.253091601687764</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.202533022825662</v>
+        <v>2.415458770943864</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.5513219013027</v>
+        <v>2.659093256222242</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.78950277016061</v>
+        <v>2.734483953144185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 9.402</t>
+          <t>X &gt; 9.394</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2684130958366637</v>
+        <v>-0.1898570488103033</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.863085765637571</v>
+        <v>0.8761894682555038</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.01157698053619782</v>
+        <v>0.3503583401248633</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.9946321708713555</v>
+        <v>-0.5335890481877499</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5757357143526463</v>
+        <v>1.085896543491351</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1170634954444125</v>
+        <v>0.3681945809763079</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4491294813875442</v>
+        <v>0.01043035300015305</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5807133601582137</v>
+        <v>-0.1487174956562711</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1939116516685147</v>
+        <v>0.7080743877887627</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.007506239561642758</v>
+        <v>0.4951132715781768</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2815658817235658</v>
+        <v>0.9131208809346916</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2960716102403751</v>
+        <v>0.7823115212155827</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4925576372259002</v>
+        <v>1.125145351286676</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5647338927441226</v>
+        <v>1.022683884605755</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.786355991057988</v>
+        <v>1.360937665986008</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.9408602150537675</v>
+        <v>1.484923900549106</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.393453342005913</v>
+        <v>1.964133867832842</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.875122902114349</v>
+        <v>2.268567546927805</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.034602502880979</v>
+        <v>2.337257179321384</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.606047086279084</v>
+        <v>2.843388813884751</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.891058745567662</v>
+        <v>3.004807286264942</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.257038999180651</v>
+        <v>3.366962548566221</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.120615331692157</v>
+        <v>4.193687412853343</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.897507673461519</v>
+        <v>4.031548418563879</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 9.988</t>
+          <t>X &gt; 9.979</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3698190760487918</v>
+        <v>-0.4060953627969397</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2299835648537254</v>
+        <v>0.08600518157298609</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4603719327753879</v>
+        <v>-0.2461796952263384</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.173325952218129</v>
+        <v>-0.8385818940345615</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9207901172906716</v>
+        <v>1.284383951105951</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.01373902371475566</v>
+        <v>0.3343064869933272</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2249400440536959</v>
+        <v>0.09273000981596624</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1293197131058434</v>
+        <v>0.1568132564442521</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4616643068920681</v>
+        <v>0.1002403211099008</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.673832319377162</v>
+        <v>-0.1423056390540793</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7736044529161816</v>
+        <v>-0.2390743144866434</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1177744171118391</v>
+        <v>0.2223511111158487</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3063570447156181</v>
+        <v>0.214470063775785</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2202276302396697</v>
+        <v>0.7042433824164789</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.057411435462846</v>
+        <v>1.49810376067903</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.091050693854434</v>
+        <v>1.321400399424888</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.517881220428364</v>
+        <v>1.955527367773684</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.59995640445765</v>
+        <v>2.007145107630528</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.002763673232444</v>
+        <v>2.406109179794747</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.815777707499535</v>
+        <v>2.25169193481684</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.020895090935369</v>
+        <v>2.422254813509895</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.692712680928132</v>
+        <v>2.90059782660996</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>4.275598608363467</v>
+        <v>4.620247072035944</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>4.386682242990652</v>
+        <v>4.458108077746481</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 10.57</t>
+          <t>X &gt; 10.56</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>387</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6692708860417866</v>
+        <v>-0.5710505007204176</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.004047684391601</v>
+        <v>-0.8169573364242879</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.666872934972979</v>
+        <v>-1.296457639866254</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.638224887232262</v>
+        <v>-2.14725777149102</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9019536324685333</v>
+        <v>1.453153080657714</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2030698455167794</v>
+        <v>0.3180970225731059</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7166205965905874</v>
+        <v>-0.2185870568430701</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.03875968992248602</v>
+        <v>0.51008423101446</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.211742792245502</v>
+        <v>-0.6539765233841237</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.209464669832379</v>
+        <v>-0.6748342201538478</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.710598826120069</v>
+        <v>-1.177793003999128</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.989348229568066</v>
+        <v>-1.454374958470424</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.562122699524956</v>
+        <v>-1.018879479021969</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2839818865607455</v>
+        <v>0.8000699220772134</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.115763478203263</v>
+        <v>0.3763134730087074</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.2202255109231785</v>
+        <v>0.6792195590118197</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.4304874916873587</v>
+        <v>0.05854328165374767</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.7937261283250763</v>
+        <v>-0.3327387563243889</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.836232680217293</v>
+        <v>-0.3766744619951581</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.42458066869888</v>
+        <v>-0.9372818153857878</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.450330971031832</v>
+        <v>-0.9879304511334439</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.02421066445829467</v>
+        <v>0.4872946238104987</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.590675041023026</v>
+        <v>2.022918773171554</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.5484345190659</v>
+        <v>2.89437151014824</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 11.16</t>
+          <t>X &gt; 11.15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6803207976425014</v>
+        <v>-0.6014502575223588</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.001939701255466</v>
+        <v>-1.827749250088971</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.782064013444355</v>
+        <v>-2.428848580738723</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.481860138150246</v>
+        <v>-4.328440322030616</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.528176926486999</v>
+        <v>-1.009227220299877</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.314894950915942</v>
+        <v>-2.813077928027283</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.100001529543128</v>
+        <v>-2.62776778339726</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.404528763769882</v>
+        <v>-0.9719039130803893</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.007778423960445</v>
+        <v>-2.804759317121771</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.793851994733771</v>
+        <v>-2.293621269857447</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.506634457835013</v>
+        <v>-3.001778412115861</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.127489124440906</v>
+        <v>-2.624765595345323</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.934861717612812</v>
+        <v>-2.43246817031244</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5243616466909842</v>
+        <v>-0.06632314677822393</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.8535575758504947</v>
+        <v>-0.4216801430423658</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3987240829346135</v>
+        <v>0.793218647019124</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.251649051220291</v>
+        <v>1.669730392156858</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1599662421359582</v>
+        <v>0.556454130132515</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.3758576230602841</v>
+        <v>0.7709163572782884</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8916508014493587</v>
+        <v>1.312300187958186</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.335946738746486</v>
+        <v>1.725247843440201</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.89167972470581</v>
+        <v>4.264464406452227</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>4.824049174029966</v>
+        <v>5.161693662972446</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>4.748216920806691</v>
+        <v>4.999554668682983</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 11.75</t>
+          <t>X &gt; 11.74</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>247</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1995515668732608</v>
+        <v>-0.1013311815518918</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1294700656279346</v>
+        <v>0.05762028233937855</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4568023833167842</v>
+        <v>0.8272176784235086</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.470726534911378</v>
+        <v>-0.9797594191701364</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.2177744905170513</v>
+        <v>0.7689739387062318</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.429267420551561</v>
+        <v>-1.908100552461676</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.581782906061342</v>
+        <v>-1.083749366313825</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2405611524338624</v>
+        <v>0.2307633886581115</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.223365468494862</v>
+        <v>-1.665599199633483</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.186564545341064</v>
+        <v>-1.651934095662533</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.722221502369429</v>
+        <v>-2.189415680248487</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5718211082465743</v>
+        <v>-0.03684783714893314</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.8852665759124108</v>
+        <v>-0.3420233554094239</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.727662644806998</v>
+        <v>2.243750680323465</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.1450555515589897</v>
+        <v>0.3470213996529807</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.04447307078885387</v>
+        <v>0.5034671188774951</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.4943023657837529</v>
+        <v>-0.005271592442646522</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.004001369200076</v>
+        <v>-0.5430139971993881</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.383251688680609</v>
+        <v>0.07630652954152595</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.1964058787125822</v>
+        <v>0.29089297460051</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4756228521068167</v>
+        <v>0.9380233720052047</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.828926688268567</v>
+        <v>3.292010647620771</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>4.722834599131176</v>
+        <v>5.155078331279704</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>4.6470023459079</v>
+        <v>4.99293933699024</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 12.33</t>
+          <t>X &gt; 12.32</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.466934069953709</v>
+        <v>-0.9110477807421802</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.284802655743135</v>
+        <v>-2.113892415489104</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>0.4591646787915593</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.0203167870188</v>
+        <v>-1.568644218581255</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.508627039950838</v>
+        <v>1.983548837491661</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2367739237102313</v>
+        <v>0.226606845403623</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.889828117037091</v>
+        <v>2.30233823030008</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.510167396921695</v>
+        <v>4.868231184020651</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.585471003957181</v>
+        <v>4.039222294661691</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.778738902799908</v>
+        <v>4.200108598485421</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.086614970082614</v>
+        <v>3.515405814046687</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.740232716393066</v>
+        <v>5.152699457661527</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.549437799295397</v>
+        <v>5.951682938296877</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8.226909647486494</v>
+        <v>8.57426227399295</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>6.119490987587092</v>
+        <v>6.456701193543303</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>5.747694334650859</v>
+        <v>6.061067413319904</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.130685410233767</v>
+        <v>5.478718102073366</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.542752918972965</v>
+        <v>4.867365097390234</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>4.758644299897291</v>
+        <v>5.081827324536007</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>4.945490109865318</v>
+        <v>5.296413769594992</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>4.886035729338907</v>
+        <v>5.207438167735788</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>7.708740492567493</v>
+        <v>8.003089042909686</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>9.432490567368376</v>
+        <v>9.682130226752655</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>8.873566526705496</v>
+        <v>9.041522332941661</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 12.92</t>
+          <t>X &gt; 12.91</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.010412330823279</v>
+        <v>-1.392089093701998</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.801710868303523</v>
+        <v>-1.100361520803716</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5223386129866867</v>
+        <v>0.3331164203154557</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.32224915416856</v>
+        <v>-1.872189004299223</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.146308199371127</v>
+        <v>1.615693715816505</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8406386580097518</v>
+        <v>-0.3779103125940182</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.104803962447725</v>
+        <v>1.515179718184022</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.174418604651166</v>
+        <v>4.973700134990452</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.128949264826737</v>
+        <v>4.026360227470263</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.986468371398949</v>
+        <v>4.843211958057374</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.173571491821733</v>
+        <v>4.040178155457404</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.068735131851994</v>
+        <v>5.914133835394708</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.119486108474142</v>
+        <v>6.949779352352543</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>10.70275505811451</v>
+        <v>10.46498615113449</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8.414176977925258</v>
+        <v>8.169928543442971</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>9.00856389986825</v>
+        <v>8.731232562262633</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>8.874646762890777</v>
+        <v>8.627352150537625</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>8.226327798200032</v>
+        <v>7.956833636773879</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>7.898740918254795</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>7.542108467353245</v>
+        <v>7.310613491774333</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.999562299387215</v>
+        <v>6.743168990393599</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>9.641107642325942</v>
+        <v>9.35617851144908</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>11.00253887654713</v>
+        <v>10.67508181393175</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>10.92670662332386</v>
+        <v>10.51294281964228</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 13.5</t>
+          <t>X &gt; 13.49</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3075137800986312</v>
+        <v>0.07183110321470565</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.248351184509062</v>
+        <v>-0.7764853710433783</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.949993402823587</v>
+        <v>1.583278358390345</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3690212226797485</v>
+        <v>0.3884665210278939</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>4.329775850808083</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.30033630905217</v>
+        <v>2.077070902589291</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.558690655464851</v>
+        <v>4.294037083127662</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.916842847075415</v>
+        <v>7.603574471044354</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.352269422929503</v>
+        <v>7.129093742174227</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>9.345090439725979</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.277655813297365</v>
+        <v>9.014915815776106</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>10.42314883409179</v>
+        <v>11.14797241552166</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>12.3302897975387</v>
+        <v>13.04512849084198</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>14.53345334533454</v>
+        <v>15.20653298362574</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>12.05712822957216</v>
+        <v>12.71714968607804</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>12.65151515151516</v>
+        <v>13.2784537048977</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>12.51759801453768</v>
+        <v>13.17457329317269</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>12.4127573107165</v>
+        <v>13.04168918801109</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>13.23470929770144</v>
+        <v>13.85856105371107</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>12.81549450160885</v>
+        <v>13.47073786021585</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>11.66688772758221</v>
+        <v>12.30088372028089</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>14.01528419041554</v>
+        <v>14.63535975254248</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>15.50188011501879</v>
+        <v>16.0838135149293</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>14.81998725573492</v>
+        <v>15.3192648820856</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 14.09</t>
+          <t>X &gt; 14.08</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>146</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.153673434513237</v>
+        <v>1.251893819834606</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1339651293141131</v>
+        <v>0.3210554772814262</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.490466628228326</v>
+        <v>3.86088192333505</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7227180882376416</v>
+        <v>1.213685203978883</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.811585149936938</v>
+        <v>4.362784598126119</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5738938017877473</v>
+        <v>1.095060669877633</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.911534158993284</v>
+        <v>4.409567698740801</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.057980248486786</v>
+        <v>7.529304789578759</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.099467430401489</v>
+        <v>7.657233699262868</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.751209288611577</v>
+        <v>10.28583973829011</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>10.0252689307735</v>
+        <v>10.55807475289444</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>12.48624555472276</v>
+        <v>13.0212188258204</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.10280951526391</v>
+        <v>14.64605273576689</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>16.62145666621457</v>
+        <v>17.13754470173104</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>13.22358734123676</v>
+        <v>13.71566429244873</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>13.13304275633043</v>
+        <v>13.59203680441907</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>11.62926260565432</v>
+        <v>12.11829337899542</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>11.52442190183314</v>
+        <v>11.98540927383382</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>12.42524478960679</v>
+        <v>12.88480300782892</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>12.61209059957481</v>
+        <v>13.09938945288791</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>12.75447593845809</v>
+        <v>13.21687645835648</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>16.10328751129557</v>
+        <v>16.56637147064777</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>17.06269373062693</v>
+        <v>17.49493746277546</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>16.98686147740366</v>
+        <v>17.332798468486</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 14.68</t>
+          <t>X &gt; 14.66</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.8306976020151851</v>
+        <v>1.296082949308754</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.308928933746678</v>
+        <v>1.050176113604884</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.748958665203496</v>
+        <v>4.634191689132663</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7839721254355396</v>
+        <v>0.8159830387115434</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.887206043132174</v>
+        <v>2.959779737321881</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.448155969066953</v>
+        <v>1.503810117513517</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.741247935583104</v>
+        <v>4.740986169796919</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.715069011155222</v>
+        <v>7.661872178001204</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.756556193069926</v>
+        <v>7.789801087685312</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>11.04868116743995</v>
+        <v>11.0260076569821</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.696724549439274</v>
+        <v>9.685339445779988</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>12.67000766631648</v>
+        <v>12.6345639429216</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>13.98586998970426</v>
+        <v>13.9390266641805</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>16.20381550350157</v>
+        <v>16.11014744145707</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>11.48063155551451</v>
+        <v>11.39573499505588</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>11.2620103473762</v>
+        <v>11.15058740097233</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>8.68906882015483</v>
+        <v>9.433803763440856</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>8.584228116333648</v>
+        <v>9.300919658279255</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>9.613127627339274</v>
+        <v>10.32183349832826</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.6129815673886</v>
+        <v>10.53641994338724</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.88344352950387</v>
+        <v>10.77542705490974</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>14.05963008841997</v>
+        <v>14.73252259747057</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>15.96012106106463</v>
+        <v>16.58906030855541</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>16.69729693792265</v>
+        <v>17.23337292716916</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 15.26</t>
+          <t>X &gt; 15.25</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>114</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.376696746217156</v>
+        <v>3.474917131538525</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4103410004989243</v>
+        <v>0.5974313484662375</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.235479846204768</v>
+        <v>4.605895141311493</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.768139861849754</v>
+        <v>2.259106977590996</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.309542371758624</v>
+        <v>2.860741819947805</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>0.386096478577457</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.356138821334071</v>
+        <v>4.854172361081588</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.709506323949412</v>
+        <v>7.180830865041386</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.750993505864116</v>
+        <v>7.308759774725495</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.486849759652188</v>
+        <v>10.02148020933072</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.006523436901837</v>
+        <v>8.539329259022779</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.2365459632784</v>
+        <v>11.77151923437604</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.7449628437907</v>
+        <v>13.28820606429368</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>16.03265589716867</v>
+        <v>16.54874393268513</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>11.86574066976355</v>
+        <v>12.35781762097552</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>11.5829346092504</v>
+        <v>12.04192865733904</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.940245542448366</v>
+        <v>8.429276315789473</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.835404838627184</v>
+        <v>8.296392210627872</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>9.805682184463798</v>
+        <v>10.26524040268593</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>9.992527994431825</v>
+        <v>10.47982684774492</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>8.572788844009644</v>
+        <v>9.035189363908032</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>12.0057148124251</v>
+        <v>12.46879877177731</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>14.03457548981943</v>
+        <v>14.46681922196796</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>14.83593621905231</v>
+        <v>15.18187321013465</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 15.85</t>
+          <t>X &gt; 15.83</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.128383655798807</v>
+        <v>1.695468509984643</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.091008527166395</v>
+        <v>-1.407581182862081</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.278664731494914</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.604172250513713</v>
+        <v>0.5548463259619183</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2683817779664395</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.429267420551561</v>
+        <v>-1.468540112901238</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.606476203250395</v>
+        <v>2.49828263677081</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.212880143112706</v>
+        <v>5.050505050505045</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>5.178433960189153</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.327605495144766</v>
+        <v>8.191906274493618</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.678588214229762</v>
+        <v>6.559379384336047</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.20753111847408</v>
+        <v>11.04470219176952</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.96898443623335</v>
+        <v>12.78695293146161</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>14.63252094440215</v>
+        <v>15.39586172717136</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>10.12822380066773</v>
+        <v>10.90418353576249</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>9.761072261072258</v>
+        <v>10.51310660220119</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.781001277940945</v>
+        <v>6.599702380952372</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.676160574119763</v>
+        <v>6.466818275790772</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.815128878121008</v>
+        <v>8.586042407698457</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>8.001974688089035</v>
+        <v>8.800628852757441</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.497890058584538</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>10.26819794332929</v>
+        <v>11.01516468656428</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>12.46574957888826</v>
+        <v>13.16356107660456</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>13.35145578720344</v>
+        <v>13.95380303469604</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 16.43</t>
+          <t>X &gt; 16.42</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>100</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.35915288656804</v>
+        <v>2.457373271889409</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.975623911781781</v>
+        <v>-1.788533563814468</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.58635703918722</v>
+        <v>2.956772334293944</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.873403019744487</v>
+        <v>3.364370135485728</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.537612547197213</v>
+        <v>3.088811995386394</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2754212667054006</v>
+        <v>0.2457456013844848</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.952630049404242</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.674418604651166</v>
+        <v>5.14574314574314</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.71590578656587</v>
+        <v>6.273672055427248</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.942990110529379</v>
+        <v>9.47762056020791</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.217049752691302</v>
+        <v>6.749855574812244</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.93830034924331</v>
+        <v>11.47327362034095</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.81513828238719</v>
+        <v>13.35838150289018</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>15.5940594059406</v>
+        <v>16.11014744145707</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.93591610836004</v>
+        <v>10.42799305957201</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>10.53030303030303</v>
+        <v>10.98929707839167</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>7.396385893325558</v>
+        <v>7.885416666666664</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>8.291545189504376</v>
+        <v>8.752532561505063</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>10.5074365704287</v>
+        <v>10.96699478865084</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>10.69428238039673</v>
+        <v>11.18158123370982</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>9.151736212430698</v>
+        <v>9.614136732329086</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>12.0758902510216</v>
+        <v>12.5389742103738</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>13.35036496350365</v>
+        <v>13.78260869565218</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>13.27453271028038</v>
+        <v>13.62046970136272</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 17.02</t>
+          <t>X &gt; 17</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>94</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.678301822738248</v>
+        <v>1.776522208059617</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.039453699015823</v>
+        <v>-4.85236335104851</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.09449402464255741</v>
+        <v>0.2759212704641669</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2563817431487365</v>
+        <v>0.7473488588899784</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.07940872939853705</v>
+        <v>0.4717907187906434</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.020102117769241</v>
+        <v>-1.498935249679356</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.527098134510624</v>
+        <v>3.025131674258141</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.376546264225631</v>
+        <v>4.847870805317605</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.545693020608425</v>
+        <v>7.103459289469804</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.96426670627406</v>
+        <v>9.498897155952591</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.983007199499809</v>
+        <v>5.515813021620751</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.959576944987987</v>
+        <v>9.494550216085628</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.02790423983399</v>
+        <v>11.57114746033698</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.99831472508953</v>
+        <v>14.514402760606</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.021022491338762</v>
+        <v>8.513099442550732</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>8.615409413281753</v>
+        <v>9.074403461370395</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.290002914602155</v>
+        <v>5.779033687943262</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.248991998015015</v>
+        <v>6.709979370015702</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>9.65637274064148</v>
+        <v>10.11593095886361</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>10.90704833784353</v>
+        <v>11.39434719115663</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>10.3645021698775</v>
+        <v>10.82690268977589</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>13.48014557017053</v>
+        <v>13.94322952952273</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>12.69079049541855</v>
+        <v>13.12303422756708</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>12.61495824219528</v>
+        <v>12.96089523327762</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 17.61</t>
+          <t>X &gt; 17.59</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>93</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.197862563987385</v>
+        <v>1.296082949308754</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.513258320383933</v>
+        <v>-4.32616797241662</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5749332833934204</v>
+        <v>-0.2045179882866961</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2126184856318645</v>
+        <v>0.2783486301093774</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.548408958179138</v>
+        <v>0.00279049001004239</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.511980406490359</v>
+        <v>-1.990813538400474</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.092414995640802</v>
+        <v>2.590448535388319</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.964741185296326</v>
+        <v>4.4360657263883</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.15676600161963</v>
+        <v>6.714532270481008</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.582641150540766</v>
+        <v>5.115446972661708</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.70761140066676</v>
+        <v>11.25085462116974</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.71233897583308</v>
+        <v>14.22842701134955</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7.677851592231001</v>
+        <v>8.169928543442971</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.272238514173992</v>
+        <v>8.731232562262633</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.912514925583622</v>
+        <v>5.401545698924728</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.882943038966744</v>
+        <v>6.343930410967431</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>9.324640871503981</v>
+        <v>9.784199089726116</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>10.5867554986763</v>
+        <v>11.07405435198939</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10.04420933071027</v>
+        <v>10.50660985060865</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>13.19416982091408</v>
+        <v>13.65725378026628</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>12.39337571619183</v>
+        <v>12.82561944834035</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>12.31754346296855</v>
+        <v>12.66348045405089</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 18.19</t>
+          <t>X &gt; 18.17</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>89</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.415332661848936</v>
+        <v>1.513553047170305</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.537421664590774</v>
+        <v>-4.350331316623461</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.481058691149855</v>
+        <v>-1.11064339604313</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.194012710592595</v>
+        <v>-1.703045594851353</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.529803183139869</v>
+        <v>-1.978603734950688</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.590028008278438</v>
+        <v>-4.068861140188552</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2560008359210926</v>
+        <v>0.7540343756686099</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.224980402403979</v>
+        <v>2.696304943495953</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.513658595554631</v>
+        <v>5.071424864416009</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.111529436372081</v>
+        <v>7.646159886050611</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.891207056062093</v>
+        <v>3.424012878183035</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.106839675086007</v>
+        <v>7.641812946183649</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.354464125083815</v>
+        <v>9.897707345586802</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.50417176549117</v>
+        <v>13.02025980100763</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.228050939820712</v>
+        <v>6.720127891032682</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>6.822437861763703</v>
+        <v>7.281431909852344</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.317734207932297</v>
+        <v>3.806764981273403</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.336489009729092</v>
+        <v>4.79747638172978</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>7.923166907507358</v>
+        <v>8.382725125729493</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>9.233608223093356</v>
+        <v>9.720907076406448</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.691062055127325</v>
+        <v>9.153462575025713</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>11.98600261057216</v>
+        <v>12.44908656992437</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>11.13688181743623</v>
+        <v>11.56912554958476</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>11.06104956421296</v>
+        <v>11.4069865552953</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 18.78</t>
+          <t>X &gt; 18.76</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>83</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.190478187772847</v>
+        <v>4.288698573094216</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.168394996119133</v>
+        <v>-1.98130464815182</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.00804378617517898</v>
+        <v>0.3784590812819033</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7049102332675616</v>
+        <v>-0.2139431175263198</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.040700705814835</v>
+        <v>-0.4895012576256548</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.263373073934318</v>
+        <v>-2.742206205844433</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.988774627717497</v>
+        <v>2.486808167465014</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.120201737181283</v>
+        <v>4.591526278273257</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.571327473312849</v>
+        <v>7.129093742174227</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9.412869628601669</v>
+        <v>9.9475000782802</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.867652162329861</v>
+        <v>5.400457984450803</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.408179867315596</v>
+        <v>9.943153138413237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.89947563178477</v>
+        <v>12.44271885228776</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.29285458666348</v>
+        <v>15.80894262217995</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.610614903540757</v>
+        <v>9.102691854752727</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>10.40982110259219</v>
+        <v>10.86881515068083</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>5.456626857180979</v>
+        <v>5.945657630522085</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>6.556605430468238</v>
+        <v>7.017592802468926</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>10.38695464271786</v>
+        <v>10.84651286094</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>11.77861972979431</v>
+        <v>12.26591858310741</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>11.23607356182828</v>
+        <v>11.69847408172667</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>14.77468543174448</v>
+        <v>15.23776939109668</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>13.84434086711811</v>
+        <v>14.27658459926663</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>13.76850861389483</v>
+        <v>14.11444560497717</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 19.36</t>
+          <t>X &gt; 19.34</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.431616654683978</v>
+        <v>1.529837040005347</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-4.513171244973883</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.790454555015664</v>
+        <v>-1.42003925990894</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.401959299096092</v>
+        <v>-4.91099218335485</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.187025133962202</v>
+        <v>-6.635825685773021</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.898609672502509</v>
+        <v>-9.377442804412624</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-3.42418154479865</v>
+        <v>-2.926148005051132</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>-0.3325177238220789</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2.136195641638331</v>
+        <v>2.693961910499709</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.160381414877207</v>
+        <v>7.695011864555738</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>3.086614970082614</v>
+        <v>3.619420792203556</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.38035567369153</v>
+        <v>10.92359889419452</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>14.50710288420146</v>
+        <v>15.02319091971793</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.715226473035699</v>
+        <v>3.204257246376805</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.610385769214517</v>
+        <v>3.071373141215204</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>8.810224409382243</v>
+        <v>9.297523262695336</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.267678241416213</v>
+        <v>8.730078761314601</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12.53965836696363</v>
+        <v>13.00274232631583</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>11.36485771712684</v>
+        <v>11.79710144927537</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>11.28902546390356</v>
+        <v>11.6349624549859</v>
       </c>
     </row>
   </sheetData>
@@ -5824,165 +5824,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 2.37</t>
+          <t>X &lt; 2.372</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.814760156910225</v>
+        <v>-5.716539771588856</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.94663840453541</v>
+        <v>-11.75954805656809</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16.28320817820408</v>
+        <v>-15.91279288309735</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.54688683532797</v>
+        <v>-15.05591971958673</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.43340194555641</v>
+        <v>-13.88220249736723</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.24643575945903</v>
+        <v>-13.72526889136915</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-17.91693516798706</v>
+        <v>-17.41890162823955</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-22.54297269969666</v>
+        <v>-22.07164815860469</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-23.9507608801008</v>
+        <v>-23.39299461123942</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-24.72367655613729</v>
+        <v>-24.18904610645876</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-27.34816763861304</v>
+        <v>-26.8153618164921</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-30.52546776669872</v>
+        <v>-29.99049449560108</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-35.99645592051137</v>
+        <v>-35.45321270000838</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-39.11608552159564</v>
+        <v>-38.59999748607916</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-38.32495345685735</v>
+        <v>-37.83287650564538</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-37.73056653491436</v>
+        <v>-37.27157248682572</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-39.31375903421068</v>
+        <v>-38.82472826086956</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-37.96932437571301</v>
+        <v>-37.50833700371233</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-37.75343299478869</v>
+        <v>-37.29387477656655</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-36.11731182250182</v>
+        <v>-35.63001296918873</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-36.65985799046786</v>
+        <v>-36.19745747056946</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-36.73570395187696</v>
+        <v>-36.27261999252475</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-37.91050460171374</v>
+        <v>-37.47826086956521</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-36.53706149261818</v>
+        <v>-36.19112450153584</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 2.956</t>
+          <t>X &lt; 2.957</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.433117644832926</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-4.30399748134024</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.138280641972187</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.783601811173391</v>
+        <v>-7.182021617091593</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-11.05175943347911</v>
+        <v>-10.03489934481979</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.38170145994212</v>
+        <v>-10.39342965634748</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-10.67055835639286</v>
+        <v>-11.70397558610597</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-11.91495337602516</v>
+        <v>-13.03982386456614</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.28892513130852</v>
+        <v>-14.97375062498512</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-14.5787490199054</v>
+        <v>-15.76980212020446</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-16.72014831494155</v>
+        <v>-18.07488669322899</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-16.03271414351032</v>
+        <v>-17.83600473017452</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.67278442292682</v>
+        <v>-17.91996901257374</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-16.4107715119338</v>
+        <v>-17.1372752389553</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-14.65345587231629</v>
+        <v>-14.72664611568572</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-15.50834431269214</v>
+        <v>-15.19626993191761</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-18.05772038686768</v>
+        <v>-17.36200601374571</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-18.64565287812847</v>
+        <v>-16.97942620138154</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-19.87903685952299</v>
+        <v>-17.79589180928731</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-19.69219104955496</v>
+        <v>-17.58130536422833</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-19.75164543008137</v>
+        <v>-17.11782203055751</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-18.37821602917164</v>
+        <v>-16.67752063498703</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-17.62064952924997</v>
+        <v>-15.91842223218287</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-16.24720642015441</v>
+        <v>-15.56509730894656</v>
       </c>
     </row>
     <row r="8">
@@ -5992,2293 +5992,2293 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.007595279691138</v>
+        <v>-5.089018480687919</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.320367188065397</v>
+        <v>-5.850389233917561</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.06889968452915</v>
+        <v>-4.270031789417395</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.759848813996342</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.318133174074184</v>
+        <v>-7.199847798428038</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.642169432964579</v>
+        <v>-6.785182233667072</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.169619339348813</v>
+        <v>-7.580264245899791</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.714334451583561</v>
+        <v>-7.11198881301975</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.628837489717746</v>
+        <v>-8.530451655912955</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-9.401753165754236</v>
+        <v>-9.326503151132293</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.35018741112287</v>
+        <v>-10.08519597157951</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-10.38443803706476</v>
+        <v>-9.846314008525027</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.75209888142699</v>
+        <v>-10.9612061259758</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-12.95117286789804</v>
+        <v>-11.98263606369758</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-13.36481738797248</v>
+        <v>-12.14932652805686</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-13.50392679854782</v>
+        <v>-12.36121838552585</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.37134026804364</v>
+        <v>-13.75375859106529</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-13.00918830682814</v>
+        <v>-12.59798290241246</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-12.79329692590382</v>
+        <v>-11.61032479897803</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-12.60645111593579</v>
+        <v>-11.91120227144482</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-11.92650339637126</v>
+        <v>-10.67452306148535</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-11.75785058027424</v>
+        <v>-11.00741754220352</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-12.46137097781664</v>
+        <v>-11.27924697445091</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-11.31470934350936</v>
+        <v>-10.66819009245172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 4.128</t>
+          <t>X &lt; 4.127</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1490194759876857</v>
+        <v>-0.5380042319626739</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7809730945455229</v>
+        <v>-0.7839110676665442</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4359312223283709</v>
+        <v>-0.1896067103901729</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5545316013550661</v>
+        <v>-0.1656760894757525</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.524794585046472</v>
+        <v>-2.136149483812375</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.823712499989206</v>
+        <v>-3.52004792712092</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.595661183879557</v>
+        <v>-4.623296349214961</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.616814679152689</v>
+        <v>-5.698632817276888</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.723915907342011</v>
+        <v>-5.416620702662122</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.348243173274476</v>
+        <v>-6.21267219788146</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.262890811944658</v>
+        <v>-7.019019617791756</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.650109754768586</v>
+        <v>-6.217019137748423</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.476095001416667</v>
+        <v>-6.715578435476544</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.440115928383328</v>
+        <v>-7.734228521562962</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.949670815859875</v>
+        <v>-8.108216493586696</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-9.09822594443694</v>
+        <v>-8.317328499420341</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-9.380731491518425</v>
+        <v>-8.575292116076014</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-9.485572195339607</v>
+        <v>-8.862259426168279</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.566857634623304</v>
+        <v>-8.493713994091841</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-10.71730751559139</v>
+        <v>-9.974042803270144</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-10.21973481282933</v>
+        <v>-9.154738460274913</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-10.14699236413442</v>
+        <v>-9.383984187160863</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-10.46687129206842</v>
+        <v>-9.448516111743814</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-9.502584674563607</v>
+        <v>-8.840239081379963</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 4.714</t>
+          <t>X &lt; 4.712</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>925</v>
+        <v>903</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.01922549181034583</v>
+        <v>-0.2757385775015138</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.07843014227227485</v>
+        <v>0.1428064140371461</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6944651472953396</v>
+        <v>0.9922097650802257</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.846375992717455</v>
+        <v>1.396485307135784</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6786036690190045</v>
+        <v>-0.0972345162415138</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4916374829216252</v>
+        <v>-0.05104288145051328</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.047369950595751</v>
+        <v>-0.7353829224761483</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.217473287240722</v>
+        <v>-0.9295613946776839</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.392202321542243</v>
+        <v>-0.8016324849935756</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.192145024605757</v>
+        <v>-0.7117482105562161</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.56673403109248</v>
+        <v>-0.9932230519873144</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.088726677783725</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.319996852747948</v>
+        <v>-1.388019383045588</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.081616269735079</v>
+        <v>-2.189963300514144</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-2.766786594342662</v>
+        <v>-1.764697970328321</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.929156429156428</v>
+        <v>-1.978587749958272</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-3.387397890458224</v>
+        <v>-2.525436046511629</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.492238594279407</v>
+        <v>-2.769062122880314</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.600671537679411</v>
+        <v>-2.55459989573454</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.062474376360029</v>
+        <v>-3.225949220332254</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.091507030812544</v>
+        <v>-2.021522182399593</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-2.843028667897315</v>
+        <v>-1.985942733147795</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.325310712172026</v>
+        <v>-2.296018103904849</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.184926749179084</v>
+        <v>-2.458157098194313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 5.3</t>
+          <t>X &lt; 5.298</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1191</v>
+        <v>1165</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.019102508734285</v>
+        <v>0.8779741302584938</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.607919329192192</v>
+        <v>1.747947122880809</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.101050574031888</v>
+        <v>2.467501948027852</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.227727117141633</v>
+        <v>2.81930575780332</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.724010532083867</v>
+        <v>2.286236888090258</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.575124493160246</v>
+        <v>1.928149034860873</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.390917203056631</v>
+        <v>1.733925391726864</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.448557983324548</v>
+        <v>1.772352587803226</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.574008221494495</v>
+        <v>2.071955317229822</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.724686164265734</v>
+        <v>2.220109830594176</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.914782750172414</v>
+        <v>2.49234484519851</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.391700853021646</v>
+        <v>3.074131989439657</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.184575729910279</v>
+        <v>2.045076781860132</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7116076846979453</v>
+        <v>1.453495080942048</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.5572427246488658</v>
+        <v>1.372199068155702</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.2280360277841424</v>
+        <v>1.07513398826292</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2417333342143237</v>
+        <v>0.5420690271816824</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.5984632068012488</v>
+        <v>0.06583728253511367</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.7184240508979158</v>
+        <v>0.1944625998096328</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.119319634716618</v>
+        <v>-0.3634831439725872</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.7382721838749262</v>
+        <v>0.1849521829728644</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.9820442577945201</v>
+        <v>-0.2335579784674024</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.379273995354453</v>
+        <v>-0.5049449524164871</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.203217079811978</v>
+        <v>-0.5812470368347107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 5.886</t>
+          <t>X &lt; 5.883</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1468</v>
+        <v>1449</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5964410221612511</v>
+        <v>0.4463691453419543</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.820986257709741</v>
+        <v>2.164666711478034</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.145679073085539</v>
+        <v>2.601400433467511</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.975097934998729</v>
+        <v>2.600069653059819</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.842697292959926</v>
+        <v>2.39342950055525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.62288381804035</v>
+        <v>2.067937193389987</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.86788428669238</v>
+        <v>2.278249796048314</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.928655892786757</v>
+        <v>2.249191421605211</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.698956634023503</v>
+        <v>2.239189296806551</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.576640042686776</v>
+        <v>1.994861939518259</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.619629521869847</v>
+        <v>2.060200402398451</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.816100756575281</v>
+        <v>2.335342585858193</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.828716014905865</v>
+        <v>1.537815595367746</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6484072320275516</v>
+        <v>1.289581533934637</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.5069562171295843</v>
+        <v>1.15953205198057</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.3262213976499666</v>
+        <v>0.8926787209037457</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.3691564855651777</v>
+        <v>0.8578114216701209</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.03543028733485443</v>
+        <v>0.3108486415602698</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1601383614514091</v>
+        <v>0.387284643723298</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.6544914615651223</v>
+        <v>-0.2262862611141898</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.5158387194494125</v>
+        <v>0.03442658740154769</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.72792446287486</v>
+        <v>-0.3167883845192279</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.06652876946638</v>
+        <v>-0.5562456866804695</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.142361022689656</v>
+        <v>-0.8564109059526785</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 6.472</t>
+          <t>X &lt; 6.468</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1696</v>
+        <v>1684</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5477879187883019</v>
+        <v>0.5161968013011631</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.443239591440246</v>
+        <v>1.596987330829442</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.70410747855454</v>
+        <v>2.082802958557785</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9911534591117999</v>
+        <v>1.347281154931807</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.006856835422163</v>
+        <v>1.307433091438249</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.8423291726619055</v>
+        <v>0.9929465442247789</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.007697419058609</v>
+        <v>1.174720192925349</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.291065732435456</v>
+        <v>1.375831641318356</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.308281153134786</v>
+        <v>1.538134865344595</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.156605134003556</v>
+        <v>1.367165746268157</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9369558008416305</v>
+        <v>1.201392217838247</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.045233369219801</v>
+        <v>1.373332756946503</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.07439754164644086</v>
+        <v>0.4708075383931387</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1118229470005829</v>
+        <v>0.2575719530023548</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3819179116517262</v>
+        <v>0.08439116383741663</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.7535603383659932</v>
+        <v>-0.3859252096936814</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.029660070139386</v>
+        <v>-0.6922820284697551</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.335813301061663</v>
+        <v>-1.146577230779798</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.237846448439228</v>
+        <v>-0.8727678226251285</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.463736487527804</v>
+        <v>-1.192306006646255</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.47562227813534</v>
+        <v>-1.04758433592017</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.964204088601051</v>
+        <v>-1.681928402452805</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.220389753477477</v>
+        <v>-1.79458845399153</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-2.060372950096976</v>
+        <v>-1.897345025478138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 7.058</t>
+          <t>X &lt; 7.053</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1909</v>
+        <v>1899</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3174862199013617</v>
+        <v>0.2594566052227307</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8681260882182187</v>
+        <v>1.031685300177195</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8884403725205559</v>
+        <v>1.213289539716271</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6442363530778223</v>
+        <v>1.119717031677702</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7771958805305488</v>
+        <v>1.186933080981383</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6516620666279209</v>
+        <v>0.9559283690084968</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7651300494042417</v>
+        <v>1.078667768880081</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.09026018880958</v>
+        <v>1.326610892737385</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.214341657264512</v>
+        <v>1.589571637017208</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.150084528891405</v>
+        <v>1.451979534566888</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.037509042879186</v>
+        <v>1.388599030309621</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.363887816606237</v>
+        <v>1.718951985977405</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.7942396407988923</v>
+        <v>1.211630978781166</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8136098502688824</v>
+        <v>1.204536534273004</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.5530709200755197</v>
+        <v>0.9736383901071548</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1849341135055482</v>
+        <v>0.5693495718299886</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.07481829515612048</v>
+        <v>0.2341561624649842</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.305626104366759</v>
+        <v>-0.07773543639298452</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.2992685107656357</v>
+        <v>0.1152597728779625</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.5314902754440283</v>
+        <v>-0.1650784191044892</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5502019751020413</v>
+        <v>-0.01744221503933119</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.9927320643267521</v>
+        <v>-0.5879346890469392</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.189708373321913</v>
+        <v>-0.7129152643267602</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.108390286052781</v>
+        <v>-0.822394964250762</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 7.644</t>
+          <t>X &lt; 7.639</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2112</v>
+        <v>2128</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4005062700266819</v>
+        <v>0.3857786647299406</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3732242311425296</v>
+        <v>0.6300710873483268</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7951999366472506</v>
+        <v>0.9828309662157793</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5792853726856606</v>
+        <v>0.8355060758954096</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4317301942560405</v>
+        <v>0.58625028136683</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5513207295281148</v>
+        <v>0.5831174559977157</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8424086645714581</v>
+        <v>0.8865610250491898</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8742301032374087</v>
+        <v>0.9349222502207581</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8488619393240029</v>
+        <v>0.9498269784323767</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8109146388312638</v>
+        <v>0.880981904745731</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7824107720400519</v>
+        <v>0.9002525855548811</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.333956628752276</v>
+        <v>1.491965209125993</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8056909512582351</v>
+        <v>1.059176266798545</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.038293810477462</v>
+        <v>1.30659271741591</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.8342612620243415</v>
+        <v>1.167347294480756</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4167741750523177</v>
+        <v>0.7739412731482247</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.4058511086592063</v>
+        <v>0.6980630366900797</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3767724622316493</v>
+        <v>0.6400677067721645</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2138759643680928</v>
+        <v>0.6481949761801431</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.06928238039672863</v>
+        <v>0.4217313275184509</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.09491803061251858</v>
+        <v>0.5859809369278679</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.3123673247359804</v>
+        <v>0.1164389991061938</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.6060744304357399</v>
+        <v>-0.08164682337083917</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.4925127442650847</v>
+        <v>-0.02802653923878751</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 8.23</t>
+          <t>X &lt; 8.224</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2353</v>
+        <v>2370</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3675917051334281</v>
+        <v>0.3228141410912428</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.09782480075514854</v>
+        <v>0.3084564027407168</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3296002824304693</v>
+        <v>0.5402102263893056</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1471672782996265</v>
+        <v>0.3894747379961814</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.08875371372300123</v>
+        <v>0.2629434311335714</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3419148855144698</v>
+        <v>0.4434005427580061</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5668432473737823</v>
+        <v>0.6773079125702779</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.5246090405377473</v>
+        <v>0.6059275547959473</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4212402488859368</v>
+        <v>0.5483051791169729</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3927995133248032</v>
+        <v>0.4893655266508645</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1407785662506313</v>
+        <v>0.2823776058655341</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3952736430118478</v>
+        <v>0.5757085489723437</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1874877310725154</v>
+        <v>0.4511996465273</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5007204156987655</v>
+        <v>0.7740129876755546</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.4197870761019757</v>
+        <v>0.7474550183782327</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.5727658753136424</v>
+        <v>0.9136032180047877</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.506836190691736</v>
+        <v>0.7928630276258559</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.5975375396956153</v>
+        <v>0.8535426625151601</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.5159363579340095</v>
+        <v>0.9248895254929437</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.362790667689552</v>
+        <v>0.7013790433138709</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.4577285626219378</v>
+        <v>0.9175501330876159</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.2118868511065912</v>
+        <v>0.6148595392102223</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.01887325079647439</v>
+        <v>0.5042451359727167</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.02803887262631122</v>
+        <v>0.4516933300547024</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 8.816</t>
+          <t>X &lt; 8.809</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2565</v>
+        <v>2583</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.07771775634444111</v>
+        <v>-0.0890580404666963</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3917416955865036</v>
+        <v>-0.1608944083442125</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1810848212778922</v>
+        <v>0.06429921601437627</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01919596274564839</v>
+        <v>0.2998292211561093</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4887644892651579</v>
+        <v>-0.2616876202938556</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.357687467714328</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1374320623970036</v>
+        <v>-0.01087487238670093</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.08286294874690014</v>
+        <v>0.05224564670504606</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3687872981272093</v>
+        <v>-0.1828329484218614</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4588754160932353</v>
+        <v>-0.3025103600847387</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5512239642604868</v>
+        <v>-0.3549210045406141</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5354452750273992</v>
+        <v>-0.3012928536474959</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.7412819510758411</v>
+        <v>-0.4303617507721214</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5892804150014044</v>
+        <v>-0.2704927436567033</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.7182894991165938</v>
+        <v>-0.3513279280823127</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.6851235376751532</v>
+        <v>-0.3074995252362669</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.7181893210158279</v>
+        <v>-0.3887146074646139</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.8780454537704827</v>
+        <v>-0.5761657776220162</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.013031265828609</v>
+        <v>-0.5708722901745134</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.021117229739723</v>
+        <v>-0.6429259174305031</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.01785443084416</v>
+        <v>-0.530488170996513</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.093700392253261</v>
+        <v>-0.660252095235478</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.17010287275366</v>
+        <v>-0.6647597254004509</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.206948771201112</v>
+        <v>-0.7655155870615928</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 9.402</t>
+          <t>X &lt; 9.394</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2721</v>
+        <v>2739</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.08375116304889474</v>
+        <v>-0.06688451232493975</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.508470627110249</v>
+        <v>-0.2209855739557227</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3570529644637332</v>
+        <v>-0.07945954976402447</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1368234229143894</v>
+        <v>0.1816952532820295</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5252299811184571</v>
+        <v>-0.2549153432647984</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3543686351264554</v>
+        <v>-0.1503370972009392</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2649202248187947</v>
+        <v>-0.09070070692951759</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2297511100525682</v>
+        <v>-0.04844923175232907</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4235014582200876</v>
+        <v>-0.1903802321544532</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3703334619450018</v>
+        <v>-0.1667673802207048</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4413171458806531</v>
+        <v>-0.2370630298389145</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.4426520317090805</v>
+        <v>-0.165766728623062</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4820401712588307</v>
+        <v>-0.1688912243825484</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.498315960628311</v>
+        <v>-0.1412166909547139</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5481322964804463</v>
+        <v>-0.1833606522183757</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.592220814157713</v>
+        <v>-0.2192941119978471</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.7045315378671049</v>
+        <v>-0.3745978999757256</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8244606842107487</v>
+        <v>-0.486083103340107</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.8655443399971503</v>
+        <v>-0.3959789722821085</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.009095005800042</v>
+        <v>-0.597492772852334</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.074401819874737</v>
+        <v>-0.5601885776636237</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.165387751181854</v>
+        <v>-0.7233388140698267</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.346916447223755</v>
+        <v>-0.8597270707711786</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.254316977334469</v>
+        <v>-0.8910308462824119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 9.988</t>
+          <t>X &lt; 9.979</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2865</v>
+        <v>2883</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.07436511897213194</v>
+        <v>-0.032647375047965</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3213114767280985</v>
+        <v>-0.01917039686093602</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2507877979576136</v>
+        <v>0.0531910670763196</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.147394207291903</v>
+        <v>0.2031575967327157</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5331225429553541</v>
+        <v>-0.2254540280457178</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>-0.1182668081294835</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3159334481668949</v>
+        <v>-0.1010605487792802</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3314821242624078</v>
+        <v>-0.1105521284893527</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2702053245452447</v>
+        <v>-0.03205603290953007</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2244291322632535</v>
+        <v>-0.01461278463158067</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.208245591297576</v>
+        <v>0.03576717702219412</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3279492162763376</v>
+        <v>-0.01377301178339962</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2836099790870819</v>
+        <v>0.06605254642852998</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3798536375376642</v>
+        <v>-0.02362373033692222</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.5303330217721722</v>
+        <v>-0.1321729155317257</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.5417470915208469</v>
+        <v>-0.1037503100552328</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6203271985964491</v>
+        <v>-0.2564518454440616</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.63496125424345</v>
+        <v>-0.2997346589864591</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.7120756246932558</v>
+        <v>-0.2726173997148109</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.6790184212763251</v>
+        <v>-0.314781772871406</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7129778740407104</v>
+        <v>-0.2729041547117959</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.8379569760450281</v>
+        <v>-0.4315630513246376</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.101135385414707</v>
+        <v>-0.6875716094795834</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.086723834222248</v>
+        <v>-0.7253506246865413</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 10.57</t>
+          <t>X &lt; 10.56</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3013</v>
+        <v>3038</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.05059678405120138</v>
+        <v>-0.03070252033536036</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1370736646648112</v>
+        <v>0.1003553250744176</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1071169225794222</v>
+        <v>0.170894596471129</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.01054027072699881</v>
+        <v>0.3159724899657874</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4597489303753477</v>
+        <v>-0.1702655316008546</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.320290946679016</v>
+        <v>-0.09325963421761685</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2486900826089595</v>
+        <v>-0.05179140266493931</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3430789192841246</v>
+        <v>-0.1417486682712692</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.183697912245222</v>
+        <v>0.0702655700030661</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1779216833259198</v>
+        <v>0.04642789965745919</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1160632677977986</v>
+        <v>0.1408749127342332</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.07822857637652447</v>
+        <v>0.2109785383737304</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1240151567662551</v>
+        <v>0.2301427360813832</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3586365914130312</v>
+        <v>0.001223556942626658</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3023367043467786</v>
+        <v>0.09323756236163661</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.3502001143510611</v>
+        <v>0.05036076847702731</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.2658657623035765</v>
+        <v>0.09723932676518388</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2185574935032477</v>
+        <v>0.1152132448164949</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.2148961002141121</v>
+        <v>0.2177341905568539</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1409844409489764</v>
+        <v>0.2216864276611759</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1334096761634669</v>
+        <v>0.2984511026020229</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.3221196992271587</v>
+        <v>0.04555315774221924</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4923689449236903</v>
+        <v>-0.08609811579896132</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.5817567022652597</v>
+        <v>-0.2616896139763227</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 11.16</t>
+          <t>X &lt; 11.15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3096</v>
+        <v>3119</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.0659833750542802</v>
+        <v>-0.04167192225445859</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.06285931909415865</v>
+        <v>0.1751722623555381</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.03988614336009277</v>
+        <v>0.2433965381156042</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.0993337001039265</v>
+        <v>0.4650391383528856</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1863039857080793</v>
+        <v>0.1117565460556094</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.01337887749538424</v>
+        <v>0.2227937365454551</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.02841717192566051</v>
+        <v>0.1789799156823761</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1919053028038533</v>
+        <v>0.01974633553580674</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.03562105367841895</v>
+        <v>0.2615469756569908</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.05057902130342029</v>
+        <v>0.1858873971054464</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.01698542332493957</v>
+        <v>0.2849769030370268</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.01794160699865444</v>
+        <v>0.282280327463269</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.02811887886160491</v>
+        <v>0.3360172856377801</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.262347548341431</v>
+        <v>0.1066319412972732</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.225114487453169</v>
+        <v>0.1786324457612736</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3524289284598581</v>
+        <v>0.05549471190622057</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.4350675388368686</v>
+        <v>-0.06148032629559452</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3274103230681504</v>
+        <v>0.01653256150505911</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.3503512399550459</v>
+        <v>0.08991412283777578</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4024918131516628</v>
+        <v>-0.02879340605963421</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4420037036712685</v>
+        <v>-0.0008536584460543395</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6923473216059008</v>
+        <v>-0.313316722019664</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7539295150239553</v>
+        <v>-0.3391861761426895</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.7138393827428757</v>
+        <v>-0.3862632258575402</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 11.75</t>
+          <t>X &lt; 11.74</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3153</v>
+        <v>3178</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1143987507115654</v>
+        <v>-0.09058049255921219</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2433404472148482</v>
+        <v>-0.007283563814468152</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3411791926968277</v>
+        <v>-0.05729456161101609</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.217362817003071</v>
+        <v>0.117966132984165</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3463723203942166</v>
+        <v>-0.04631468587728449</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.141709503854571</v>
+        <v>0.09680943117170671</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2019440830878736</v>
+        <v>0.007784089934233407</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3044390791607654</v>
+        <v>-0.09157682920989885</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1502558295957428</v>
+        <v>0.1167663241400589</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1473161730197177</v>
+        <v>0.09040251509512842</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1076501841374977</v>
+        <v>0.1613253335085787</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2733900141058214</v>
+        <v>0.02813255451022911</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2404875077518724</v>
+        <v>0.1228844818804475</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4429307932373945</v>
+        <v>-0.0755489198980186</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.2917878764596864</v>
+        <v>0.1079428556184467</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.3112028222752627</v>
+        <v>0.09161974003636431</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.2681710686997505</v>
+        <v>0.1004873103087434</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.2276064407583647</v>
+        <v>0.1118290439171261</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.2778705859994162</v>
+        <v>0.1564387094802484</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.2939976322735234</v>
+        <v>0.07535873213847566</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3425603655160643</v>
+        <v>0.09228825700685661</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5263284494538354</v>
+        <v>-0.1528496889972715</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.6451962286333099</v>
+        <v>-0.2365797283805335</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6071672580037912</v>
+        <v>-0.2857606321803985</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 12.33</t>
+          <t>X &lt; 12.32</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3193</v>
+        <v>3216</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.03388193930261707</v>
+        <v>-0.03845877503866291</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1031511279559609</v>
+        <v>0.1336406177791076</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3109671674089185</v>
+        <v>-0.02314734442091293</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1975586982760547</v>
+        <v>0.1431093196637221</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4225368924042812</v>
+        <v>-0.1152065517542482</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3115470842077457</v>
+        <v>-0.06470585192411704</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4430085798792405</v>
+        <v>-0.2239420402945811</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.6100937044794108</v>
+        <v>-0.3876726958410188</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5509271311398649</v>
+        <v>-0.2732174524650475</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5577894342164882</v>
+        <v>-0.3087571487704182</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.515327040820857</v>
+        <v>-0.2355888352218258</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6202019908502976</v>
+        <v>-0.308634682013448</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.664262466676476</v>
+        <v>-0.2902085188018049</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8358500539407672</v>
+        <v>-0.4583584481895571</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.6949396068179752</v>
+        <v>-0.2851852350016415</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6755701343330216</v>
+        <v>-0.2638046585810372</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.634864106674442</v>
+        <v>-0.2563766935567386</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.5962322409426406</v>
+        <v>-0.246846706030631</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.6120130856063213</v>
+        <v>-0.1692982880334242</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6257051078735216</v>
+        <v>-0.2469901948616027</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.6179759277445172</v>
+        <v>-0.1749281946668759</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.8004790760519498</v>
+        <v>-0.4181420108816383</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8831979669910339</v>
+        <v>-0.4670027435769128</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8153514112354401</v>
+        <v>-0.4864954727666344</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 12.92</t>
+          <t>X &lt; 12.91</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3216</v>
+        <v>3239</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.01318425452490146</v>
+        <v>-0.01718221554162369</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1460995140053711</v>
+        <v>0.05997916234314715</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2699914316190828</v>
+        <v>-0.01255281908027683</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1933460531850599</v>
+        <v>0.1483529523006979</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3881988902061835</v>
+        <v>-0.07938935513540457</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2766581250851203</v>
+        <v>-0.02812605965328885</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3817343180563242</v>
+        <v>-0.1611300226418564</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6114724844577424</v>
+        <v>-0.3565610017223051</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5524321892930004</v>
+        <v>-0.2420009623969719</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5957095798731018</v>
+        <v>-0.3136490370868898</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5516092748714172</v>
+        <v>-0.2390743144866434</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.6577343471631423</v>
+        <v>-0.3135611997144139</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7094976023354604</v>
+        <v>-0.3031569586482874</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.912450203482841</v>
+        <v>-0.5026564982166803</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.777262186213612</v>
+        <v>-0.3355537384575484</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8158508158508155</v>
+        <v>-0.3719594661109511</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.8074614538665017</v>
+        <v>-0.3961606592729581</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.7699073244621033</v>
+        <v>-0.3876831549818434</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7530415419587513</v>
+        <v>-0.278381290264079</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7342890481746949</v>
+        <v>-0.3231982914212352</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.6994598111791177</v>
+        <v>-0.2248515465111396</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.8501507682450224</v>
+        <v>-0.4360335032948157</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.899246475725441</v>
+        <v>-0.4519592055823836</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.8635269912121615</v>
+        <v>-0.5033339417370044</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 13.5</t>
+          <t>X &lt; 13.49</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3235</v>
+        <v>3259</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1110742466425307</v>
+        <v>-0.09960418088329703</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1837909366512847</v>
+        <v>0.03651977358266834</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3460753932452079</v>
+        <v>-0.07371547058409789</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3047843842493663</v>
+        <v>0.02158270029207188</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5004943981008836</v>
+        <v>-0.2064900180364262</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3885476116177955</v>
+        <v>-0.1546205872026505</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4975544524407809</v>
+        <v>-0.2917051532169808</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6660920074681798</v>
+        <v>-0.4573102893713639</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6379403672802866</v>
+        <v>-0.3732430331494143</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7470683690027897</v>
+        <v>-0.5104637660982334</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7324576364712669</v>
+        <v>-0.4653033493931318</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8396485266421223</v>
+        <v>-0.5410950742478633</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9285462524248871</v>
+        <v>-0.5682240016969828</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.039222566324426</v>
+        <v>-0.6763316041226162</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.9087201431812701</v>
+        <v>-0.5144794006483053</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.9436408488212322</v>
+        <v>-0.5472808218225964</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.9361249024794986</v>
+        <v>-0.5720236272708803</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.930299920029718</v>
+        <v>-0.5950937784643031</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9740449110527862</v>
+        <v>-0.5464856035060279</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9543746125023205</v>
+        <v>-0.5897948006144134</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.8921180185760917</v>
+        <v>-0.464955848909419</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.011536378573702</v>
+        <v>-0.6447117755201006</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.058782131675585</v>
+        <v>-0.6591090957588719</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.9928552340782062</v>
+        <v>-0.6805428791834629</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 14.09</t>
+          <t>X &lt; 14.08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3254</v>
+        <v>3279</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1773133935662372</v>
+        <v>-0.1507430212662655</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2515701877280563</v>
+        <v>-0.01694919544125639</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4518108997440677</v>
+        <v>-0.164439786918166</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3538419405487332</v>
+        <v>-0.01271382935210141</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4892741011376458</v>
+        <v>-0.1804420980035388</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3463259121821807</v>
+        <v>-0.097596831129934</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4897423137874384</v>
+        <v>-0.2689966050229984</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6283336889268156</v>
+        <v>-0.4050914521324245</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6306833844344339</v>
+        <v>-0.3511002578696534</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7436683962025654</v>
+        <v>-0.4923156681552854</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.758156858878948</v>
+        <v>-0.4761468553214172</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.8663536617793497</v>
+        <v>-0.5531621134785638</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9306503853004102</v>
+        <v>-0.5565121141311025</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.041970005824112</v>
+        <v>-0.6654682472020994</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8854139559979117</v>
+        <v>-0.478332974491245</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.8860059825725131</v>
+        <v>-0.4770856414136233</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8179655326174071</v>
+        <v>-0.4414244775816627</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8127492890232304</v>
+        <v>-0.4651234506714985</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.8549445280677688</v>
+        <v>-0.4154656254782694</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.8649564164111325</v>
+        <v>-0.4876237617211885</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.8676067412076165</v>
+        <v>-0.4279107996636</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.017475842344496</v>
+        <v>-0.6374963778614884</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.032123515759018</v>
+        <v>-0.6198303287380682</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.9977475601560144</v>
+        <v>-0.6726074563073041</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 14.68</t>
+          <t>X &lt; 14.66</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3277</v>
+        <v>3301</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1559986285834896</v>
+        <v>-0.1431080758843706</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2926896892901212</v>
+        <v>-0.04191905884907499</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4712536339480025</v>
+        <v>-0.1666472924369344</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3486169984538705</v>
+        <v>0.01025992771698014</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4247660935794855</v>
+        <v>-0.09793499256541338</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3725381104079872</v>
+        <v>-0.1049624432072704</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4899929014154338</v>
+        <v>-0.2503611245311888</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5991920846898608</v>
+        <v>-0.3574223652607742</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.601226655718456</v>
+        <v>-0.3029262557910926</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.7188148119865758</v>
+        <v>-0.448472954120902</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.6704882412296769</v>
+        <v>-0.3702409852360375</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7798510645602761</v>
+        <v>-0.4485495006973892</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8211147589753338</v>
+        <v>-0.4290581106363902</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9027461918689497</v>
+        <v>-0.5086988285519922</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.7214180364969351</v>
+        <v>-0.2970824691288954</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.7177943821779493</v>
+        <v>-0.2920568049567791</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.6206664818266958</v>
+        <v>-0.2572677347843566</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.6161611766241606</v>
+        <v>-0.2816373810410511</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.6564878658906181</v>
+        <v>-0.2308273529099694</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.6955377963786447</v>
+        <v>-0.3010208842932016</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.7019223241546726</v>
+        <v>-0.245427432319822</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.8207245705703485</v>
+        <v>-0.4540624229898071</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.863790009040585</v>
+        <v>-0.4651199536512678</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8606519097989676</v>
+        <v>-0.5488729220847191</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 15.26</t>
+          <t>X &lt; 15.25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3286</v>
+        <v>3311</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2410284370947053</v>
+        <v>-0.2132925949372293</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2573651451554255</v>
+        <v>-0.02315702616070325</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4393460149403836</v>
+        <v>-0.1512708829929679</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3794705434739001</v>
+        <v>-0.03671062104384504</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.395821643423055</v>
+        <v>-0.08536217878778274</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3129515330492367</v>
+        <v>-0.06185427845931457</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4624471531388963</v>
+        <v>-0.2392402570020877</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5418139816601695</v>
+        <v>-0.3168357541666893</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5437125109197467</v>
+        <v>-0.2621066577417253</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6327674652281985</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5837989893517417</v>
+        <v>-0.3006859414332439</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6935977708294701</v>
+        <v>-0.379570195488121</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7377886208581899</v>
+        <v>-0.363472801745587</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8501153513409534</v>
+        <v>-0.4737128415902134</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.7014131784381377</v>
+        <v>-0.2948985066930518</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.6961693437103236</v>
+        <v>-0.2881961424579771</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.5692988925839515</v>
+        <v>-0.1935465641953016</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.565076924711903</v>
+        <v>-0.2182241463634966</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6350733049891062</v>
+        <v>-0.1970582873443405</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.6431036378403476</v>
+        <v>-0.2663825671951514</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.5901306163926492</v>
+        <v>-0.1523086508936089</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.708781281825118</v>
+        <v>-0.3303285363814084</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.7509432202505337</v>
+        <v>-0.3405797101449295</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.7479870706082465</v>
+        <v>-0.42453180875507</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 15.85</t>
+          <t>X &lt; 15.83</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3296</v>
+        <v>3320</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1910128259959976</v>
+        <v>-0.1474726748650141</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2082941950849744</v>
+        <v>0.04150832726871556</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3638992164654695</v>
+        <v>-0.05968980279074998</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.336488415719927</v>
+        <v>0.0230527702162675</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3236242552160604</v>
+        <v>-0.02619249697659143</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2404182492038984</v>
+        <v>-0.002307124798861082</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3615866725999837</v>
+        <v>-0.1513741693139252</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.441523424334342</v>
+        <v>-0.229556614448704</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4432606284144924</v>
+        <v>-0.1746038066417128</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5343512791987166</v>
+        <v>-0.2938251506499157</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4846728221047059</v>
+        <v>-0.2144408548307268</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6251821175039751</v>
+        <v>-0.3238452271980705</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6726149682931819</v>
+        <v>-0.3107869150023461</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7550029050091922</v>
+        <v>-0.391354060044435</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6087132411104577</v>
+        <v>-0.2148426268202996</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.601658228776877</v>
+        <v>-0.2066163831467875</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.47554871157908</v>
+        <v>-0.1124793357379019</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4716286445355991</v>
+        <v>-0.1374253458912023</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5407306516252177</v>
+        <v>-0.1157119782664608</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5481418620275207</v>
+        <v>-0.1842430743527501</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4969452061810031</v>
+        <v>-0.07199026135131703</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6154378266012017</v>
+        <v>-0.2497073067845434</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6566110753195247</v>
+        <v>-0.2592461673408977</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6538653479720509</v>
+        <v>-0.3433857203240294</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 16.43</t>
+          <t>X &lt; 16.42</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3300</v>
+        <v>3325</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1951655004316706</v>
+        <v>-0.1674773852193141</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1827280659058061</v>
+        <v>0.05072547412996187</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3699814130861867</v>
+        <v>-0.08208002673413972</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4037054139904512</v>
+        <v>-0.06014406481322965</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3912816980573766</v>
+        <v>-0.0798482916949439</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3079709954576657</v>
+        <v>-0.05577997444561333</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3997968423654257</v>
+        <v>-0.1759073264676303</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4498274749628237</v>
+        <v>-0.2245052828710499</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.481680940432625</v>
+        <v>-0.1993818367883264</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.5736061477687571</v>
+        <v>-0.3196241238292288</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4934845062884818</v>
+        <v>-0.2100006265059164</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6341634188726388</v>
+        <v>-0.3196541591016668</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6828985644868624</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7654572103735973</v>
+        <v>-0.3891029333555238</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5899225135801203</v>
+        <v>-0.1838845649030887</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6123813711479897</v>
+        <v>-0.2048223335495294</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.5168285003847473</v>
+        <v>-0.1409938975590279</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5433005455228468</v>
+        <v>-0.1961315033403324</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6120793145939913</v>
+        <v>-0.1741463524903111</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6192769416371675</v>
+        <v>-0.2422697725983767</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.56882085690021</v>
+        <v>-0.1310555753632272</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6569989070644056</v>
+        <v>-0.2785791409937985</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.6675084082018969</v>
+        <v>-0.2576799393448113</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6345581988105309</v>
+        <v>-0.3118611257049508</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 17.02</t>
+          <t>X &lt; 17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3306</v>
+        <v>3331</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1713367499594511</v>
+        <v>-0.1437000733699918</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.09942198870485441</v>
+        <v>0.1333274561676419</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2889059605122029</v>
+        <v>-0.001461555920840851</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3238308948676547</v>
+        <v>0.01939848523208099</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3120115129531555</v>
+        <v>-0.0007402434195782348</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2585740946235759</v>
+        <v>-0.00626992563851303</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.381706393568976</v>
+        <v>-0.1574606641337795</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4321437072091641</v>
+        <v>-0.2065126056760391</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4939707566440106</v>
+        <v>-0.2110858644771128</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5570098894706277</v>
+        <v>-0.3026484980880539</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4464030945518402</v>
+        <v>-0.1628238510250739</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5571788550966517</v>
+        <v>-0.2428496222555268</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6078342831841113</v>
+        <v>-0.2334796580912695</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6906209318157295</v>
+        <v>-0.3145756953283225</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.516572579422764</v>
+        <v>-0.1109290961166209</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.5378925037947297</v>
+        <v>-0.1307987586852946</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4427327302784292</v>
+        <v>-0.06724960055921514</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4693243757130219</v>
+        <v>-0.1225048972902627</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5677672954728408</v>
+        <v>-0.1301275135074391</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6048112751923966</v>
+        <v>-0.227714118614017</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5856466827037821</v>
+        <v>-0.1477108981448154</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6738074515177033</v>
+        <v>-0.2951091979670366</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6233272046245659</v>
+        <v>-0.2137898637715949</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.590561058624651</v>
+        <v>-0.2681523340620799</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 17.61</t>
+          <t>X &lt; 17.59</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3307</v>
+        <v>3332</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1573636299484846</v>
+        <v>-0.1298100366053845</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1156058883513253</v>
+        <v>0.1172505745278158</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2754218069666194</v>
+        <v>0.01194680491727951</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3105464843132211</v>
+        <v>0.03262789204897132</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2988276211732028</v>
+        <v>0.01241688944787001</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.24534607873548</v>
+        <v>0.006939631235226784</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3686695895849326</v>
+        <v>-0.1444394266738627</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4191715247499701</v>
+        <v>-0.1935639032413263</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4809635692438832</v>
+        <v>-0.1980937049551841</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.544212539274902</v>
+        <v>-0.2898630022547266</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4335526569472492</v>
+        <v>-0.1499949483566709</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5443751554267777</v>
+        <v>-0.2300756619557092</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.595349963544102</v>
+        <v>-0.2210381800293604</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.678174540396455</v>
+        <v>-0.3021805058798606</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5043733970681856</v>
+        <v>-0.09879532713855355</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5255039078568444</v>
+        <v>-0.1184873527460581</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.4304095200721534</v>
+        <v>-0.05498465109315021</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4570210646459429</v>
+        <v>-0.1102595295674362</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.5553653619384491</v>
+        <v>-0.1178119239652773</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5923379759910645</v>
+        <v>-0.2153012602949715</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5733393162702072</v>
+        <v>-0.1354884550772155</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.661492644112883</v>
+        <v>-0.2828614224996286</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.6109409615265804</v>
+        <v>-0.2014897141888028</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5782039090120321</v>
+        <v>-0.255880838853372</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 18.19</t>
+          <t>X &lt; 18.17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3311</v>
+        <v>3336</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1615429742597954</v>
+        <v>-0.1338741231686527</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1202383732279273</v>
+        <v>0.1125980621533671</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2515781348824078</v>
+        <v>0.03571186363562617</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2574886043924067</v>
+        <v>0.08546667898989568</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2461712365865694</v>
+        <v>0.06496698793482381</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1925134865912668</v>
+        <v>0.05969908975657034</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3166007198265319</v>
+        <v>-0.09243214601077909</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3673607761723972</v>
+        <v>-0.141846353063535</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4290130348412262</v>
+        <v>-0.1462026088520716</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4931001150345224</v>
+        <v>-0.2387973502398495</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.09875595101636492</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.493237417834635</v>
+        <v>-0.1790561287630013</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.545487846450861</v>
+        <v>-0.1713466118394393</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6284639304038748</v>
+        <v>-0.2526738376822095</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4556501567002016</v>
+        <v>-0.05033279991977224</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4760241766870266</v>
+        <v>-0.06931536179971687</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3811909602006622</v>
+        <v>-0.005998230132618687</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4078820037425288</v>
+        <v>-0.06135134035011447</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5058324283650251</v>
+        <v>-0.06862328976879439</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5425200328762685</v>
+        <v>-0.1657241555117324</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.524184125529473</v>
+        <v>-0.08667189300783917</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.6123077568262758</v>
+        <v>-0.233943704545311</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.5614707852886198</v>
+        <v>-0.1523628356633751</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5288499535674021</v>
+        <v>-0.2068684281336886</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 18.78</t>
+          <t>X &lt; 18.76</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3317</v>
+        <v>3342</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2276734607373569</v>
+        <v>-0.1993875007703281</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1870644628449725</v>
+        <v>0.04618700693463751</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2908149200698205</v>
+        <v>-0.003084936000426808</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2980084276633619</v>
+        <v>0.04551231276116141</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2873275007644196</v>
+        <v>0.02454540806120065</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2334422562106511</v>
+        <v>0.01955512519400315</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3587076830492748</v>
+        <v>-0.1337365299312978</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4098898261919217</v>
+        <v>-0.1836195701591805</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4713691233981194</v>
+        <v>-0.1877518349510652</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5367457045411754</v>
+        <v>-0.2816166269196216</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4255928899513464</v>
+        <v>-0.141351578689985</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5369174338747484</v>
+        <v>-0.2220155865761626</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5911117176128116</v>
+        <v>-0.2163277127376162</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6743505730194244</v>
+        <v>-0.2979671170154887</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.5030496162340725</v>
+        <v>-0.09722329375535566</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.5524037366142664</v>
+        <v>-0.1450312798172888</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4279221692496549</v>
+        <v>-0.05217664476958106</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4547683825690498</v>
+        <v>-0.1076824922583768</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.552166078577919</v>
+        <v>-0.11457079246658</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5884637803982073</v>
+        <v>-0.21112647698952</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.5711553538343637</v>
+        <v>-0.1332474231268179</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.6592709421088685</v>
+        <v>-0.2804037800568224</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6080437164240209</v>
+        <v>-0.1985459558584424</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5756331022007757</v>
+        <v>-0.2532586050406422</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 19.36</t>
+          <t>X &lt; 19.34</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3331</v>
+        <v>3356</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1524750204087155</v>
+        <v>-0.1244556715849967</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1432350063239838</v>
+        <v>0.08950077603159201</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2525451087841333</v>
+        <v>0.03524435087672373</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2029920861940369</v>
+        <v>0.1404364861966272</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1638799901162216</v>
+        <v>0.1480712546456573</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1094015593300739</v>
+        <v>0.1437894662333221</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2373341083018516</v>
+        <v>-0.01212917693184323</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2894296176374453</v>
+        <v>-0.06303502744784595</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3504420914974915</v>
+        <v>-0.06658306174865913</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.448639186929519</v>
+        <v>-0.19300258519268</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3666823047249679</v>
+        <v>-0.08184522661250782</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4786903776487037</v>
+        <v>-0.1633059521056026</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5074230581274719</v>
+        <v>-0.1325599880513124</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5912144641581705</v>
+        <v>-0.2148674129695536</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.423365328765712</v>
+        <v>-0.0177721707400238</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4400473740096373</v>
+        <v>-0.03329507380809105</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.346573962875766</v>
+        <v>0.02903843294676989</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3437559792100373</v>
+        <v>0.002978724503279295</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.4398056358063087</v>
+        <v>-0.002954631164698185</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4751329119570968</v>
+        <v>-0.09818067105208428</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4601414120444005</v>
+        <v>-0.02295764099631015</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.548172155219028</v>
+        <v>-0.1697810010615726</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4959735719105112</v>
+        <v>-0.08721555218815524</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4639842515929402</v>
+        <v>-0.1423431711045069</v>
       </c>
     </row>
   </sheetData>
